--- a/backend/data/reports/riwayat_hasil_ndt.xlsx
+++ b/backend/data/reports/riwayat_hasil_ndt.xlsx
@@ -440,21 +440,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -480,12 +483,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Keliling P (mm)</t>
+          <t>Luas Babbit (mm2)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Luas Babbit (mm2)</t>
+          <t>Luas Zone A (mm2)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -495,37 +498,52 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Luas Zone A (mm2)</t>
+          <t>Unbond Zone A (mm2)</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Total Unbond (mm2)</t>
+          <t>% Unbond Zone A</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Luas Bond (mm2)</t>
+          <t>Status Zone A</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Persen Unbond (%)</t>
+          <t>Unbond Zone C (mm2)</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>% Unbond Zone C</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Status Zone C</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Status Akhir</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Inspector</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>bearing</t>
+          <t>Bearing</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -533,43 +551,58 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Zona A</t>
+          <t>Zone C</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>565.49</v>
+        <v>57114.15</v>
       </c>
       <c r="F2" t="n">
-        <v>84823</v>
+        <v>30824.33</v>
       </c>
       <c r="G2" t="n">
-        <v>51548.67</v>
+        <v>26289.82</v>
       </c>
       <c r="H2" t="n">
-        <v>33274.33</v>
+        <v>11733</v>
       </c>
       <c r="I2" t="n">
-        <v>7270</v>
-      </c>
-      <c r="J2" t="n">
-        <v>44278.67</v>
+        <v>61.46</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
       </c>
       <c r="K2" t="n">
-        <v>16.42</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>REJECT</t>
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>kahfi</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>bearing</t>
+          <t>Bearing</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -577,39 +610,54 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Zona A</t>
+          <t>Zone C</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>565.49</v>
+        <v>57114.15</v>
       </c>
       <c r="F3" t="n">
-        <v>84823</v>
+        <v>30824.33</v>
       </c>
       <c r="G3" t="n">
-        <v>51548.67</v>
+        <v>26289.82</v>
       </c>
       <c r="H3" t="n">
-        <v>33274.33</v>
+        <v>39</v>
       </c>
       <c r="I3" t="n">
-        <v>2720</v>
-      </c>
-      <c r="J3" t="n">
-        <v>48828.67</v>
+        <v>0.13</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
       </c>
       <c r="K3" t="n">
-        <v>5.57</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>REJECT</t>
+        <v>300</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -617,43 +665,58 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>360</v>
+        <v>19</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Zona A</t>
+          <t>zone D</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>565.49</v>
+        <v>22234.62</v>
       </c>
       <c r="F4" t="n">
-        <v>113097.34</v>
+        <v>36242.26</v>
       </c>
       <c r="G4" t="n">
-        <v>77323</v>
+        <v>-14007.63</v>
       </c>
       <c r="H4" t="n">
-        <v>35774.33</v>
+        <v>525</v>
       </c>
       <c r="I4" t="n">
-        <v>1100</v>
-      </c>
-      <c r="J4" t="n">
-        <v>76223</v>
+        <v>1.47</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
       </c>
       <c r="K4" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+        <v>2304</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-14.12</v>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -661,43 +724,58 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>360</v>
+        <v>21</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Zona A</t>
+          <t>zone a</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>565.49</v>
+        <v>692.72</v>
       </c>
       <c r="F5" t="n">
-        <v>113097.34</v>
+        <v>199.34</v>
       </c>
       <c r="G5" t="n">
-        <v>77323</v>
+        <v>493.39</v>
       </c>
       <c r="H5" t="n">
-        <v>35774.33</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>665</v>
-      </c>
-      <c r="J5" t="n">
-        <v>76658</v>
+        <v>0</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
       </c>
       <c r="K5" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+        <v>6371</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-108.39</v>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -705,43 +783,58 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>360</v>
+        <v>21</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Zona A</t>
+          <t>zone a</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>565.49</v>
+        <v>692.72</v>
       </c>
       <c r="F6" t="n">
-        <v>113097.34</v>
+        <v>199.34</v>
       </c>
       <c r="G6" t="n">
-        <v>77323</v>
+        <v>493.39</v>
       </c>
       <c r="H6" t="n">
-        <v>35774.33</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>500</v>
-      </c>
-      <c r="J6" t="n">
-        <v>76823</v>
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
       </c>
       <c r="K6" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+        <v>6371</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-108.39</v>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -749,43 +842,58 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>360</v>
+        <v>21</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Zona A</t>
+          <t>zone a</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>565.49</v>
+        <v>692.72</v>
       </c>
       <c r="F7" t="n">
-        <v>113097.34</v>
+        <v>199.34</v>
       </c>
       <c r="G7" t="n">
-        <v>77323</v>
+        <v>493.39</v>
       </c>
       <c r="H7" t="n">
-        <v>35774.33</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>800</v>
-      </c>
-      <c r="J7" t="n">
-        <v>76523</v>
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
       </c>
       <c r="K7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+        <v>341</v>
+      </c>
+      <c r="L7" t="n">
+        <v>223.78</v>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -793,81 +901,403 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>360</v>
+        <v>21</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Zona A</t>
+          <t>zone a</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>565.49</v>
+        <v>692.72</v>
       </c>
       <c r="F8" t="n">
-        <v>113097.34</v>
+        <v>199.34</v>
       </c>
       <c r="G8" t="n">
-        <v>77323</v>
+        <v>493.39</v>
       </c>
       <c r="H8" t="n">
-        <v>35774.33</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>820</v>
-      </c>
-      <c r="J8" t="n">
-        <v>76503</v>
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
       </c>
       <c r="K8" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+        <v>341</v>
+      </c>
+      <c r="L8" t="n">
+        <v>223.78</v>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
+        <v>9</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>bearing</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>49</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1616.35</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2398.45</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-782.1</v>
+      </c>
+      <c r="J9" s="2" t="n"/>
+      <c r="M9" s="2" t="n"/>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>bearing</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>360</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Zona A</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>84823</v>
+      </c>
+      <c r="F10" t="n">
+        <v>33274.33</v>
+      </c>
+      <c r="G10" t="n">
+        <v>51548.67</v>
+      </c>
+      <c r="J10" s="2" t="n"/>
+      <c r="M10" s="2" t="n"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>bearing</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>360</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Zona A</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>84823</v>
+      </c>
+      <c r="F11" t="n">
+        <v>33274.33</v>
+      </c>
+      <c r="G11" t="n">
+        <v>51548.67</v>
+      </c>
+      <c r="J11" s="2" t="n"/>
+      <c r="M11" s="2" t="n"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>bearing</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>360</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Zona A</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>113097.34</v>
+      </c>
+      <c r="F12" t="n">
+        <v>35774.33</v>
+      </c>
+      <c r="G12" t="n">
+        <v>77323</v>
+      </c>
+      <c r="J12" s="2" t="n"/>
+      <c r="M12" s="2" t="n"/>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>5</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>bearing</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>360</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Zona A</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>113097.34</v>
+      </c>
+      <c r="F13" t="n">
+        <v>35774.33</v>
+      </c>
+      <c r="G13" t="n">
+        <v>77323</v>
+      </c>
+      <c r="J13" s="2" t="n"/>
+      <c r="M13" s="2" t="n"/>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>bearing</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>360</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Zona A</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>113097.34</v>
+      </c>
+      <c r="F14" t="n">
+        <v>35774.33</v>
+      </c>
+      <c r="G14" t="n">
+        <v>77323</v>
+      </c>
+      <c r="J14" s="2" t="n"/>
+      <c r="M14" s="2" t="n"/>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>3</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>bearing</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>360</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Zona A</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>113097.34</v>
+      </c>
+      <c r="F15" t="n">
+        <v>35774.33</v>
+      </c>
+      <c r="G15" t="n">
+        <v>77323</v>
+      </c>
+      <c r="J15" s="2" t="n"/>
+      <c r="M15" s="2" t="n"/>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>bearing</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>360</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Zona A</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>113097.34</v>
+      </c>
+      <c r="F16" t="n">
+        <v>35774.33</v>
+      </c>
+      <c r="G16" t="n">
+        <v>77323</v>
+      </c>
+      <c r="J16" s="2" t="n"/>
+      <c r="M16" s="2" t="n"/>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
         <v>1</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>bearing</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C17" t="n">
         <v>360</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Zona A</t>
         </is>
       </c>
-      <c r="E9" t="n">
-        <v>565.49</v>
-      </c>
-      <c r="F9" t="n">
+      <c r="E17" t="n">
         <v>113097.34</v>
       </c>
-      <c r="G9" t="n">
+      <c r="F17" t="n">
+        <v>35774.33</v>
+      </c>
+      <c r="G17" t="n">
         <v>77323</v>
       </c>
-      <c r="H9" t="n">
-        <v>35774.33</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1100</v>
-      </c>
-      <c r="J9" t="n">
-        <v>76223</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+      <c r="J17" s="2" t="n"/>
+      <c r="M17" s="2" t="n"/>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>

--- a/backend/data/reports/riwayat_hasil_ndt.xlsx
+++ b/backend/data/reports/riwayat_hasil_ndt.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -539,35 +539,35 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bearing</t>
+          <t>bearing</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>360</v>
+        <v>42</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Zone C</t>
+          <t>zone W</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>57114.15</v>
+        <v>4024.38</v>
       </c>
       <c r="F2" t="n">
-        <v>30824.33</v>
+        <v>4018.41</v>
       </c>
       <c r="G2" t="n">
-        <v>26289.82</v>
+        <v>5.97</v>
       </c>
       <c r="H2" t="n">
-        <v>11733</v>
+        <v>1683</v>
       </c>
       <c r="I2" t="n">
-        <v>61.46</v>
+        <v>72.06</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -575,14 +575,14 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1920</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+        <v>-100.31</v>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -592,72 +592,72 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>kahfi</t>
+          <t>admin</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bearing</t>
+          <t>bearing</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>360</v>
+        <v>18</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Zone C</t>
+          <t>zone D</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>57114.15</v>
+        <v>424.12</v>
       </c>
       <c r="F3" t="n">
-        <v>30824.33</v>
+        <v>-336.28</v>
       </c>
       <c r="G3" t="n">
-        <v>26289.82</v>
+        <v>760.4</v>
       </c>
       <c r="H3" t="n">
-        <v>39</v>
+        <v>204</v>
       </c>
       <c r="I3" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+        <v>-37.76</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>300</v>
+        <v>782</v>
       </c>
       <c r="L3" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+        <v>-3620.09</v>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>admin</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -673,19 +673,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>22234.62</v>
+        <v>424.12</v>
       </c>
       <c r="F4" t="n">
-        <v>36242.26</v>
+        <v>-336.28</v>
       </c>
       <c r="G4" t="n">
-        <v>-14007.63</v>
+        <v>760.4</v>
       </c>
       <c r="H4" t="n">
-        <v>525</v>
+        <v>204</v>
       </c>
       <c r="I4" t="n">
-        <v>1.47</v>
+        <v>-37.76</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -693,10 +693,10 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>2304</v>
+        <v>782</v>
       </c>
       <c r="L4" t="n">
-        <v>-14.12</v>
+        <v>-3620.09</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
@@ -710,35 +710,35 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>admin</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>bearing</t>
+          <t>Bearing</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21</v>
+        <v>360</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>zone a</t>
+          <t>Zone C</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>692.72</v>
+        <v>57114.15</v>
       </c>
       <c r="F5" t="n">
-        <v>199.34</v>
+        <v>12929.73</v>
       </c>
       <c r="G5" t="n">
-        <v>493.39</v>
+        <v>44184.42</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -752,69 +752,69 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>6371</v>
+        <v>231</v>
       </c>
       <c r="L5" t="n">
-        <v>-108.39</v>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>REJECT</t>
+        <v>0.53</v>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>kahfi</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>bearing</t>
+          <t>Bearing</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21</v>
+        <v>360</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>zone a</t>
+          <t>Zone C</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>692.72</v>
+        <v>57114.15</v>
       </c>
       <c r="F6" t="n">
-        <v>199.34</v>
+        <v>30824.33</v>
       </c>
       <c r="G6" t="n">
-        <v>493.39</v>
+        <v>26289.82</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>252</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+        <v>0.82</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>6371</v>
+        <v>1113</v>
       </c>
       <c r="L6" t="n">
-        <v>-108.39</v>
+        <v>4.42</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
@@ -828,56 +828,56 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>staff1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>bearing</t>
+          <t>Bearing</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>21</v>
+        <v>360</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>zone a</t>
+          <t>Zone C</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>692.72</v>
+        <v>57114.15</v>
       </c>
       <c r="F7" t="n">
-        <v>199.34</v>
+        <v>30824.33</v>
       </c>
       <c r="G7" t="n">
-        <v>493.39</v>
+        <v>26289.82</v>
       </c>
       <c r="H7" t="n">
+        <v>11733</v>
+      </c>
+      <c r="I7" t="n">
+        <v>61.46</v>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
         <v>0</v>
       </c>
-      <c r="I7" t="n">
+      <c r="L7" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>341</v>
-      </c>
-      <c r="L7" t="n">
-        <v>223.78</v>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>REJECT</t>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -887,41 +887,41 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>kahfi</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>bearing</t>
+          <t>Bearing</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21</v>
+        <v>360</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>zone a</t>
+          <t>Zone C</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>692.72</v>
+        <v>57114.15</v>
       </c>
       <c r="F8" t="n">
-        <v>199.34</v>
+        <v>30824.33</v>
       </c>
       <c r="G8" t="n">
-        <v>493.39</v>
+        <v>26289.82</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>341</v>
+        <v>300</v>
       </c>
       <c r="L8" t="n">
-        <v>223.78</v>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>REJECT</t>
+        <v>1.15</v>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -952,7 +952,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -960,27 +960,47 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>zone D</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1616.35</v>
+        <v>22234.62</v>
       </c>
       <c r="F9" t="n">
-        <v>2398.45</v>
+        <v>36242.26</v>
       </c>
       <c r="G9" t="n">
-        <v>-782.1</v>
-      </c>
-      <c r="J9" s="2" t="n"/>
-      <c r="M9" s="2" t="n"/>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+        <v>-14007.63</v>
+      </c>
+      <c r="H9" t="n">
+        <v>525</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>2304</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-14.12</v>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -991,7 +1011,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -999,24 +1019,44 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>360</v>
+        <v>21</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Zona A</t>
+          <t>zone a</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>84823</v>
+        <v>692.72</v>
       </c>
       <c r="F10" t="n">
-        <v>33274.33</v>
+        <v>199.34</v>
       </c>
       <c r="G10" t="n">
-        <v>51548.67</v>
-      </c>
-      <c r="J10" s="2" t="n"/>
-      <c r="M10" s="2" t="n"/>
+        <v>493.39</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>6371</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-108.39</v>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>REJECT</t>
@@ -1030,7 +1070,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1038,24 +1078,44 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>360</v>
+        <v>21</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Zona A</t>
+          <t>zone a</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>84823</v>
+        <v>692.72</v>
       </c>
       <c r="F11" t="n">
-        <v>33274.33</v>
+        <v>199.34</v>
       </c>
       <c r="G11" t="n">
-        <v>51548.67</v>
-      </c>
-      <c r="J11" s="2" t="n"/>
-      <c r="M11" s="2" t="n"/>
+        <v>493.39</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>6371</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-108.39</v>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>REJECT</t>
@@ -1069,7 +1129,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1077,27 +1137,47 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>360</v>
+        <v>21</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Zona A</t>
+          <t>zone a</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>113097.34</v>
+        <v>692.72</v>
       </c>
       <c r="F12" t="n">
-        <v>35774.33</v>
+        <v>199.34</v>
       </c>
       <c r="G12" t="n">
-        <v>77323</v>
-      </c>
-      <c r="J12" s="2" t="n"/>
-      <c r="M12" s="2" t="n"/>
-      <c r="N12" s="3" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+        <v>493.39</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>341</v>
+      </c>
+      <c r="L12" t="n">
+        <v>223.78</v>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1108,7 +1188,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1116,27 +1196,47 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>360</v>
+        <v>21</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Zona A</t>
+          <t>zone a</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>113097.34</v>
+        <v>692.72</v>
       </c>
       <c r="F13" t="n">
-        <v>35774.33</v>
+        <v>199.34</v>
       </c>
       <c r="G13" t="n">
-        <v>77323</v>
-      </c>
-      <c r="J13" s="2" t="n"/>
-      <c r="M13" s="2" t="n"/>
-      <c r="N13" s="3" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+        <v>493.39</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>341</v>
+      </c>
+      <c r="L13" t="n">
+        <v>223.78</v>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1147,7 +1247,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1155,21 +1255,21 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>360</v>
+        <v>49</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Zona A</t>
+          <t>b</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>113097.34</v>
+        <v>1616.35</v>
       </c>
       <c r="F14" t="n">
-        <v>35774.33</v>
+        <v>2398.45</v>
       </c>
       <c r="G14" t="n">
-        <v>77323</v>
+        <v>-782.1</v>
       </c>
       <c r="J14" s="2" t="n"/>
       <c r="M14" s="2" t="n"/>
@@ -1186,7 +1286,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1202,19 +1302,19 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>113097.34</v>
+        <v>84823</v>
       </c>
       <c r="F15" t="n">
-        <v>35774.33</v>
+        <v>33274.33</v>
       </c>
       <c r="G15" t="n">
-        <v>77323</v>
+        <v>51548.67</v>
       </c>
       <c r="J15" s="2" t="n"/>
       <c r="M15" s="2" t="n"/>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1225,7 +1325,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1241,19 +1341,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>113097.34</v>
+        <v>84823</v>
       </c>
       <c r="F16" t="n">
-        <v>35774.33</v>
+        <v>33274.33</v>
       </c>
       <c r="G16" t="n">
-        <v>77323</v>
+        <v>51548.67</v>
       </c>
       <c r="J16" s="2" t="n"/>
       <c r="M16" s="2" t="n"/>
-      <c r="N16" s="3" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1264,7 +1364,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1296,6 +1396,201 @@
         </is>
       </c>
       <c r="O17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>5</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>bearing</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>360</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Zona A</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>113097.34</v>
+      </c>
+      <c r="F18" t="n">
+        <v>35774.33</v>
+      </c>
+      <c r="G18" t="n">
+        <v>77323</v>
+      </c>
+      <c r="J18" s="2" t="n"/>
+      <c r="M18" s="2" t="n"/>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>4</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>bearing</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>360</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Zona A</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>113097.34</v>
+      </c>
+      <c r="F19" t="n">
+        <v>35774.33</v>
+      </c>
+      <c r="G19" t="n">
+        <v>77323</v>
+      </c>
+      <c r="J19" s="2" t="n"/>
+      <c r="M19" s="2" t="n"/>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>bearing</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>360</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Zona A</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>113097.34</v>
+      </c>
+      <c r="F20" t="n">
+        <v>35774.33</v>
+      </c>
+      <c r="G20" t="n">
+        <v>77323</v>
+      </c>
+      <c r="J20" s="2" t="n"/>
+      <c r="M20" s="2" t="n"/>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>bearing</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>360</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Zona A</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>113097.34</v>
+      </c>
+      <c r="F21" t="n">
+        <v>35774.33</v>
+      </c>
+      <c r="G21" t="n">
+        <v>77323</v>
+      </c>
+      <c r="J21" s="2" t="n"/>
+      <c r="M21" s="2" t="n"/>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>bearing</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>360</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Zona A</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>113097.34</v>
+      </c>
+      <c r="F22" t="n">
+        <v>35774.33</v>
+      </c>
+      <c r="G22" t="n">
+        <v>77323</v>
+      </c>
+      <c r="J22" s="2" t="n"/>
+      <c r="M22" s="2" t="n"/>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/backend/data/reports/riwayat_hasil_ndt.xlsx
+++ b/backend/data/reports/riwayat_hasil_ndt.xlsx
@@ -440,11 +440,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O22"/>
+  <dimension ref="A1:O30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
@@ -539,35 +539,35 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>bearing</t>
+          <t>bearing pltu</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>42</v>
+        <v>185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>zone W</t>
+          <t>zone</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4024.38</v>
+        <v>10170.91</v>
       </c>
       <c r="F2" t="n">
-        <v>4018.41</v>
+        <v>13779.87</v>
       </c>
       <c r="G2" t="n">
-        <v>5.97</v>
+        <v>-3608.96</v>
       </c>
       <c r="H2" t="n">
-        <v>1683</v>
+        <v>105</v>
       </c>
       <c r="I2" t="n">
-        <v>72.06</v>
+        <v>0.77</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -575,14 +575,14 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>1920</v>
+        <v>390</v>
       </c>
       <c r="L2" t="n">
-        <v>-100.31</v>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>REJECT</t>
+        <v>-9.75</v>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -598,35 +598,35 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>bearing</t>
+          <t>bearing pltu</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>18</v>
+        <v>185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>zone D</t>
+          <t>zone</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>424.12</v>
+        <v>10170.91</v>
       </c>
       <c r="F3" t="n">
-        <v>-336.28</v>
+        <v>13779.87</v>
       </c>
       <c r="G3" t="n">
-        <v>760.4</v>
+        <v>-3608.96</v>
       </c>
       <c r="H3" t="n">
-        <v>204</v>
+        <v>105</v>
       </c>
       <c r="I3" t="n">
-        <v>-37.76</v>
+        <v>0.77</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -634,14 +634,14 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>782</v>
+        <v>195</v>
       </c>
       <c r="L3" t="n">
-        <v>-3620.09</v>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>REJECT</t>
+        <v>-5.13</v>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -657,35 +657,35 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>bearing</t>
+          <t>bearing pltu</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>18</v>
+        <v>360</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>zone D</t>
+          <t>zone</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>424.12</v>
+        <v>57114.15</v>
       </c>
       <c r="F4" t="n">
-        <v>-336.28</v>
+        <v>30824.33</v>
       </c>
       <c r="G4" t="n">
-        <v>760.4</v>
+        <v>26289.82</v>
       </c>
       <c r="H4" t="n">
-        <v>204</v>
+        <v>2994.3</v>
       </c>
       <c r="I4" t="n">
-        <v>-37.76</v>
+        <v>10.76</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -693,10 +693,10 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>782</v>
+        <v>5600</v>
       </c>
       <c r="L4" t="n">
-        <v>-3620.09</v>
+        <v>27.07</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
@@ -716,11 +716,11 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bearing</t>
+          <t>bearing pltu</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -728,58 +728,58 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Zone C</t>
+          <t>zone</t>
         </is>
       </c>
       <c r="E5" t="n">
         <v>57114.15</v>
       </c>
       <c r="F5" t="n">
-        <v>12929.73</v>
+        <v>30824.33</v>
       </c>
       <c r="G5" t="n">
-        <v>44184.42</v>
+        <v>26289.82</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2994.3</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+        <v>10.76</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>231</v>
+        <v>600</v>
       </c>
       <c r="L5" t="n">
-        <v>0.53</v>
+        <v>2.34</v>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
           <t>ACCEPT</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>kahfi</t>
+          <t>admin</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bearing</t>
+          <t>bearing pltu</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -787,7 +787,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Zone C</t>
+          <t>zone</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -800,10 +800,10 @@
         <v>26289.82</v>
       </c>
       <c r="H6" t="n">
-        <v>252</v>
+        <v>2994.3</v>
       </c>
       <c r="I6" t="n">
-        <v>0.82</v>
+        <v>10.76</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -811,14 +811,14 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1113</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>REJECT</t>
+        <v>0</v>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -828,17 +828,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>staff1</t>
+          <t>admin</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bearing</t>
+          <t>bearing pltu</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Zone C</t>
+          <t>zone</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -859,10 +859,10 @@
         <v>26289.82</v>
       </c>
       <c r="H7" t="n">
-        <v>11733</v>
+        <v>2720</v>
       </c>
       <c r="I7" t="n">
-        <v>61.46</v>
+        <v>9.68</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -870,14 +870,14 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>4550</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+        <v>20.93</v>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -887,17 +887,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>kahfi</t>
+          <t>admin</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bearing</t>
+          <t>bearing pltu</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -905,7 +905,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Zone C</t>
+          <t>zone c</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -918,10 +918,10 @@
         <v>26289.82</v>
       </c>
       <c r="H8" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -929,30 +929,30 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>300</v>
+        <v>9448.15</v>
       </c>
       <c r="L8" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+        <v>56.1</v>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>admin</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -960,38 +960,38 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>19</v>
+        <v>61</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>zone D</t>
+          <t>zone y</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>22234.62</v>
+        <v>4024.38</v>
       </c>
       <c r="F9" t="n">
-        <v>36242.26</v>
+        <v>4390.93</v>
       </c>
       <c r="G9" t="n">
-        <v>-14007.63</v>
+        <v>-366.55</v>
       </c>
       <c r="H9" t="n">
-        <v>525</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>REJECT</t>
+        <v>0</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>2304</v>
+        <v>242</v>
       </c>
       <c r="L9" t="n">
-        <v>-14.12</v>
+        <v>-39.77</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
@@ -1005,13 +1005,13 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>admin</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1019,38 +1019,38 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>zone a</t>
+          <t>zone W</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>692.72</v>
+        <v>4024.38</v>
       </c>
       <c r="F10" t="n">
-        <v>199.34</v>
+        <v>4018.41</v>
       </c>
       <c r="G10" t="n">
-        <v>493.39</v>
+        <v>5.97</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1683</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+        <v>72.06</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>6371</v>
+        <v>1920</v>
       </c>
       <c r="L10" t="n">
-        <v>-108.39</v>
+        <v>-100.31</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
@@ -1064,13 +1064,13 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>admin</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1078,38 +1078,38 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>zone a</t>
+          <t>zone D</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>692.72</v>
+        <v>424.12</v>
       </c>
       <c r="F11" t="n">
-        <v>199.34</v>
+        <v>-336.28</v>
       </c>
       <c r="G11" t="n">
-        <v>493.39</v>
+        <v>760.4</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+        <v>-37.76</v>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>6371</v>
+        <v>782</v>
       </c>
       <c r="L11" t="n">
-        <v>-108.39</v>
+        <v>-3620.09</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
@@ -1123,13 +1123,13 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>admin</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1137,38 +1137,38 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>zone a</t>
+          <t>zone D</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>692.72</v>
+        <v>424.12</v>
       </c>
       <c r="F12" t="n">
-        <v>199.34</v>
+        <v>-336.28</v>
       </c>
       <c r="G12" t="n">
-        <v>493.39</v>
+        <v>760.4</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+        <v>-37.76</v>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>341</v>
+        <v>782</v>
       </c>
       <c r="L12" t="n">
-        <v>223.78</v>
+        <v>-3620.09</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
@@ -1182,35 +1182,35 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>admin</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>bearing</t>
+          <t>Bearing</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>21</v>
+        <v>360</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>zone a</t>
+          <t>Zone C</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>692.72</v>
+        <v>57114.15</v>
       </c>
       <c r="F13" t="n">
-        <v>199.34</v>
+        <v>12929.73</v>
       </c>
       <c r="G13" t="n">
-        <v>493.39</v>
+        <v>44184.42</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1224,73 +1224,93 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>341</v>
+        <v>231</v>
       </c>
       <c r="L13" t="n">
-        <v>223.78</v>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>REJECT</t>
+        <v>0.53</v>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>kahfi</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>bearing</t>
+          <t>Bearing</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>360</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>Zone C</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1616.35</v>
+        <v>57114.15</v>
       </c>
       <c r="F14" t="n">
-        <v>2398.45</v>
+        <v>30824.33</v>
       </c>
       <c r="G14" t="n">
-        <v>-782.1</v>
-      </c>
-      <c r="J14" s="2" t="n"/>
-      <c r="M14" s="2" t="n"/>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+        <v>26289.82</v>
+      </c>
+      <c r="H14" t="n">
+        <v>252</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>1113</v>
+      </c>
+      <c r="L14" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>staff1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>bearing</t>
+          <t>Bearing</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1298,20 +1318,40 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Zona A</t>
+          <t>Zone C</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>84823</v>
+        <v>57114.15</v>
       </c>
       <c r="F15" t="n">
-        <v>33274.33</v>
+        <v>30824.33</v>
       </c>
       <c r="G15" t="n">
-        <v>51548.67</v>
-      </c>
-      <c r="J15" s="2" t="n"/>
-      <c r="M15" s="2" t="n"/>
+        <v>26289.82</v>
+      </c>
+      <c r="H15" t="n">
+        <v>11733</v>
+      </c>
+      <c r="I15" t="n">
+        <v>61.46</v>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
           <t>REJECT</t>
@@ -1319,17 +1359,17 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>kahfi</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>bearing</t>
+          <t>Bearing</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1337,23 +1377,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Zona A</t>
+          <t>Zone C</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>84823</v>
+        <v>57114.15</v>
       </c>
       <c r="F16" t="n">
-        <v>33274.33</v>
+        <v>30824.33</v>
       </c>
       <c r="G16" t="n">
-        <v>51548.67</v>
-      </c>
-      <c r="J16" s="2" t="n"/>
-      <c r="M16" s="2" t="n"/>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>REJECT</t>
+        <v>26289.82</v>
+      </c>
+      <c r="H16" t="n">
+        <v>39</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>300</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1364,7 +1424,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1372,27 +1432,47 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>360</v>
+        <v>19</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Zona A</t>
+          <t>zone D</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>113097.34</v>
+        <v>22234.62</v>
       </c>
       <c r="F17" t="n">
-        <v>35774.33</v>
+        <v>36242.26</v>
       </c>
       <c r="G17" t="n">
-        <v>77323</v>
-      </c>
-      <c r="J17" s="2" t="n"/>
-      <c r="M17" s="2" t="n"/>
-      <c r="N17" s="3" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+        <v>-14007.63</v>
+      </c>
+      <c r="H17" t="n">
+        <v>525</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>2304</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-14.12</v>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1403,7 +1483,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1411,27 +1491,47 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>360</v>
+        <v>21</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Zona A</t>
+          <t>zone a</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>113097.34</v>
+        <v>692.72</v>
       </c>
       <c r="F18" t="n">
-        <v>35774.33</v>
+        <v>199.34</v>
       </c>
       <c r="G18" t="n">
-        <v>77323</v>
-      </c>
-      <c r="J18" s="2" t="n"/>
-      <c r="M18" s="2" t="n"/>
-      <c r="N18" s="3" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+        <v>493.39</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>6371</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-108.39</v>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1442,7 +1542,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1450,27 +1550,47 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>360</v>
+        <v>21</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Zona A</t>
+          <t>zone a</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>113097.34</v>
+        <v>692.72</v>
       </c>
       <c r="F19" t="n">
-        <v>35774.33</v>
+        <v>199.34</v>
       </c>
       <c r="G19" t="n">
-        <v>77323</v>
-      </c>
-      <c r="J19" s="2" t="n"/>
-      <c r="M19" s="2" t="n"/>
-      <c r="N19" s="3" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+        <v>493.39</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>6371</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-108.39</v>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1481,7 +1601,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1489,27 +1609,47 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>360</v>
+        <v>21</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Zona A</t>
+          <t>zone a</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>113097.34</v>
+        <v>692.72</v>
       </c>
       <c r="F20" t="n">
-        <v>35774.33</v>
+        <v>199.34</v>
       </c>
       <c r="G20" t="n">
-        <v>77323</v>
-      </c>
-      <c r="J20" s="2" t="n"/>
-      <c r="M20" s="2" t="n"/>
-      <c r="N20" s="3" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+        <v>493.39</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>341</v>
+      </c>
+      <c r="L20" t="n">
+        <v>223.78</v>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -1520,7 +1660,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1528,27 +1668,47 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>360</v>
+        <v>21</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Zona A</t>
+          <t>zone a</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>113097.34</v>
+        <v>692.72</v>
       </c>
       <c r="F21" t="n">
-        <v>35774.33</v>
+        <v>199.34</v>
       </c>
       <c r="G21" t="n">
-        <v>77323</v>
-      </c>
-      <c r="J21" s="2" t="n"/>
-      <c r="M21" s="2" t="n"/>
-      <c r="N21" s="3" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+        <v>493.39</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>341</v>
+      </c>
+      <c r="L21" t="n">
+        <v>223.78</v>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -1559,7 +1719,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1567,21 +1727,21 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>360</v>
+        <v>49</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Zona A</t>
+          <t>b</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>113097.34</v>
+        <v>1616.35</v>
       </c>
       <c r="F22" t="n">
-        <v>35774.33</v>
+        <v>2398.45</v>
       </c>
       <c r="G22" t="n">
-        <v>77323</v>
+        <v>-782.1</v>
       </c>
       <c r="J22" s="2" t="n"/>
       <c r="M22" s="2" t="n"/>
@@ -1591,6 +1751,318 @@
         </is>
       </c>
       <c r="O22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>8</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>bearing</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>360</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Zona A</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>84823</v>
+      </c>
+      <c r="F23" t="n">
+        <v>33274.33</v>
+      </c>
+      <c r="G23" t="n">
+        <v>51548.67</v>
+      </c>
+      <c r="J23" s="2" t="n"/>
+      <c r="M23" s="2" t="n"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>7</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>bearing</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>360</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Zona A</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>84823</v>
+      </c>
+      <c r="F24" t="n">
+        <v>33274.33</v>
+      </c>
+      <c r="G24" t="n">
+        <v>51548.67</v>
+      </c>
+      <c r="J24" s="2" t="n"/>
+      <c r="M24" s="2" t="n"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>bearing</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>360</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Zona A</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>113097.34</v>
+      </c>
+      <c r="F25" t="n">
+        <v>35774.33</v>
+      </c>
+      <c r="G25" t="n">
+        <v>77323</v>
+      </c>
+      <c r="J25" s="2" t="n"/>
+      <c r="M25" s="2" t="n"/>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>bearing</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>360</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Zona A</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>113097.34</v>
+      </c>
+      <c r="F26" t="n">
+        <v>35774.33</v>
+      </c>
+      <c r="G26" t="n">
+        <v>77323</v>
+      </c>
+      <c r="J26" s="2" t="n"/>
+      <c r="M26" s="2" t="n"/>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>bearing</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>360</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Zona A</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>113097.34</v>
+      </c>
+      <c r="F27" t="n">
+        <v>35774.33</v>
+      </c>
+      <c r="G27" t="n">
+        <v>77323</v>
+      </c>
+      <c r="J27" s="2" t="n"/>
+      <c r="M27" s="2" t="n"/>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>3</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>bearing</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>360</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Zona A</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>113097.34</v>
+      </c>
+      <c r="F28" t="n">
+        <v>35774.33</v>
+      </c>
+      <c r="G28" t="n">
+        <v>77323</v>
+      </c>
+      <c r="J28" s="2" t="n"/>
+      <c r="M28" s="2" t="n"/>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>bearing</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>360</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Zona A</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>113097.34</v>
+      </c>
+      <c r="F29" t="n">
+        <v>35774.33</v>
+      </c>
+      <c r="G29" t="n">
+        <v>77323</v>
+      </c>
+      <c r="J29" s="2" t="n"/>
+      <c r="M29" s="2" t="n"/>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>1</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>bearing</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>360</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Zona A</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>113097.34</v>
+      </c>
+      <c r="F30" t="n">
+        <v>35774.33</v>
+      </c>
+      <c r="G30" t="n">
+        <v>77323</v>
+      </c>
+      <c r="J30" s="2" t="n"/>
+      <c r="M30" s="2" t="n"/>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/backend/data/reports/riwayat_hasil_ndt.xlsx
+++ b/backend/data/reports/riwayat_hasil_ndt.xlsx
@@ -45,14 +45,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DC2626"/>
-        <bgColor rgb="00DC2626"/>
+        <fgColor rgb="0016A34A"/>
+        <bgColor rgb="0016A34A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0016A34A"/>
-        <bgColor rgb="0016A34A"/>
+        <fgColor rgb="00DC2626"/>
+        <bgColor rgb="00DC2626"/>
       </patternFill>
     </fill>
   </fills>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O22"/>
+  <dimension ref="A1:P29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -458,6 +458,7 @@
     <col width="17" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="17" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -536,209 +537,229 @@
           <t>Inspector</t>
         </is>
       </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Unit Asal</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>bearing</t>
+          <t>Bearing</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>42</v>
+        <v>150</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>zone W</t>
+          <t>Upper</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4024.38</v>
+        <v>23797.56</v>
       </c>
       <c r="F2" t="n">
-        <v>4018.41</v>
+        <v>6391.67</v>
       </c>
       <c r="G2" t="n">
-        <v>5.97</v>
+        <v>17405.89</v>
       </c>
       <c r="H2" t="n">
-        <v>1683</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>72.06</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>REJECT</t>
+          <t>ACCEPT</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>1920</v>
+        <v>100</v>
       </c>
       <c r="L2" t="n">
-        <v>-100.31</v>
+        <v>0.58</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>REJECT</t>
+          <t>ACCEPT</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>REJECT</t>
+          <t>ACCEPT</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>kahfi</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>PLTA Maninjau</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>bearing</t>
+          <t>Bearing</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>zone D</t>
+          <t>Upper</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>424.12</v>
+        <v>15150</v>
       </c>
       <c r="F3" t="n">
-        <v>-336.28</v>
+        <v>4662.16</v>
       </c>
       <c r="G3" t="n">
-        <v>760.4</v>
+        <v>10487.84</v>
       </c>
       <c r="H3" t="n">
-        <v>204</v>
+        <v>2720</v>
       </c>
       <c r="I3" t="n">
-        <v>-37.76</v>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
+        <v>140.05</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>REJECT</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>782</v>
+        <v>4550</v>
       </c>
       <c r="L3" t="n">
-        <v>-3620.09</v>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
+        <v>76.63</v>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>REJECT</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>kahfi</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>PLTA Maninjau</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>bearing</t>
+          <t>Bearing</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>zone D</t>
+          <t>Upper</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>424.12</v>
+        <v>15150</v>
       </c>
       <c r="F4" t="n">
-        <v>-336.28</v>
+        <v>4662.16</v>
       </c>
       <c r="G4" t="n">
-        <v>760.4</v>
+        <v>10487.84</v>
       </c>
       <c r="H4" t="n">
-        <v>204</v>
+        <v>2720</v>
       </c>
       <c r="I4" t="n">
-        <v>-37.76</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+        <v>140.05</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>REJECT</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>782</v>
+        <v>4550</v>
       </c>
       <c r="L4" t="n">
-        <v>-3620.09</v>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+        <v>76.63</v>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>REJECT</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>kahfi</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>PLTA Maninjau</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bearing</t>
+          <t>Beearing</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>360</v>
+        <v>150</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Zone C</t>
+          <t>Lower</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>57114.15</v>
+        <v>23797.56</v>
       </c>
       <c r="F5" t="n">
-        <v>12929.73</v>
+        <v>6391.67</v>
       </c>
       <c r="G5" t="n">
-        <v>44184.42</v>
+        <v>17405.89</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -746,23 +767,23 @@
       <c r="I5" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>ACCEPT</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>231</v>
+        <v>100</v>
       </c>
       <c r="L5" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
+        <v>0.58</v>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>ACCEPT</t>
         </is>
@@ -770,71 +791,81 @@
       <c r="O5" t="inlineStr">
         <is>
           <t>kahfi</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bearing</t>
+          <t>Beearing</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Zone C</t>
+          <t>Upper</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>57114.15</v>
+        <v>15150</v>
       </c>
       <c r="F6" t="n">
-        <v>30824.33</v>
+        <v>4662.16</v>
       </c>
       <c r="G6" t="n">
-        <v>26289.82</v>
+        <v>10487.84</v>
       </c>
       <c r="H6" t="n">
-        <v>252</v>
+        <v>2720</v>
       </c>
       <c r="I6" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
+        <v>140.05</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>REJECT</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1113</v>
+        <v>4550</v>
       </c>
       <c r="L6" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
+        <v>76.63</v>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
         <is>
           <t>REJECT</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>staff1</t>
+          <t>kahfi</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -842,58 +873,63 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>360</v>
+        <v>17</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Zone C</t>
+          <t>Lower</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>57114.15</v>
+        <v>721</v>
       </c>
       <c r="F7" t="n">
-        <v>30824.33</v>
+        <v>260.84</v>
       </c>
       <c r="G7" t="n">
-        <v>26289.82</v>
+        <v>460.16</v>
       </c>
       <c r="H7" t="n">
-        <v>11733</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>61.46</v>
+        <v>0</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>REJECT</t>
+          <t>ACCEPT</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1948</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-130.93</v>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>ACCEPT</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
         <is>
           <t>REJECT</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>kahfi</t>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -901,50 +937,55 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>360</v>
+        <v>65</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Zone C</t>
+          <t>Upper</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>57114.15</v>
+        <v>10822.79</v>
       </c>
       <c r="F8" t="n">
-        <v>30824.33</v>
+        <v>3962.32</v>
       </c>
       <c r="G8" t="n">
-        <v>26289.82</v>
+        <v>6860.47</v>
       </c>
       <c r="H8" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>ACCEPT</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>300</v>
+        <v>1560</v>
       </c>
       <c r="L8" t="n">
-        <v>1.15</v>
+        <v>29.43</v>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>ACCEPT</t>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>ACCEPT</t>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -952,7 +993,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -960,50 +1001,55 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>19</v>
+        <v>795</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>zone D</t>
+          <t>Upper</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>22234.62</v>
+        <v>427083.81</v>
       </c>
       <c r="F9" t="n">
-        <v>36242.26</v>
+        <v>104131</v>
       </c>
       <c r="G9" t="n">
-        <v>-14007.63</v>
+        <v>322952.81</v>
       </c>
       <c r="H9" t="n">
-        <v>525</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>REJECT</t>
+          <t>ACCEPT</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>2304</v>
+        <v>8612</v>
       </c>
       <c r="L9" t="n">
-        <v>-14.12</v>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
+        <v>2.74</v>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
         <is>
           <t>REJECT</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1011,7 +1057,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1019,21 +1065,21 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>21</v>
+        <v>123</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>zone a</t>
+          <t>Upper</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>692.72</v>
+        <v>5989.45</v>
       </c>
       <c r="F10" t="n">
-        <v>199.34</v>
+        <v>1351.65</v>
       </c>
       <c r="G10" t="n">
-        <v>493.39</v>
+        <v>4637.8</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1041,28 +1087,33 @@
       <c r="I10" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>ACCEPT</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>6371</v>
+        <v>1253</v>
       </c>
       <c r="L10" t="n">
-        <v>-108.39</v>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+        <v>37.02</v>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
         <is>
           <t>REJECT</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1070,7 +1121,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1078,21 +1129,21 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>21</v>
+        <v>123</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>zone a</t>
+          <t>Upper</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>692.72</v>
+        <v>5989.45</v>
       </c>
       <c r="F11" t="n">
-        <v>199.34</v>
+        <v>1351.65</v>
       </c>
       <c r="G11" t="n">
-        <v>493.39</v>
+        <v>4637.8</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1100,28 +1151,33 @@
       <c r="I11" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>ACCEPT</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>6371</v>
+        <v>1253</v>
       </c>
       <c r="L11" t="n">
-        <v>-108.39</v>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
+        <v>37.02</v>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
         <is>
           <t>REJECT</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1129,29 +1185,29 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>bearing</t>
+          <t>Bearing</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>21</v>
+        <v>234</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>zone a</t>
+          <t>Lower</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>692.72</v>
+        <v>158788.66</v>
       </c>
       <c r="F12" t="n">
-        <v>199.34</v>
+        <v>61617.57</v>
       </c>
       <c r="G12" t="n">
-        <v>493.39</v>
+        <v>97171.09</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1159,28 +1215,33 @@
       <c r="I12" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>ACCEPT</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>341</v>
+        <v>10620</v>
       </c>
       <c r="L12" t="n">
-        <v>223.78</v>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+        <v>12.27</v>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
         <is>
           <t>REJECT</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1188,7 +1249,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1196,50 +1257,51 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>21</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>zone a</t>
-        </is>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>692.72</v>
+        <v>5105.09</v>
       </c>
       <c r="F13" t="n">
-        <v>199.34</v>
+        <v>5748.34</v>
       </c>
       <c r="G13" t="n">
-        <v>493.39</v>
+        <v>-643.26</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>ACCEPT</t>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>341</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>223.78</v>
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
         <is>
           <t>REJECT</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1247,38 +1309,63 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>bearing</t>
+          <t>Bearing</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>Upper</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1616.35</v>
+        <v>15150</v>
       </c>
       <c r="F14" t="n">
-        <v>2398.45</v>
+        <v>4620</v>
       </c>
       <c r="G14" t="n">
-        <v>-782.1</v>
-      </c>
-      <c r="J14" s="2" t="n"/>
-      <c r="M14" s="2" t="n"/>
+        <v>10530</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2720</v>
+      </c>
+      <c r="I14" t="n">
+        <v>143.16</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>4550</v>
+      </c>
+      <c r="L14" t="n">
+        <v>76.09</v>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>ACCEPT</t>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
+        <is>
+          <t>kahfi</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1286,38 +1373,63 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>bearing</t>
+          <t>Bearing</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>360</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Zona A</t>
+          <t>Upper</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>84823</v>
+        <v>15135.25</v>
       </c>
       <c r="F15" t="n">
-        <v>33274.33</v>
+        <v>9868.5</v>
       </c>
       <c r="G15" t="n">
-        <v>51548.67</v>
-      </c>
-      <c r="J15" s="2" t="n"/>
-      <c r="M15" s="2" t="n"/>
-      <c r="N15" s="2" t="inlineStr">
+        <v>5266.75</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2720</v>
+      </c>
+      <c r="I15" t="n">
+        <v>38.05</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>4550</v>
+      </c>
+      <c r="L15" t="n">
+        <v>634.8099999999999</v>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
         <is>
           <t>REJECT</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
+        <is>
+          <t>kahfi</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1325,11 +1437,11 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>bearing</t>
+          <t>Bearing</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1337,7 +1449,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Zona A</t>
+          <t>Upper</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1349,14 +1461,39 @@
       <c r="G16" t="n">
         <v>51548.67</v>
       </c>
-      <c r="J16" s="2" t="n"/>
-      <c r="M16" s="2" t="n"/>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="H16" t="n">
+        <v>2720</v>
+      </c>
+      <c r="I16" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>4550</v>
+      </c>
+      <c r="L16" t="n">
+        <v>9.68</v>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
         <is>
           <t>REJECT</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
+        <is>
+          <t>kahfi</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1364,7 +1501,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1372,30 +1509,55 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>360</v>
+        <v>65</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Zona A</t>
+          <t>Upper</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>113097.34</v>
+        <v>5105.09</v>
       </c>
       <c r="F17" t="n">
-        <v>35774.33</v>
+        <v>5105.09</v>
       </c>
       <c r="G17" t="n">
-        <v>77323</v>
-      </c>
-      <c r="J17" s="2" t="n"/>
-      <c r="M17" s="2" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>14760</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-152.88</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>ACCEPT</t>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1403,11 +1565,11 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>bearing</t>
+          <t>Bearing</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1415,26 +1577,51 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Zona A</t>
+          <t>Zone C</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>113097.34</v>
+        <v>57114.15</v>
       </c>
       <c r="F18" t="n">
-        <v>35774.33</v>
+        <v>30824.33</v>
       </c>
       <c r="G18" t="n">
-        <v>77323</v>
-      </c>
-      <c r="J18" s="2" t="n"/>
-      <c r="M18" s="2" t="n"/>
-      <c r="N18" s="3" t="inlineStr">
+        <v>26289.82</v>
+      </c>
+      <c r="H18" t="n">
+        <v>39</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>300</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>ACCEPT</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1442,7 +1629,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1450,30 +1637,55 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>360</v>
+        <v>21</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Zona A</t>
+          <t>zone a</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>113097.34</v>
+        <v>692.72</v>
       </c>
       <c r="F19" t="n">
-        <v>35774.33</v>
+        <v>199.34</v>
       </c>
       <c r="G19" t="n">
-        <v>77323</v>
-      </c>
-      <c r="J19" s="2" t="n"/>
-      <c r="M19" s="2" t="n"/>
+        <v>493.39</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>6371</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-108.39</v>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>ACCEPT</t>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1481,7 +1693,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1489,30 +1701,55 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>360</v>
+        <v>21</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Zona A</t>
+          <t>zone a</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>113097.34</v>
+        <v>692.72</v>
       </c>
       <c r="F20" t="n">
-        <v>35774.33</v>
+        <v>199.34</v>
       </c>
       <c r="G20" t="n">
-        <v>77323</v>
-      </c>
-      <c r="J20" s="2" t="n"/>
-      <c r="M20" s="2" t="n"/>
+        <v>493.39</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>341</v>
+      </c>
+      <c r="L20" t="n">
+        <v>223.78</v>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>ACCEPT</t>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1520,7 +1757,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1528,30 +1765,35 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>360</v>
+        <v>49</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Zona A</t>
+          <t>b</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>113097.34</v>
+        <v>1616.35</v>
       </c>
       <c r="F21" t="n">
-        <v>35774.33</v>
+        <v>2398.45</v>
       </c>
       <c r="G21" t="n">
-        <v>77323</v>
-      </c>
-      <c r="J21" s="2" t="n"/>
-      <c r="M21" s="2" t="n"/>
-      <c r="N21" s="3" t="inlineStr">
+        <v>-782.1</v>
+      </c>
+      <c r="J21" s="3" t="n"/>
+      <c r="M21" s="3" t="n"/>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>ACCEPT</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1559,7 +1801,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1575,22 +1817,335 @@
         </is>
       </c>
       <c r="E22" t="n">
+        <v>84823</v>
+      </c>
+      <c r="F22" t="n">
+        <v>33274.33</v>
+      </c>
+      <c r="G22" t="n">
+        <v>51548.67</v>
+      </c>
+      <c r="J22" s="3" t="n"/>
+      <c r="M22" s="3" t="n"/>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>7</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>bearing</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>360</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Zona A</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>84823</v>
+      </c>
+      <c r="F23" t="n">
+        <v>33274.33</v>
+      </c>
+      <c r="G23" t="n">
+        <v>51548.67</v>
+      </c>
+      <c r="J23" s="3" t="n"/>
+      <c r="M23" s="3" t="n"/>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>6</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>bearing</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>360</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Zona A</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
         <v>113097.34</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F24" t="n">
         <v>35774.33</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G24" t="n">
         <v>77323</v>
       </c>
-      <c r="J22" s="2" t="n"/>
-      <c r="M22" s="2" t="n"/>
-      <c r="N22" s="3" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
+      <c r="J24" s="3" t="n"/>
+      <c r="M24" s="3" t="n"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>bearing</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>360</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Zona A</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>113097.34</v>
+      </c>
+      <c r="F25" t="n">
+        <v>35774.33</v>
+      </c>
+      <c r="G25" t="n">
+        <v>77323</v>
+      </c>
+      <c r="J25" s="3" t="n"/>
+      <c r="M25" s="3" t="n"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>bearing</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>360</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Zona A</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>113097.34</v>
+      </c>
+      <c r="F26" t="n">
+        <v>35774.33</v>
+      </c>
+      <c r="G26" t="n">
+        <v>77323</v>
+      </c>
+      <c r="J26" s="3" t="n"/>
+      <c r="M26" s="3" t="n"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>bearing</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>360</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Zona A</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>113097.34</v>
+      </c>
+      <c r="F27" t="n">
+        <v>35774.33</v>
+      </c>
+      <c r="G27" t="n">
+        <v>77323</v>
+      </c>
+      <c r="J27" s="3" t="n"/>
+      <c r="M27" s="3" t="n"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>bearing</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>360</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Zona A</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>113097.34</v>
+      </c>
+      <c r="F28" t="n">
+        <v>35774.33</v>
+      </c>
+      <c r="G28" t="n">
+        <v>77323</v>
+      </c>
+      <c r="J28" s="3" t="n"/>
+      <c r="M28" s="3" t="n"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>bearing</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>360</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Zona A</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>113097.34</v>
+      </c>
+      <c r="F29" t="n">
+        <v>35774.33</v>
+      </c>
+      <c r="G29" t="n">
+        <v>77323</v>
+      </c>
+      <c r="J29" s="3" t="n"/>
+      <c r="M29" s="3" t="n"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/backend/data/reports/riwayat_hasil_ndt.xlsx
+++ b/backend/data/reports/riwayat_hasil_ndt.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P29"/>
+  <dimension ref="A1:P31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -545,7 +545,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -553,7 +553,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>150</v>
+        <v>38</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -561,13 +561,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>23797.56</v>
+        <v>1432.57</v>
       </c>
       <c r="F2" t="n">
-        <v>6391.67</v>
+        <v>378.67</v>
       </c>
       <c r="G2" t="n">
-        <v>17405.89</v>
+        <v>1053.89</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -581,35 +581,35 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>100</v>
+        <v>312</v>
       </c>
       <c r="L2" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+        <v>42.05</v>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>kahfi</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>PLTA Maninjau</t>
+          <t>PLTU</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -625,30 +625,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>15150</v>
+        <v>1432.57</v>
       </c>
       <c r="F3" t="n">
-        <v>4662.16</v>
+        <v>378.67</v>
       </c>
       <c r="G3" t="n">
-        <v>10487.84</v>
+        <v>1053.89</v>
       </c>
       <c r="H3" t="n">
-        <v>2720</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>140.05</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>REJECT</t>
+        <v>0</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>4550</v>
+        <v>299</v>
       </c>
       <c r="L3" t="n">
-        <v>76.63</v>
+        <v>39.61</v>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
@@ -662,18 +662,18 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>kahfi</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>PLTA Maninjau</t>
+          <t>PLTU</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -689,39 +689,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>15150</v>
+        <v>23797.56</v>
       </c>
       <c r="F4" t="n">
-        <v>4662.16</v>
+        <v>6391.67</v>
       </c>
       <c r="G4" t="n">
-        <v>10487.84</v>
+        <v>17405.89</v>
       </c>
       <c r="H4" t="n">
-        <v>2720</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>140.05</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>REJECT</t>
+        <v>0</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>4550</v>
+        <v>100</v>
       </c>
       <c r="L4" t="n">
-        <v>76.63</v>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>REJECT</t>
+        <v>0.58</v>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -737,55 +737,55 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Beearing</t>
+          <t>Bearing</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Lower</t>
+          <t>Upper</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>23797.56</v>
+        <v>15150</v>
       </c>
       <c r="F5" t="n">
-        <v>6391.67</v>
+        <v>4662.16</v>
       </c>
       <c r="G5" t="n">
-        <v>17405.89</v>
+        <v>10487.84</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2720</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+        <v>140.05</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>100</v>
+        <v>4550</v>
       </c>
       <c r="L5" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+        <v>76.63</v>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -795,17 +795,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PLTA Maninjau</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Beearing</t>
+          <t>Bearing</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -859,21 +859,21 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PLTA Maninjau</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bearing</t>
+          <t>Beearing</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17</v>
+        <v>150</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -881,13 +881,13 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>721</v>
+        <v>23797.56</v>
       </c>
       <c r="F7" t="n">
-        <v>260.84</v>
+        <v>6391.67</v>
       </c>
       <c r="G7" t="n">
-        <v>460.16</v>
+        <v>17405.89</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -901,24 +901,24 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1948</v>
+        <v>100</v>
       </c>
       <c r="L7" t="n">
-        <v>-130.93</v>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t>REJECT</t>
+        <v>0.58</v>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>kahfi</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -929,15 +929,15 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bearing</t>
+          <t>Beearing</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -945,30 +945,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>10822.79</v>
+        <v>15150</v>
       </c>
       <c r="F8" t="n">
-        <v>3962.32</v>
+        <v>4662.16</v>
       </c>
       <c r="G8" t="n">
-        <v>6860.47</v>
+        <v>10487.84</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2720</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+        <v>140.05</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>1560</v>
+        <v>4550</v>
       </c>
       <c r="L8" t="n">
-        <v>29.43</v>
+        <v>76.63</v>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>kahfi</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -993,29 +993,29 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>bearing</t>
+          <t>Bearing</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>795</v>
+        <v>17</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Upper</t>
+          <t>Lower</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>427083.81</v>
+        <v>721</v>
       </c>
       <c r="F9" t="n">
-        <v>104131</v>
+        <v>260.84</v>
       </c>
       <c r="G9" t="n">
-        <v>322952.81</v>
+        <v>460.16</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>8612</v>
+        <v>1948</v>
       </c>
       <c r="L9" t="n">
-        <v>2.74</v>
+        <v>-130.93</v>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
@@ -1057,15 +1057,15 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>bearing</t>
+          <t>Bearing</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>123</v>
+        <v>65</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1073,13 +1073,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5989.45</v>
+        <v>10822.79</v>
       </c>
       <c r="F10" t="n">
-        <v>1351.65</v>
+        <v>3962.32</v>
       </c>
       <c r="G10" t="n">
-        <v>4637.8</v>
+        <v>6860.47</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1093,10 +1093,10 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>1253</v>
+        <v>1560</v>
       </c>
       <c r="L10" t="n">
-        <v>37.02</v>
+        <v>29.43</v>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>123</v>
+        <v>795</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1137,13 +1137,13 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5989.45</v>
+        <v>427083.81</v>
       </c>
       <c r="F11" t="n">
-        <v>1351.65</v>
+        <v>104131</v>
       </c>
       <c r="G11" t="n">
-        <v>4637.8</v>
+        <v>322952.81</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1157,10 +1157,10 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>1253</v>
+        <v>8612</v>
       </c>
       <c r="L11" t="n">
-        <v>37.02</v>
+        <v>2.74</v>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
@@ -1185,29 +1185,29 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bearing</t>
+          <t>bearing</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>234</v>
+        <v>123</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Lower</t>
+          <t>Upper</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>158788.66</v>
+        <v>5989.45</v>
       </c>
       <c r="F12" t="n">
-        <v>61617.57</v>
+        <v>1351.65</v>
       </c>
       <c r="G12" t="n">
-        <v>97171.09</v>
+        <v>4637.8</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1221,10 +1221,10 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>10620</v>
+        <v>1253</v>
       </c>
       <c r="L12" t="n">
-        <v>12.27</v>
+        <v>37.02</v>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1257,38 +1257,42 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>65</v>
-      </c>
-      <c r="D13" t="inlineStr"/>
+        <v>123</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Upper</t>
+        </is>
+      </c>
       <c r="E13" t="n">
-        <v>5105.09</v>
+        <v>5989.45</v>
       </c>
       <c r="F13" t="n">
-        <v>5748.34</v>
+        <v>1351.65</v>
       </c>
       <c r="G13" t="n">
-        <v>-643.26</v>
+        <v>4637.8</v>
       </c>
       <c r="H13" t="n">
-        <v>176</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>REJECT</t>
+        <v>0</v>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1253</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+        <v>37.02</v>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -1309,7 +1313,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1317,38 +1321,38 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>234</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Upper</t>
+          <t>Lower</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>15150</v>
+        <v>158788.66</v>
       </c>
       <c r="F14" t="n">
-        <v>4620</v>
+        <v>61617.57</v>
       </c>
       <c r="G14" t="n">
-        <v>10530</v>
+        <v>97171.09</v>
       </c>
       <c r="H14" t="n">
-        <v>2720</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>143.16</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>REJECT</t>
+        <v>0</v>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>4550</v>
+        <v>10620</v>
       </c>
       <c r="L14" t="n">
-        <v>76.09</v>
+        <v>12.27</v>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
@@ -1362,7 +1366,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>kahfi</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1373,35 +1377,31 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bearing</t>
+          <t>bearing</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>95.40000000000001</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Upper</t>
-        </is>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
-        <v>15135.25</v>
+        <v>5105.09</v>
       </c>
       <c r="F15" t="n">
-        <v>9868.5</v>
+        <v>5748.34</v>
       </c>
       <c r="G15" t="n">
-        <v>5266.75</v>
+        <v>-643.26</v>
       </c>
       <c r="H15" t="n">
-        <v>2720</v>
+        <v>176</v>
       </c>
       <c r="I15" t="n">
-        <v>38.05</v>
+        <v>3.16</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1409,14 +1409,14 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>4550</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>634.8099999999999</v>
-      </c>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t>REJECT</t>
+        <v>0</v>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>kahfi</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1437,7 +1437,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1453,19 +1453,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>84823</v>
+        <v>15150</v>
       </c>
       <c r="F16" t="n">
-        <v>33274.33</v>
+        <v>4620</v>
       </c>
       <c r="G16" t="n">
-        <v>51548.67</v>
+        <v>10530</v>
       </c>
       <c r="H16" t="n">
         <v>2720</v>
       </c>
       <c r="I16" t="n">
-        <v>8.9</v>
+        <v>143.16</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>4550</v>
       </c>
       <c r="L16" t="n">
-        <v>9.68</v>
+        <v>76.09</v>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
@@ -1501,15 +1501,15 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>bearing</t>
+          <t>Bearing</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>65</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1517,19 +1517,19 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5105.09</v>
+        <v>15135.25</v>
       </c>
       <c r="F17" t="n">
-        <v>5105.09</v>
+        <v>9868.5</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>5266.75</v>
       </c>
       <c r="H17" t="n">
-        <v>14760</v>
+        <v>2720</v>
       </c>
       <c r="I17" t="n">
-        <v>-152.88</v>
+        <v>38.05</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -1537,14 +1537,14 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>4550</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+        <v>634.8099999999999</v>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>kahfi</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -1565,7 +1565,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1577,48 +1577,48 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Zone C</t>
+          <t>Upper</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>57114.15</v>
+        <v>84823</v>
       </c>
       <c r="F18" t="n">
-        <v>30824.33</v>
+        <v>33274.33</v>
       </c>
       <c r="G18" t="n">
-        <v>26289.82</v>
+        <v>51548.67</v>
       </c>
       <c r="H18" t="n">
-        <v>39</v>
+        <v>2720</v>
       </c>
       <c r="I18" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+        <v>8.9</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>300</v>
+        <v>4550</v>
       </c>
       <c r="L18" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+        <v>9.68</v>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>kahfi</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -1629,7 +1629,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1637,42 +1637,42 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>zone a</t>
+          <t>Upper</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>692.72</v>
+        <v>5105.09</v>
       </c>
       <c r="F19" t="n">
-        <v>199.34</v>
+        <v>5105.09</v>
       </c>
       <c r="G19" t="n">
-        <v>493.39</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>14760</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+        <v>-152.88</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>6371</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>-108.39</v>
-      </c>
-      <c r="M19" s="3" t="inlineStr">
-        <is>
-          <t>REJECT</t>
+        <v>0</v>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -1693,35 +1693,35 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>bearing</t>
+          <t>Bearing</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>21</v>
+        <v>360</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>zone a</t>
+          <t>Zone C</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>692.72</v>
+        <v>57114.15</v>
       </c>
       <c r="F20" t="n">
-        <v>199.34</v>
+        <v>30824.33</v>
       </c>
       <c r="G20" t="n">
-        <v>493.39</v>
+        <v>26289.82</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
@@ -1729,19 +1729,19 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>341</v>
+        <v>300</v>
       </c>
       <c r="L20" t="n">
-        <v>223.78</v>
-      </c>
-      <c r="M20" s="3" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="N20" s="3" t="inlineStr">
-        <is>
-          <t>REJECT</t>
+        <v>1.15</v>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -1757,7 +1757,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1765,27 +1765,47 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>zone a</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1616.35</v>
+        <v>692.72</v>
       </c>
       <c r="F21" t="n">
-        <v>2398.45</v>
+        <v>199.34</v>
       </c>
       <c r="G21" t="n">
-        <v>-782.1</v>
-      </c>
-      <c r="J21" s="3" t="n"/>
-      <c r="M21" s="3" t="n"/>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+        <v>493.39</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>6371</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-108.39</v>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -1801,7 +1821,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1809,24 +1829,44 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>360</v>
+        <v>21</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Zona A</t>
+          <t>zone a</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>84823</v>
+        <v>692.72</v>
       </c>
       <c r="F22" t="n">
-        <v>33274.33</v>
+        <v>199.34</v>
       </c>
       <c r="G22" t="n">
-        <v>51548.67</v>
-      </c>
-      <c r="J22" s="3" t="n"/>
-      <c r="M22" s="3" t="n"/>
+        <v>493.39</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>341</v>
+      </c>
+      <c r="L22" t="n">
+        <v>223.78</v>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
           <t>REJECT</t>
@@ -1845,7 +1885,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1853,27 +1893,27 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>360</v>
+        <v>49</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Zona A</t>
+          <t>b</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>84823</v>
+        <v>1616.35</v>
       </c>
       <c r="F23" t="n">
-        <v>33274.33</v>
+        <v>2398.45</v>
       </c>
       <c r="G23" t="n">
-        <v>51548.67</v>
+        <v>-782.1</v>
       </c>
       <c r="J23" s="3" t="n"/>
       <c r="M23" s="3" t="n"/>
-      <c r="N23" s="3" t="inlineStr">
-        <is>
-          <t>REJECT</t>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -1889,7 +1929,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1905,19 +1945,19 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>113097.34</v>
+        <v>84823</v>
       </c>
       <c r="F24" t="n">
-        <v>35774.33</v>
+        <v>33274.33</v>
       </c>
       <c r="G24" t="n">
-        <v>77323</v>
+        <v>51548.67</v>
       </c>
       <c r="J24" s="3" t="n"/>
       <c r="M24" s="3" t="n"/>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -1933,7 +1973,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1949,19 +1989,19 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>113097.34</v>
+        <v>84823</v>
       </c>
       <c r="F25" t="n">
-        <v>35774.33</v>
+        <v>33274.33</v>
       </c>
       <c r="G25" t="n">
-        <v>77323</v>
+        <v>51548.67</v>
       </c>
       <c r="J25" s="3" t="n"/>
       <c r="M25" s="3" t="n"/>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -1977,7 +2017,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -2021,7 +2061,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -2065,7 +2105,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -2109,7 +2149,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -2146,6 +2186,94 @@
         </is>
       </c>
       <c r="P29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>bearing</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>360</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Zona A</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>113097.34</v>
+      </c>
+      <c r="F30" t="n">
+        <v>35774.33</v>
+      </c>
+      <c r="G30" t="n">
+        <v>77323</v>
+      </c>
+      <c r="J30" s="3" t="n"/>
+      <c r="M30" s="3" t="n"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>1</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>bearing</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>360</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Zona A</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>113097.34</v>
+      </c>
+      <c r="F31" t="n">
+        <v>35774.33</v>
+      </c>
+      <c r="G31" t="n">
+        <v>77323</v>
+      </c>
+      <c r="J31" s="3" t="n"/>
+      <c r="M31" s="3" t="n"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/backend/data/reports/riwayat_hasil_ndt.xlsx
+++ b/backend/data/reports/riwayat_hasil_ndt.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet name="Riwayat Hasil NDT" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Riwayat Hasil NDT'!$11:$11</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,7 +29,26 @@
     </font>
     <font>
       <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="5">
@@ -56,7 +77,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -64,17 +85,138 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -149,6 +291,36 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="624862" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -438,19 +610,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P31"/>
+  <dimension ref="A1:P50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="10.09" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="16.82" customWidth="1" min="5" max="5"/>
+    <col width="17.09" customWidth="1" min="6" max="6"/>
+    <col width="16.91" customWidth="1" min="7" max="7"/>
+    <col width="20.09" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
     <col width="17" customWidth="1" min="10" max="10"/>
     <col width="23" customWidth="1" min="11" max="11"/>
@@ -461,1825 +633,2276 @@
     <col width="17" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="18" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>PT PLN (PERSERO) PUSHARLIS</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="n"/>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+      <c r="O1" s="3" t="n"/>
+      <c r="P1" s="4" t="n"/>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="5" t="n"/>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>UNIT PELAKSANA PRODUKSI DAN WORKSHOP III</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="n"/>
+      <c r="D2" s="7" t="n"/>
+      <c r="E2" s="7" t="n"/>
+      <c r="F2" s="7" t="n"/>
+      <c r="G2" s="7" t="n"/>
+      <c r="H2" s="7" t="n"/>
+      <c r="I2" s="7" t="n"/>
+      <c r="J2" s="7" t="n"/>
+      <c r="K2" s="7" t="n"/>
+      <c r="L2" s="7" t="n"/>
+      <c r="M2" s="7" t="n"/>
+      <c r="N2" s="7" t="n"/>
+      <c r="O2" s="7" t="n"/>
+      <c r="P2" s="8" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="5" t="n"/>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Jl. Banten No. 10 Bandung 40272</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="n"/>
+      <c r="D3" s="7" t="n"/>
+      <c r="E3" s="7" t="n"/>
+      <c r="F3" s="7" t="n"/>
+      <c r="G3" s="7" t="n"/>
+      <c r="H3" s="7" t="n"/>
+      <c r="I3" s="7" t="n"/>
+      <c r="J3" s="7" t="n"/>
+      <c r="K3" s="7" t="n"/>
+      <c r="L3" s="7" t="n"/>
+      <c r="M3" s="7" t="n"/>
+      <c r="N3" s="7" t="n"/>
+      <c r="O3" s="7" t="n"/>
+      <c r="P3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="10" t="n"/>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>Telp (022) 7236791, 7236792, 7236793 Faks (022) 7236794 | e-mail: pusharlis@pln.co.id</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="n"/>
+      <c r="D4" s="12" t="n"/>
+      <c r="E4" s="12" t="n"/>
+      <c r="F4" s="12" t="n"/>
+      <c r="G4" s="12" t="n"/>
+      <c r="H4" s="12" t="n"/>
+      <c r="I4" s="12" t="n"/>
+      <c r="J4" s="12" t="n"/>
+      <c r="K4" s="12" t="n"/>
+      <c r="L4" s="12" t="n"/>
+      <c r="M4" s="12" t="n"/>
+      <c r="N4" s="12" t="n"/>
+      <c r="O4" s="12" t="n"/>
+      <c r="P4" s="13" t="n"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>LAPORAN RIWAYAT INSPEKSI NDT</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="n"/>
+      <c r="C5" s="15" t="n"/>
+      <c r="D5" s="15" t="n"/>
+      <c r="E5" s="15" t="n"/>
+      <c r="F5" s="15" t="n"/>
+      <c r="G5" s="15" t="n"/>
+      <c r="H5" s="15" t="n"/>
+      <c r="I5" s="15" t="n"/>
+      <c r="J5" s="15" t="n"/>
+      <c r="K5" s="15" t="n"/>
+      <c r="L5" s="15" t="n"/>
+      <c r="M5" s="15" t="n"/>
+      <c r="N5" s="15" t="n"/>
+      <c r="O5" s="15" t="n"/>
+      <c r="P5" s="16" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Nama Sistem</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>: NDT Inspection System</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="4" t="n"/>
+      <c r="I6" s="1" t="inlineStr">
+        <is>
+          <t>Tanggal Cetak</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="n"/>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>: 20 Oktober 2026</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="n"/>
+      <c r="M6" s="3" t="n"/>
+      <c r="N6" s="3" t="n"/>
+      <c r="O6" s="3" t="n"/>
+      <c r="P6" s="4" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Jenis Laporan</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>: Riwayat Inspeksi</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="7" t="n"/>
+      <c r="H7" s="8" t="n"/>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>Dicetak Oleh</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="n"/>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>: admin</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="n"/>
+      <c r="M7" s="7" t="n"/>
+      <c r="N7" s="7" t="n"/>
+      <c r="O7" s="7" t="n"/>
+      <c r="P7" s="8" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Standar Acuan</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>: DOD-STD-2183 (SH)</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="7" t="n"/>
+      <c r="G8" s="7" t="n"/>
+      <c r="H8" s="8" t="n"/>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>Jumlah Inspeksi</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="n"/>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>: 30 data</t>
+        </is>
+      </c>
+      <c r="L8" s="7" t="n"/>
+      <c r="M8" s="7" t="n"/>
+      <c r="N8" s="7" t="n"/>
+      <c r="O8" s="7" t="n"/>
+      <c r="P8" s="8" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Pelaksana</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="n"/>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>: Workshop PLN Pusharlis</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="n"/>
+      <c r="E9" s="12" t="n"/>
+      <c r="F9" s="12" t="n"/>
+      <c r="G9" s="12" t="n"/>
+      <c r="H9" s="13" t="n"/>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>Ringkasan Status</t>
+        </is>
+      </c>
+      <c r="J9" s="12" t="n"/>
+      <c r="K9" s="12" t="inlineStr">
+        <is>
+          <t>: ACCEPT: 10  |  REJECT: 20</t>
+        </is>
+      </c>
+      <c r="L9" s="12" t="n"/>
+      <c r="M9" s="12" t="n"/>
+      <c r="N9" s="12" t="n"/>
+      <c r="O9" s="12" t="n"/>
+      <c r="P9" s="13" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>Jenis Benda</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>Diameter (mm)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>Zona</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>Luas Babbit (mm2)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>Luas Zone A (mm2)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G11" s="17" t="inlineStr">
         <is>
           <t>Luas Zone C (mm2)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H11" s="17" t="inlineStr">
         <is>
           <t>Unbond Zone A (mm2)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I11" s="17" t="inlineStr">
         <is>
           <t>% Unbond Zone A</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J11" s="17" t="inlineStr">
         <is>
           <t>Status Zone A</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K11" s="17" t="inlineStr">
         <is>
           <t>Unbond Zone C (mm2)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L11" s="17" t="inlineStr">
         <is>
           <t>% Unbond Zone C</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M11" s="17" t="inlineStr">
         <is>
           <t>Status Zone C</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N11" s="17" t="inlineStr">
         <is>
           <t>Status Akhir</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O11" s="17" t="inlineStr">
         <is>
           <t>Inspector</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P11" s="17" t="inlineStr">
         <is>
           <t>Unit Asal</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="12">
+      <c r="A12" s="18" t="n">
         <v>54</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B12" s="19" t="inlineStr">
         <is>
           <t>Bearing</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C12" s="19" t="n">
         <v>38</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D12" s="19" t="inlineStr">
         <is>
           <t>Upper</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E12" s="19" t="n">
         <v>1432.57</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F12" s="19" t="n">
         <v>378.67</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G12" s="19" t="n">
         <v>1053.89</v>
       </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="H12" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="20" t="inlineStr">
         <is>
           <t>ACCEPT</t>
         </is>
       </c>
-      <c r="K2" t="n">
+      <c r="K12" s="19" t="n">
         <v>312</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L12" s="19" t="n">
         <v>42.05</v>
       </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="M12" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="N12" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="O12" s="19" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P12" s="19" t="inlineStr">
         <is>
           <t>PLTU</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="13">
+      <c r="A13" s="18" t="n">
         <v>53</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B13" s="19" t="inlineStr">
         <is>
           <t>Bearing</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C13" s="19" t="n">
         <v>38</v>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D13" s="19" t="inlineStr">
         <is>
           <t>Upper</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E13" s="19" t="n">
         <v>1432.57</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F13" s="19" t="n">
         <v>378.67</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G13" s="19" t="n">
         <v>1053.89</v>
       </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="H13" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="20" t="inlineStr">
         <is>
           <t>ACCEPT</t>
         </is>
       </c>
-      <c r="K3" t="n">
+      <c r="K13" s="19" t="n">
         <v>299</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L13" s="19" t="n">
         <v>39.61</v>
       </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="M13" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="N13" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="O13" s="19" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P13" s="19" t="inlineStr">
         <is>
           <t>PLTU</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="14">
+      <c r="A14" s="18" t="n">
         <v>52</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B14" s="19" t="inlineStr">
         <is>
           <t>Bearing</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C14" s="19" t="n">
         <v>150</v>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D14" s="19" t="inlineStr">
         <is>
           <t>Upper</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E14" s="19" t="n">
         <v>23797.56</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F14" s="19" t="n">
         <v>6391.67</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G14" s="19" t="n">
         <v>17405.89</v>
       </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="H14" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="20" t="inlineStr">
         <is>
           <t>ACCEPT</t>
         </is>
       </c>
-      <c r="K4" t="n">
+      <c r="K14" s="19" t="n">
         <v>100</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L14" s="19" t="n">
         <v>0.58</v>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="M14" s="20" t="inlineStr">
         <is>
           <t>ACCEPT</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N14" s="20" t="inlineStr">
         <is>
           <t>ACCEPT</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O14" s="19" t="inlineStr">
         <is>
           <t>kahfi</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P14" s="19" t="inlineStr">
         <is>
           <t>PLTA Maninjau</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="15">
+      <c r="A15" s="18" t="n">
         <v>51</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B15" s="19" t="inlineStr">
         <is>
           <t>Bearing</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="inlineStr">
+      <c r="C15" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="19" t="inlineStr">
         <is>
           <t>Upper</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E15" s="19" t="n">
         <v>15150</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F15" s="19" t="n">
         <v>4662.16</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G15" s="19" t="n">
         <v>10487.84</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H15" s="19" t="n">
         <v>2720</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I15" s="19" t="n">
         <v>140.05</v>
       </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
+      <c r="J15" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="K15" s="19" t="n">
         <v>4550</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L15" s="19" t="n">
         <v>76.63</v>
       </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="M15" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="N15" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="O15" s="19" t="inlineStr">
         <is>
           <t>kahfi</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P15" s="19" t="inlineStr">
         <is>
           <t>PLTA Maninjau</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
+    <row r="16">
+      <c r="A16" s="18" t="n">
         <v>50</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B16" s="19" t="inlineStr">
         <is>
           <t>Bearing</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="inlineStr">
+      <c r="C16" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="19" t="inlineStr">
         <is>
           <t>Upper</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="E16" s="19" t="n">
         <v>15150</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F16" s="19" t="n">
         <v>4662.16</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G16" s="19" t="n">
         <v>10487.84</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H16" s="19" t="n">
         <v>2720</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I16" s="19" t="n">
         <v>140.05</v>
       </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
+      <c r="J16" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="K16" s="19" t="n">
         <v>4550</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L16" s="19" t="n">
         <v>76.63</v>
       </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="M16" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="N16" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="O16" s="19" t="inlineStr">
         <is>
           <t>kahfi</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P16" s="19" t="inlineStr">
         <is>
           <t>PLTA Maninjau</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
+    <row r="17">
+      <c r="A17" s="18" t="n">
         <v>49</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B17" s="19" t="inlineStr">
         <is>
           <t>Beearing</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C17" s="19" t="n">
         <v>150</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D17" s="19" t="inlineStr">
         <is>
           <t>Lower</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="E17" s="19" t="n">
         <v>23797.56</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F17" s="19" t="n">
         <v>6391.67</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G17" s="19" t="n">
         <v>17405.89</v>
       </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="H17" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="20" t="inlineStr">
         <is>
           <t>ACCEPT</t>
         </is>
       </c>
-      <c r="K7" t="n">
+      <c r="K17" s="19" t="n">
         <v>100</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L17" s="19" t="n">
         <v>0.58</v>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="M17" s="20" t="inlineStr">
         <is>
           <t>ACCEPT</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N17" s="20" t="inlineStr">
         <is>
           <t>ACCEPT</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="O17" s="19" t="inlineStr">
         <is>
           <t>kahfi</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
+      <c r="P17" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="18" t="n">
         <v>48</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B18" s="19" t="inlineStr">
         <is>
           <t>Beearing</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="inlineStr">
+      <c r="C18" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="19" t="inlineStr">
         <is>
           <t>Upper</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="E18" s="19" t="n">
         <v>15150</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F18" s="19" t="n">
         <v>4662.16</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G18" s="19" t="n">
         <v>10487.84</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H18" s="19" t="n">
         <v>2720</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I18" s="19" t="n">
         <v>140.05</v>
       </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
+      <c r="J18" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="K18" s="19" t="n">
         <v>4550</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L18" s="19" t="n">
         <v>76.63</v>
       </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="M18" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="N18" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="O18" s="19" t="inlineStr">
         <is>
           <t>kahfi</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
+      <c r="P18" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="18" t="n">
         <v>47</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B19" s="19" t="inlineStr">
         <is>
           <t>Bearing</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C19" s="19" t="n">
         <v>17</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D19" s="19" t="inlineStr">
         <is>
           <t>Lower</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="E19" s="19" t="n">
         <v>721</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F19" s="19" t="n">
         <v>260.84</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G19" s="19" t="n">
         <v>460.16</v>
       </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="H19" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="20" t="inlineStr">
         <is>
           <t>ACCEPT</t>
         </is>
       </c>
-      <c r="K9" t="n">
+      <c r="K19" s="19" t="n">
         <v>1948</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L19" s="19" t="n">
         <v>-130.93</v>
       </c>
-      <c r="M9" s="3" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="M19" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="N19" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="O19" s="19" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
+      <c r="P19" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="18" t="n">
         <v>46</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B20" s="19" t="inlineStr">
         <is>
           <t>Bearing</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C20" s="19" t="n">
         <v>65</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D20" s="19" t="inlineStr">
         <is>
           <t>Upper</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="E20" s="19" t="n">
         <v>10822.79</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F20" s="19" t="n">
         <v>3962.32</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G20" s="19" t="n">
         <v>6860.47</v>
       </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="H20" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="20" t="inlineStr">
         <is>
           <t>ACCEPT</t>
         </is>
       </c>
-      <c r="K10" t="n">
+      <c r="K20" s="19" t="n">
         <v>1560</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L20" s="19" t="n">
         <v>29.43</v>
       </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="M20" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="N20" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="O20" s="19" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
+      <c r="P20" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="18" t="n">
         <v>45</v>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B21" s="19" t="inlineStr">
         <is>
           <t>bearing</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C21" s="19" t="n">
         <v>795</v>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D21" s="19" t="inlineStr">
         <is>
           <t>Upper</t>
         </is>
       </c>
-      <c r="E11" t="n">
+      <c r="E21" s="19" t="n">
         <v>427083.81</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F21" s="19" t="n">
         <v>104131</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G21" s="19" t="n">
         <v>322952.81</v>
       </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="H21" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="20" t="inlineStr">
         <is>
           <t>ACCEPT</t>
         </is>
       </c>
-      <c r="K11" t="n">
+      <c r="K21" s="19" t="n">
         <v>8612</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L21" s="19" t="n">
         <v>2.74</v>
       </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
+      <c r="M21" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="N21" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="O21" s="19" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
+      <c r="P21" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="18" t="n">
         <v>44</v>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B22" s="19" t="inlineStr">
         <is>
           <t>bearing</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="C22" s="19" t="n">
         <v>123</v>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D22" s="19" t="inlineStr">
         <is>
           <t>Upper</t>
         </is>
       </c>
-      <c r="E12" t="n">
+      <c r="E22" s="19" t="n">
         <v>5989.45</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F22" s="19" t="n">
         <v>1351.65</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G22" s="19" t="n">
         <v>4637.8</v>
       </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="H22" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="20" t="inlineStr">
         <is>
           <t>ACCEPT</t>
         </is>
       </c>
-      <c r="K12" t="n">
+      <c r="K22" s="19" t="n">
         <v>1253</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L22" s="19" t="n">
         <v>37.02</v>
       </c>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="N12" s="3" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
+      <c r="M22" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="N22" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="O22" s="19" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
+      <c r="P22" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="18" t="n">
         <v>43</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B23" s="19" t="inlineStr">
         <is>
           <t>bearing</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="C23" s="19" t="n">
         <v>123</v>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D23" s="19" t="inlineStr">
         <is>
           <t>Upper</t>
         </is>
       </c>
-      <c r="E13" t="n">
+      <c r="E23" s="19" t="n">
         <v>5989.45</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F23" s="19" t="n">
         <v>1351.65</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G23" s="19" t="n">
         <v>4637.8</v>
       </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="H23" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="20" t="inlineStr">
         <is>
           <t>ACCEPT</t>
         </is>
       </c>
-      <c r="K13" t="n">
+      <c r="K23" s="19" t="n">
         <v>1253</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L23" s="19" t="n">
         <v>37.02</v>
       </c>
-      <c r="M13" s="3" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="N13" s="3" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
+      <c r="M23" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="N23" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="O23" s="19" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
+      <c r="P23" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="n">
         <v>42</v>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B24" s="19" t="inlineStr">
         <is>
           <t>Bearing</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="C24" s="19" t="n">
         <v>234</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D24" s="19" t="inlineStr">
         <is>
           <t>Lower</t>
         </is>
       </c>
-      <c r="E14" t="n">
+      <c r="E24" s="19" t="n">
         <v>158788.66</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F24" s="19" t="n">
         <v>61617.57</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G24" s="19" t="n">
         <v>97171.09</v>
       </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="H24" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="20" t="inlineStr">
         <is>
           <t>ACCEPT</t>
         </is>
       </c>
-      <c r="K14" t="n">
+      <c r="K24" s="19" t="n">
         <v>10620</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L24" s="19" t="n">
         <v>12.27</v>
       </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
+      <c r="M24" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="N24" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="O24" s="19" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
+      <c r="P24" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="18" t="n">
         <v>41</v>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B25" s="19" t="inlineStr">
         <is>
           <t>bearing</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="C25" s="19" t="n">
         <v>65</v>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="n">
+      <c r="D25" s="19" t="inlineStr"/>
+      <c r="E25" s="19" t="n">
         <v>5105.09</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F25" s="19" t="n">
         <v>5748.34</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G25" s="19" t="n">
         <v>-643.26</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H25" s="19" t="n">
         <v>176</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I25" s="19" t="n">
         <v>3.16</v>
       </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="J25" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="K25" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="20" t="inlineStr">
         <is>
           <t>ACCEPT</t>
         </is>
       </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
+      <c r="N25" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="O25" s="19" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
+      <c r="P25" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B26" s="19" t="inlineStr">
         <is>
           <t>Bearing</t>
         </is>
       </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="inlineStr">
+      <c r="C26" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="19" t="inlineStr">
         <is>
           <t>Upper</t>
         </is>
       </c>
-      <c r="E16" t="n">
+      <c r="E26" s="19" t="n">
         <v>15150</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F26" s="19" t="n">
         <v>4620</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G26" s="19" t="n">
         <v>10530</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H26" s="19" t="n">
         <v>2720</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I26" s="19" t="n">
         <v>143.16</v>
       </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
+      <c r="J26" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="K26" s="19" t="n">
         <v>4550</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L26" s="19" t="n">
         <v>76.09</v>
       </c>
-      <c r="M16" s="3" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
+      <c r="M26" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="N26" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="O26" s="19" t="inlineStr">
         <is>
           <t>kahfi</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
+      <c r="P26" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="18" t="n">
         <v>30</v>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B27" s="19" t="inlineStr">
         <is>
           <t>Bearing</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C27" s="19" t="n">
         <v>95.40000000000001</v>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D27" s="19" t="inlineStr">
         <is>
           <t>Upper</t>
         </is>
       </c>
-      <c r="E17" t="n">
+      <c r="E27" s="19" t="n">
         <v>15135.25</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F27" s="19" t="n">
         <v>9868.5</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G27" s="19" t="n">
         <v>5266.75</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H27" s="19" t="n">
         <v>2720</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I27" s="19" t="n">
         <v>38.05</v>
       </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
+      <c r="J27" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="K27" s="19" t="n">
         <v>4550</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L27" s="19" t="n">
         <v>634.8099999999999</v>
       </c>
-      <c r="M17" s="3" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="N17" s="3" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
+      <c r="M27" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="N27" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="O27" s="19" t="inlineStr">
         <is>
           <t>kahfi</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
+      <c r="P27" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="18" t="n">
         <v>29</v>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B28" s="19" t="inlineStr">
         <is>
           <t>Bearing</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="C28" s="19" t="n">
         <v>360</v>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D28" s="19" t="inlineStr">
         <is>
           <t>Upper</t>
         </is>
       </c>
-      <c r="E18" t="n">
+      <c r="E28" s="19" t="n">
         <v>84823</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F28" s="19" t="n">
         <v>33274.33</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G28" s="19" t="n">
         <v>51548.67</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H28" s="19" t="n">
         <v>2720</v>
       </c>
-      <c r="I18" t="n">
+      <c r="I28" s="19" t="n">
         <v>8.9</v>
       </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
+      <c r="J28" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="K28" s="19" t="n">
         <v>4550</v>
       </c>
-      <c r="L18" t="n">
+      <c r="L28" s="19" t="n">
         <v>9.68</v>
       </c>
-      <c r="M18" s="3" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="N18" s="3" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
+      <c r="M28" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="N28" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="O28" s="19" t="inlineStr">
         <is>
           <t>kahfi</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
+      <c r="P28" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="18" t="n">
         <v>28</v>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B29" s="19" t="inlineStr">
         <is>
           <t>bearing</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="C29" s="19" t="n">
         <v>65</v>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D29" s="19" t="inlineStr">
         <is>
           <t>Upper</t>
         </is>
       </c>
-      <c r="E19" t="n">
+      <c r="E29" s="19" t="n">
         <v>5105.09</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F29" s="19" t="n">
         <v>5105.09</v>
       </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
+      <c r="G29" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="19" t="n">
         <v>14760</v>
       </c>
-      <c r="I19" t="n">
+      <c r="I29" s="19" t="n">
         <v>-152.88</v>
       </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
+      <c r="J29" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="K29" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="20" t="inlineStr">
         <is>
           <t>ACCEPT</t>
         </is>
       </c>
-      <c r="N19" s="3" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
+      <c r="N29" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="O29" s="19" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
+      <c r="P29" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="18" t="n">
         <v>15</v>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B30" s="19" t="inlineStr">
         <is>
           <t>Bearing</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="C30" s="19" t="n">
         <v>360</v>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D30" s="19" t="inlineStr">
         <is>
           <t>Zone C</t>
         </is>
       </c>
-      <c r="E20" t="n">
+      <c r="E30" s="19" t="n">
         <v>57114.15</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F30" s="19" t="n">
         <v>30824.33</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G30" s="19" t="n">
         <v>26289.82</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H30" s="19" t="n">
         <v>39</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I30" s="19" t="n">
         <v>0.13</v>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="J30" s="20" t="inlineStr">
         <is>
           <t>ACCEPT</t>
         </is>
       </c>
-      <c r="K20" t="n">
+      <c r="K30" s="19" t="n">
         <v>300</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L30" s="19" t="n">
         <v>1.15</v>
       </c>
-      <c r="M20" s="2" t="inlineStr">
+      <c r="M30" s="20" t="inlineStr">
         <is>
           <t>ACCEPT</t>
         </is>
       </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="N30" s="20" t="inlineStr">
         <is>
           <t>ACCEPT</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
+      <c r="O30" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P30" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="18" t="n">
         <v>12</v>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B31" s="19" t="inlineStr">
         <is>
           <t>bearing</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="C31" s="19" t="n">
         <v>21</v>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D31" s="19" t="inlineStr">
         <is>
           <t>zone a</t>
         </is>
       </c>
-      <c r="E21" t="n">
+      <c r="E31" s="19" t="n">
         <v>692.72</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F31" s="19" t="n">
         <v>199.34</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G31" s="19" t="n">
         <v>493.39</v>
       </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="H31" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="20" t="inlineStr">
         <is>
           <t>ACCEPT</t>
         </is>
       </c>
-      <c r="K21" t="n">
+      <c r="K31" s="19" t="n">
         <v>6371</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L31" s="19" t="n">
         <v>-108.39</v>
       </c>
-      <c r="M21" s="3" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="N21" s="3" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
+      <c r="M31" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="N31" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="O31" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P31" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="18" t="n">
         <v>11</v>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B32" s="19" t="inlineStr">
         <is>
           <t>bearing</t>
         </is>
       </c>
-      <c r="C22" t="n">
+      <c r="C32" s="19" t="n">
         <v>21</v>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D32" s="19" t="inlineStr">
         <is>
           <t>zone a</t>
         </is>
       </c>
-      <c r="E22" t="n">
+      <c r="E32" s="19" t="n">
         <v>692.72</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F32" s="19" t="n">
         <v>199.34</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G32" s="19" t="n">
         <v>493.39</v>
       </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="H32" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="20" t="inlineStr">
         <is>
           <t>ACCEPT</t>
         </is>
       </c>
-      <c r="K22" t="n">
+      <c r="K32" s="19" t="n">
         <v>341</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L32" s="19" t="n">
         <v>223.78</v>
       </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="N22" s="3" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
+      <c r="M32" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="N32" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="O32" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P32" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="18" t="n">
         <v>9</v>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B33" s="19" t="inlineStr">
         <is>
           <t>bearing</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="C33" s="19" t="n">
         <v>49</v>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D33" s="19" t="inlineStr">
         <is>
           <t>b</t>
         </is>
       </c>
-      <c r="E23" t="n">
+      <c r="E33" s="19" t="n">
         <v>1616.35</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F33" s="19" t="n">
         <v>2398.45</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G33" s="19" t="n">
         <v>-782.1</v>
       </c>
-      <c r="J23" s="3" t="n"/>
-      <c r="M23" s="3" t="n"/>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="H33" s="19" t="n"/>
+      <c r="I33" s="19" t="n"/>
+      <c r="J33" s="19" t="n"/>
+      <c r="K33" s="19" t="n"/>
+      <c r="L33" s="19" t="n"/>
+      <c r="M33" s="19" t="n"/>
+      <c r="N33" s="20" t="inlineStr">
         <is>
           <t>ACCEPT</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
+      <c r="O33" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P33" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B34" s="19" t="inlineStr">
         <is>
           <t>bearing</t>
         </is>
       </c>
-      <c r="C24" t="n">
+      <c r="C34" s="19" t="n">
         <v>360</v>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D34" s="19" t="inlineStr">
         <is>
           <t>Zona A</t>
         </is>
       </c>
-      <c r="E24" t="n">
+      <c r="E34" s="19" t="n">
         <v>84823</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F34" s="19" t="n">
         <v>33274.33</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G34" s="19" t="n">
         <v>51548.67</v>
       </c>
-      <c r="J24" s="3" t="n"/>
-      <c r="M24" s="3" t="n"/>
-      <c r="N24" s="3" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
+      <c r="H34" s="19" t="n"/>
+      <c r="I34" s="19" t="n"/>
+      <c r="J34" s="19" t="n"/>
+      <c r="K34" s="19" t="n"/>
+      <c r="L34" s="19" t="n"/>
+      <c r="M34" s="19" t="n"/>
+      <c r="N34" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="O34" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P34" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="18" t="n">
         <v>7</v>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B35" s="19" t="inlineStr">
         <is>
           <t>bearing</t>
         </is>
       </c>
-      <c r="C25" t="n">
+      <c r="C35" s="19" t="n">
         <v>360</v>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D35" s="19" t="inlineStr">
         <is>
           <t>Zona A</t>
         </is>
       </c>
-      <c r="E25" t="n">
+      <c r="E35" s="19" t="n">
         <v>84823</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F35" s="19" t="n">
         <v>33274.33</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G35" s="19" t="n">
         <v>51548.67</v>
       </c>
-      <c r="J25" s="3" t="n"/>
-      <c r="M25" s="3" t="n"/>
-      <c r="N25" s="3" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
+      <c r="H35" s="19" t="n"/>
+      <c r="I35" s="19" t="n"/>
+      <c r="J35" s="19" t="n"/>
+      <c r="K35" s="19" t="n"/>
+      <c r="L35" s="19" t="n"/>
+      <c r="M35" s="19" t="n"/>
+      <c r="N35" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="O35" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P35" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B36" s="19" t="inlineStr">
         <is>
           <t>bearing</t>
         </is>
       </c>
-      <c r="C26" t="n">
+      <c r="C36" s="19" t="n">
         <v>360</v>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D36" s="19" t="inlineStr">
         <is>
           <t>Zona A</t>
         </is>
       </c>
-      <c r="E26" t="n">
+      <c r="E36" s="19" t="n">
         <v>113097.34</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F36" s="19" t="n">
         <v>35774.33</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G36" s="19" t="n">
         <v>77323</v>
       </c>
-      <c r="J26" s="3" t="n"/>
-      <c r="M26" s="3" t="n"/>
-      <c r="N26" s="2" t="inlineStr">
+      <c r="H36" s="19" t="n"/>
+      <c r="I36" s="19" t="n"/>
+      <c r="J36" s="19" t="n"/>
+      <c r="K36" s="19" t="n"/>
+      <c r="L36" s="19" t="n"/>
+      <c r="M36" s="19" t="n"/>
+      <c r="N36" s="20" t="inlineStr">
         <is>
           <t>ACCEPT</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
+      <c r="O36" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P36" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B37" s="19" t="inlineStr">
         <is>
           <t>bearing</t>
         </is>
       </c>
-      <c r="C27" t="n">
+      <c r="C37" s="19" t="n">
         <v>360</v>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D37" s="19" t="inlineStr">
         <is>
           <t>Zona A</t>
         </is>
       </c>
-      <c r="E27" t="n">
+      <c r="E37" s="19" t="n">
         <v>113097.34</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F37" s="19" t="n">
         <v>35774.33</v>
       </c>
-      <c r="G27" t="n">
+      <c r="G37" s="19" t="n">
         <v>77323</v>
       </c>
-      <c r="J27" s="3" t="n"/>
-      <c r="M27" s="3" t="n"/>
-      <c r="N27" s="2" t="inlineStr">
+      <c r="H37" s="19" t="n"/>
+      <c r="I37" s="19" t="n"/>
+      <c r="J37" s="19" t="n"/>
+      <c r="K37" s="19" t="n"/>
+      <c r="L37" s="19" t="n"/>
+      <c r="M37" s="19" t="n"/>
+      <c r="N37" s="20" t="inlineStr">
         <is>
           <t>ACCEPT</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
+      <c r="O37" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P37" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B38" s="19" t="inlineStr">
         <is>
           <t>bearing</t>
         </is>
       </c>
-      <c r="C28" t="n">
+      <c r="C38" s="19" t="n">
         <v>360</v>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D38" s="19" t="inlineStr">
         <is>
           <t>Zona A</t>
         </is>
       </c>
-      <c r="E28" t="n">
+      <c r="E38" s="19" t="n">
         <v>113097.34</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F38" s="19" t="n">
         <v>35774.33</v>
       </c>
-      <c r="G28" t="n">
+      <c r="G38" s="19" t="n">
         <v>77323</v>
       </c>
-      <c r="J28" s="3" t="n"/>
-      <c r="M28" s="3" t="n"/>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="H38" s="19" t="n"/>
+      <c r="I38" s="19" t="n"/>
+      <c r="J38" s="19" t="n"/>
+      <c r="K38" s="19" t="n"/>
+      <c r="L38" s="19" t="n"/>
+      <c r="M38" s="19" t="n"/>
+      <c r="N38" s="20" t="inlineStr">
         <is>
           <t>ACCEPT</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
+      <c r="O38" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P38" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B39" s="19" t="inlineStr">
         <is>
           <t>bearing</t>
         </is>
       </c>
-      <c r="C29" t="n">
+      <c r="C39" s="19" t="n">
         <v>360</v>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D39" s="19" t="inlineStr">
         <is>
           <t>Zona A</t>
         </is>
       </c>
-      <c r="E29" t="n">
+      <c r="E39" s="19" t="n">
         <v>113097.34</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F39" s="19" t="n">
         <v>35774.33</v>
       </c>
-      <c r="G29" t="n">
+      <c r="G39" s="19" t="n">
         <v>77323</v>
       </c>
-      <c r="J29" s="3" t="n"/>
-      <c r="M29" s="3" t="n"/>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="H39" s="19" t="n"/>
+      <c r="I39" s="19" t="n"/>
+      <c r="J39" s="19" t="n"/>
+      <c r="K39" s="19" t="n"/>
+      <c r="L39" s="19" t="n"/>
+      <c r="M39" s="19" t="n"/>
+      <c r="N39" s="20" t="inlineStr">
         <is>
           <t>ACCEPT</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
+      <c r="O39" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P39" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B40" s="19" t="inlineStr">
         <is>
           <t>bearing</t>
         </is>
       </c>
-      <c r="C30" t="n">
+      <c r="C40" s="19" t="n">
         <v>360</v>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D40" s="19" t="inlineStr">
         <is>
           <t>Zona A</t>
         </is>
       </c>
-      <c r="E30" t="n">
+      <c r="E40" s="19" t="n">
         <v>113097.34</v>
       </c>
-      <c r="F30" t="n">
+      <c r="F40" s="19" t="n">
         <v>35774.33</v>
       </c>
-      <c r="G30" t="n">
+      <c r="G40" s="19" t="n">
         <v>77323</v>
       </c>
-      <c r="J30" s="3" t="n"/>
-      <c r="M30" s="3" t="n"/>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="H40" s="19" t="n"/>
+      <c r="I40" s="19" t="n"/>
+      <c r="J40" s="19" t="n"/>
+      <c r="K40" s="19" t="n"/>
+      <c r="L40" s="19" t="n"/>
+      <c r="M40" s="19" t="n"/>
+      <c r="N40" s="20" t="inlineStr">
         <is>
           <t>ACCEPT</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
+      <c r="O40" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P40" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B41" s="19" t="inlineStr">
         <is>
           <t>bearing</t>
         </is>
       </c>
-      <c r="C31" t="n">
+      <c r="C41" s="19" t="n">
         <v>360</v>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D41" s="19" t="inlineStr">
         <is>
           <t>Zona A</t>
         </is>
       </c>
-      <c r="E31" t="n">
+      <c r="E41" s="19" t="n">
         <v>113097.34</v>
       </c>
-      <c r="F31" t="n">
+      <c r="F41" s="19" t="n">
         <v>35774.33</v>
       </c>
-      <c r="G31" t="n">
+      <c r="G41" s="19" t="n">
         <v>77323</v>
       </c>
-      <c r="J31" s="3" t="n"/>
-      <c r="M31" s="3" t="n"/>
-      <c r="N31" s="2" t="inlineStr">
+      <c r="H41" s="19" t="n"/>
+      <c r="I41" s="19" t="n"/>
+      <c r="J41" s="19" t="n"/>
+      <c r="K41" s="19" t="n"/>
+      <c r="L41" s="19" t="n"/>
+      <c r="M41" s="19" t="n"/>
+      <c r="N41" s="20" t="inlineStr">
         <is>
           <t>ACCEPT</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O41" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P41" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="D43" s="22" t="inlineStr">
+        <is>
+          <t>CHECKED BY</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="n"/>
+      <c r="F43" s="4" t="n"/>
+      <c r="H43" s="22" t="inlineStr">
+        <is>
+          <t>CHECKED BY</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="n"/>
+      <c r="J43" s="4" t="n"/>
+      <c r="L43" s="22" t="inlineStr">
+        <is>
+          <t>CHECKED BY</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="n"/>
+      <c r="N43" s="4" t="n"/>
+    </row>
+    <row r="44">
+      <c r="D44" s="23" t="inlineStr">
+        <is>
+          <t>TL QUALITY CONTROL</t>
+        </is>
+      </c>
+      <c r="E44" s="12" t="n"/>
+      <c r="F44" s="13" t="n"/>
+      <c r="H44" s="23" t="inlineStr">
+        <is>
+          <t>TL QUALITY CONTROL</t>
+        </is>
+      </c>
+      <c r="I44" s="12" t="n"/>
+      <c r="J44" s="13" t="n"/>
+      <c r="L44" s="23" t="inlineStr">
+        <is>
+          <t>TL QUALITY CONTROL</t>
+        </is>
+      </c>
+      <c r="M44" s="12" t="n"/>
+      <c r="N44" s="13" t="n"/>
+    </row>
+    <row r="45">
+      <c r="D45" s="22" t="n"/>
+      <c r="E45" s="3" t="n"/>
+      <c r="F45" s="4" t="n"/>
+      <c r="H45" s="22" t="n"/>
+      <c r="I45" s="3" t="n"/>
+      <c r="J45" s="4" t="n"/>
+      <c r="L45" s="22" t="n"/>
+      <c r="M45" s="3" t="n"/>
+      <c r="N45" s="4" t="n"/>
+    </row>
+    <row r="46">
+      <c r="D46" s="5" t="n"/>
+      <c r="E46" s="7" t="n"/>
+      <c r="F46" s="8" t="n"/>
+      <c r="H46" s="5" t="n"/>
+      <c r="I46" s="7" t="n"/>
+      <c r="J46" s="8" t="n"/>
+      <c r="L46" s="5" t="n"/>
+      <c r="M46" s="7" t="n"/>
+      <c r="N46" s="8" t="n"/>
+    </row>
+    <row r="47">
+      <c r="D47" s="5" t="n"/>
+      <c r="E47" s="7" t="n"/>
+      <c r="F47" s="8" t="n"/>
+      <c r="H47" s="5" t="n"/>
+      <c r="I47" s="7" t="n"/>
+      <c r="J47" s="8" t="n"/>
+      <c r="L47" s="5" t="n"/>
+      <c r="M47" s="7" t="n"/>
+      <c r="N47" s="8" t="n"/>
+    </row>
+    <row r="48">
+      <c r="D48" s="10" t="n"/>
+      <c r="E48" s="12" t="n"/>
+      <c r="F48" s="13" t="n"/>
+      <c r="H48" s="10" t="n"/>
+      <c r="I48" s="12" t="n"/>
+      <c r="J48" s="13" t="n"/>
+      <c r="L48" s="10" t="n"/>
+      <c r="M48" s="12" t="n"/>
+      <c r="N48" s="13" t="n"/>
+    </row>
+    <row r="49">
+      <c r="D49" s="24" t="inlineStr">
+        <is>
+          <t>BAGUS SANJAYA PUTRA</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="n"/>
+      <c r="F49" s="4" t="n"/>
+      <c r="H49" s="24" t="inlineStr">
+        <is>
+          <t>BAGUS SANJAYA PUTRA</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="n"/>
+      <c r="J49" s="4" t="n"/>
+      <c r="L49" s="24" t="inlineStr">
+        <is>
+          <t>BAGUS SANJAYA PUTRA</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="n"/>
+      <c r="N49" s="4" t="n"/>
+    </row>
+    <row r="50">
+      <c r="D50" s="10" t="n"/>
+      <c r="E50" s="12" t="n"/>
+      <c r="F50" s="13" t="n"/>
+      <c r="H50" s="10" t="n"/>
+      <c r="I50" s="12" t="n"/>
+      <c r="J50" s="13" t="n"/>
+      <c r="L50" s="10" t="n"/>
+      <c r="M50" s="12" t="n"/>
+      <c r="N50" s="13" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="33">
+    <mergeCell ref="A5:P5"/>
+    <mergeCell ref="B2:P2"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="L49:N50"/>
+    <mergeCell ref="C9:H9"/>
+    <mergeCell ref="B1:P1"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="K8:P8"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="L44:N44"/>
+    <mergeCell ref="D49:F50"/>
+    <mergeCell ref="C8:H8"/>
+    <mergeCell ref="C7:H7"/>
+    <mergeCell ref="K7:P7"/>
+    <mergeCell ref="H49:J50"/>
+    <mergeCell ref="K6:P6"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="B4:P4"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="H43:J43"/>
+    <mergeCell ref="D45:F48"/>
+    <mergeCell ref="C6:H6"/>
+    <mergeCell ref="H45:J48"/>
+    <mergeCell ref="K9:P9"/>
+    <mergeCell ref="H44:J44"/>
+    <mergeCell ref="L45:N48"/>
+    <mergeCell ref="B3:P3"/>
+    <mergeCell ref="L43:N43"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="I9:J9"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;RHalaman &amp;P dari &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/backend/data/reports/riwayat_hasil_ndt.xlsx
+++ b/backend/data/reports/riwayat_hasil_ndt.xlsx
@@ -45,14 +45,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DC2626"/>
-        <bgColor rgb="00DC2626"/>
+        <fgColor rgb="0016A34A"/>
+        <bgColor rgb="0016A34A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0016A34A"/>
-        <bgColor rgb="0016A34A"/>
+        <fgColor rgb="00DC2626"/>
+        <bgColor rgb="00DC2626"/>
       </patternFill>
     </fill>
   </fills>
@@ -440,13 +440,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O30"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -539,55 +539,55 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>bearing pltu</t>
+          <t>bearing contoh</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>185</v>
+        <v>360</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>zone</t>
+          <t>Lower</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>10170.91</v>
+        <v>57114.15</v>
       </c>
       <c r="F2" t="n">
-        <v>13779.87</v>
+        <v>13054.99</v>
       </c>
       <c r="G2" t="n">
-        <v>-3608.96</v>
+        <v>44059.16</v>
       </c>
       <c r="H2" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I2" t="n">
         <v>0.77</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>REJECT</t>
+          <t>ACCEPT</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>390</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-9.75</v>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>ACCEPT</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>REJECT</t>
+          <t>ACCEPT</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -598,53 +598,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>bearing pltu</t>
+          <t>bearing contoh</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>185</v>
+        <v>360</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>zone</t>
+          <t>Lower</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>10170.91</v>
+        <v>57114.15</v>
       </c>
       <c r="F3" t="n">
-        <v>13779.87</v>
+        <v>13054.99</v>
       </c>
       <c r="G3" t="n">
-        <v>-3608.96</v>
+        <v>44059.16</v>
       </c>
       <c r="H3" t="n">
-        <v>105</v>
+        <v>250</v>
       </c>
       <c r="I3" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
+        <v>1.95</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>REJECT</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>195</v>
+        <v>2020</v>
       </c>
       <c r="L3" t="n">
-        <v>-5.13</v>
+        <v>4.81</v>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>ACCEPT</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>REJECT</t>
         </is>
@@ -657,11 +657,11 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>bearing pltu</t>
+          <t>bearing contoh</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -669,58 +669,58 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>zone</t>
+          <t>Lower</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>57114.15</v>
+        <v>113097.34</v>
       </c>
       <c r="F4" t="n">
-        <v>30824.33</v>
+        <v>29019.47</v>
       </c>
       <c r="G4" t="n">
-        <v>26289.82</v>
+        <v>84077.87</v>
       </c>
       <c r="H4" t="n">
-        <v>2994.3</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>10.76</v>
+        <v>0</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>REJECT</t>
+          <t>ACCEPT</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>5600</v>
+        <v>1400</v>
       </c>
       <c r="L4" t="n">
-        <v>27.07</v>
+        <v>1.69</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>REJECT</t>
+          <t>ACCEPT</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>REJECT</t>
+          <t>ACCEPT</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>kahfi</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>bearing pltu</t>
+          <t>buku bearing</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -728,58 +728,58 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>zone</t>
+          <t>Lower</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>57114.15</v>
+        <v>113097.34</v>
       </c>
       <c r="F5" t="n">
-        <v>30824.33</v>
+        <v>29019.47</v>
       </c>
       <c r="G5" t="n">
-        <v>26289.82</v>
+        <v>84077.87</v>
       </c>
       <c r="H5" t="n">
-        <v>2994.3</v>
+        <v>1006.86</v>
       </c>
       <c r="I5" t="n">
-        <v>10.76</v>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+        <v>3.59</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>REJECT</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="L5" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
+        <v>0.36</v>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>REJECT</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>kahfi</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>bearing pltu</t>
+          <t>buku bearing</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -787,58 +787,58 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>zone</t>
+          <t>Lower</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>57114.15</v>
+        <v>113097.34</v>
       </c>
       <c r="F6" t="n">
-        <v>30824.33</v>
+        <v>29019.47</v>
       </c>
       <c r="G6" t="n">
-        <v>26289.82</v>
+        <v>84077.87</v>
       </c>
       <c r="H6" t="n">
-        <v>2994.3</v>
+        <v>200</v>
       </c>
       <c r="I6" t="n">
-        <v>10.76</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>REJECT</t>
+          <t>ACCEPT</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="3" t="inlineStr">
+        <v>1.08</v>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>ACCEPT</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>REJECT</t>
+          <t>ACCEPT</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>kahfi</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>bearing pltu</t>
+          <t>bearing</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -846,41 +846,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>zone</t>
+          <t>Lower</t>
         </is>
       </c>
       <c r="E7" t="n">
         <v>57114.15</v>
       </c>
       <c r="F7" t="n">
-        <v>30824.33</v>
+        <v>13054.99</v>
       </c>
       <c r="G7" t="n">
-        <v>26289.82</v>
+        <v>44059.16</v>
       </c>
       <c r="H7" t="n">
-        <v>2720</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>9.68</v>
+        <v>0</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>REJECT</t>
+          <t>ACCEPT</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>4550</v>
+        <v>5000</v>
       </c>
       <c r="L7" t="n">
-        <v>20.93</v>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+        <v>12.8</v>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
         <is>
           <t>REJECT</t>
         </is>
@@ -893,7 +893,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -905,17 +905,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>zone c</t>
+          <t>Lower</t>
         </is>
       </c>
       <c r="E8" t="n">
         <v>57114.15</v>
       </c>
       <c r="F8" t="n">
-        <v>30824.33</v>
+        <v>13054.99</v>
       </c>
       <c r="G8" t="n">
-        <v>26289.82</v>
+        <v>44059.16</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -923,23 +923,23 @@
       <c r="I8" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>ACCEPT</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>9448.15</v>
+        <v>5050</v>
       </c>
       <c r="L8" t="n">
-        <v>56.1</v>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+        <v>12.95</v>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
         <is>
           <t>REJECT</t>
         </is>
@@ -952,53 +952,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>bearing</t>
+          <t>pad bearing grati</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>zone y</t>
+          <t>Lower</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4024.38</v>
+        <v>15150</v>
       </c>
       <c r="F9" t="n">
-        <v>4390.93</v>
+        <v>4662.16</v>
       </c>
       <c r="G9" t="n">
-        <v>-366.55</v>
+        <v>10487.84</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>2720</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>140.05</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>ACCEPT</t>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>242</v>
+        <v>4550</v>
       </c>
       <c r="L9" t="n">
-        <v>-39.77</v>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
+        <v>76.63</v>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
         <is>
           <t>REJECT</t>
         </is>
@@ -1011,53 +1011,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>bearing</t>
+          <t>bearing plta bengkok</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>42</v>
+        <v>185</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>zone W</t>
+          <t>Lower</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4024.38</v>
+        <v>10170.91</v>
       </c>
       <c r="F10" t="n">
-        <v>4018.41</v>
+        <v>13779.87</v>
       </c>
       <c r="G10" t="n">
-        <v>5.97</v>
+        <v>-3608.96</v>
       </c>
       <c r="H10" t="n">
-        <v>1683</v>
+        <v>105</v>
       </c>
       <c r="I10" t="n">
-        <v>72.06</v>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+        <v>0.77</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>REJECT</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>1920</v>
+        <v>195</v>
       </c>
       <c r="L10" t="n">
-        <v>-100.31</v>
+        <v>-5.13</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
         <is>
           <t>REJECT</t>
         </is>
@@ -1070,53 +1070,53 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>bearing</t>
+          <t>bearing cikalong</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>18</v>
+        <v>331.29</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>zone D</t>
+          <t>zone</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>424.12</v>
+        <v>140713.22</v>
       </c>
       <c r="F11" t="n">
-        <v>-336.28</v>
+        <v>37039.46</v>
       </c>
       <c r="G11" t="n">
-        <v>760.4</v>
+        <v>103673.76</v>
       </c>
       <c r="H11" t="n">
-        <v>204</v>
+        <v>14408.99</v>
       </c>
       <c r="I11" t="n">
-        <v>-37.76</v>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
+        <v>63.67</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
         <is>
           <t>REJECT</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>782</v>
+        <v>17095.81</v>
       </c>
       <c r="L11" t="n">
-        <v>-3620.09</v>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
+        <v>19.75</v>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
         <is>
           <t>REJECT</t>
         </is>
@@ -1129,55 +1129,55 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>bearing</t>
+          <t>bearing cikalong</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>18</v>
+        <v>315</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>zone D</t>
+          <t>zone</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>424.12</v>
+        <v>123700.21</v>
       </c>
       <c r="F12" t="n">
-        <v>-336.28</v>
+        <v>34740.04</v>
       </c>
       <c r="G12" t="n">
-        <v>760.4</v>
+        <v>88960.17</v>
       </c>
       <c r="H12" t="n">
-        <v>204</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>-37.76</v>
+        <v>0</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>REJECT</t>
+          <t>ACCEPT</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>782</v>
+        <v>468</v>
       </c>
       <c r="L12" t="n">
-        <v>-3620.09</v>
+        <v>0.53</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>REJECT</t>
+          <t>ACCEPT</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>REJECT</t>
+          <t>ACCEPT</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1188,11 +1188,11 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bearing</t>
+          <t>bearing pltu</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1200,58 +1200,58 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Zone C</t>
+          <t>zone</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>57114.15</v>
+        <v>169646</v>
       </c>
       <c r="F13" t="n">
-        <v>12929.73</v>
+        <v>40774.33</v>
       </c>
       <c r="G13" t="n">
-        <v>44184.42</v>
+        <v>128871.67</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1082.46</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>ACCEPT</t>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>231</v>
+        <v>1977.89</v>
       </c>
       <c r="L13" t="n">
-        <v>0.53</v>
+        <v>1.56</v>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>ACCEPT</t>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>ACCEPT</t>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>kahfi</t>
+          <t>admin</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bearing</t>
+          <t>bearing pltu</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1259,58 +1259,58 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Zone C</t>
+          <t>zone</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>57114.15</v>
+        <v>169646</v>
       </c>
       <c r="F14" t="n">
-        <v>30824.33</v>
+        <v>40774.33</v>
       </c>
       <c r="G14" t="n">
-        <v>26289.82</v>
+        <v>128871.67</v>
       </c>
       <c r="H14" t="n">
-        <v>252</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0.82</v>
+        <v>0</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>REJECT</t>
+          <t>ACCEPT</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>1113</v>
+        <v>3060.35</v>
       </c>
       <c r="L14" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+        <v>2.43</v>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
         <is>
           <t>REJECT</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>staff1</t>
+          <t>admin</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bearing</t>
+          <t>bearing pltu</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Zone C</t>
+          <t>zone</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1331,45 +1331,45 @@
         <v>26289.82</v>
       </c>
       <c r="H15" t="n">
-        <v>11733</v>
+        <v>947.1</v>
       </c>
       <c r="I15" t="n">
-        <v>61.46</v>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
+        <v>3.17</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>REJECT</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1809.17</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>7.39</v>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>ACCEPT</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
         <is>
           <t>REJECT</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>kahfi</t>
+          <t>admin</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bearing</t>
+          <t>bearing pltu</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Zone C</t>
+          <t>zone</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1390,681 +1390,271 @@
         <v>26289.82</v>
       </c>
       <c r="H16" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>ACCEPT</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="L16" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="M16" s="3" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="inlineStr">
+        <v>2.34</v>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>ACCEPT</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>admin</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>bearing</t>
+          <t>bearing pltu</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>19</v>
+        <v>185</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>zone D</t>
+          <t>zone</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>22234.62</v>
+        <v>10170.91</v>
       </c>
       <c r="F17" t="n">
-        <v>36242.26</v>
+        <v>13779.87</v>
       </c>
       <c r="G17" t="n">
-        <v>-14007.63</v>
+        <v>-3608.96</v>
       </c>
       <c r="H17" t="n">
-        <v>525</v>
+        <v>105</v>
       </c>
       <c r="I17" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
+        <v>0.77</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>REJECT</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>2304</v>
+        <v>390</v>
       </c>
       <c r="L17" t="n">
-        <v>-14.12</v>
+        <v>-9.75</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
         <is>
           <t>REJECT</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>admin</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>bearing</t>
+          <t>bearing pltu</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>zone a</t>
+          <t>zone</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>692.72</v>
+        <v>10170.91</v>
       </c>
       <c r="F18" t="n">
-        <v>199.34</v>
+        <v>13779.87</v>
       </c>
       <c r="G18" t="n">
-        <v>493.39</v>
+        <v>-3608.96</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>ACCEPT</t>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>6371</v>
+        <v>195</v>
       </c>
       <c r="L18" t="n">
-        <v>-108.39</v>
+        <v>-5.13</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
         <is>
           <t>REJECT</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>admin</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>bearing</t>
+          <t>bearing pltu</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>21</v>
+        <v>360</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>zone a</t>
+          <t>zone</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>692.72</v>
+        <v>57114.15</v>
       </c>
       <c r="F19" t="n">
-        <v>199.34</v>
+        <v>30824.33</v>
       </c>
       <c r="G19" t="n">
-        <v>493.39</v>
+        <v>26289.82</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>2994.3</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>10.76</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>ACCEPT</t>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>6371</v>
+        <v>5600</v>
       </c>
       <c r="L19" t="n">
-        <v>-108.39</v>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+        <v>27.07</v>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
         <is>
           <t>REJECT</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>admin</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>bearing</t>
+          <t>bearing pltu</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>21</v>
+        <v>360</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>zone a</t>
+          <t>zone</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>692.72</v>
+        <v>57114.15</v>
       </c>
       <c r="F20" t="n">
-        <v>199.34</v>
+        <v>30824.33</v>
       </c>
       <c r="G20" t="n">
-        <v>493.39</v>
+        <v>26289.82</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>2994.3</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>10.76</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>ACCEPT</t>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>341</v>
+        <v>600</v>
       </c>
       <c r="L20" t="n">
-        <v>223.78</v>
+        <v>2.34</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
         <is>
           <t>REJECT</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>10</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>bearing</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>21</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>zone a</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>692.72</v>
-      </c>
-      <c r="F21" t="n">
-        <v>199.34</v>
-      </c>
-      <c r="G21" t="n">
-        <v>493.39</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>341</v>
-      </c>
-      <c r="L21" t="n">
-        <v>223.78</v>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>9</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>bearing</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>49</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>1616.35</v>
-      </c>
-      <c r="F22" t="n">
-        <v>2398.45</v>
-      </c>
-      <c r="G22" t="n">
-        <v>-782.1</v>
-      </c>
-      <c r="J22" s="2" t="n"/>
-      <c r="M22" s="2" t="n"/>
-      <c r="N22" s="3" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>8</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>bearing</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>360</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Zona A</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>84823</v>
-      </c>
-      <c r="F23" t="n">
-        <v>33274.33</v>
-      </c>
-      <c r="G23" t="n">
-        <v>51548.67</v>
-      </c>
-      <c r="J23" s="2" t="n"/>
-      <c r="M23" s="2" t="n"/>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>7</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>bearing</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>360</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Zona A</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>84823</v>
-      </c>
-      <c r="F24" t="n">
-        <v>33274.33</v>
-      </c>
-      <c r="G24" t="n">
-        <v>51548.67</v>
-      </c>
-      <c r="J24" s="2" t="n"/>
-      <c r="M24" s="2" t="n"/>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>6</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>bearing</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>360</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Zona A</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>113097.34</v>
-      </c>
-      <c r="F25" t="n">
-        <v>35774.33</v>
-      </c>
-      <c r="G25" t="n">
-        <v>77323</v>
-      </c>
-      <c r="J25" s="2" t="n"/>
-      <c r="M25" s="2" t="n"/>
-      <c r="N25" s="3" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>5</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>bearing</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>360</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Zona A</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>113097.34</v>
-      </c>
-      <c r="F26" t="n">
-        <v>35774.33</v>
-      </c>
-      <c r="G26" t="n">
-        <v>77323</v>
-      </c>
-      <c r="J26" s="2" t="n"/>
-      <c r="M26" s="2" t="n"/>
-      <c r="N26" s="3" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>4</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>bearing</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>360</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Zona A</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>113097.34</v>
-      </c>
-      <c r="F27" t="n">
-        <v>35774.33</v>
-      </c>
-      <c r="G27" t="n">
-        <v>77323</v>
-      </c>
-      <c r="J27" s="2" t="n"/>
-      <c r="M27" s="2" t="n"/>
-      <c r="N27" s="3" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>3</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>bearing</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>360</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Zona A</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>113097.34</v>
-      </c>
-      <c r="F28" t="n">
-        <v>35774.33</v>
-      </c>
-      <c r="G28" t="n">
-        <v>77323</v>
-      </c>
-      <c r="J28" s="2" t="n"/>
-      <c r="M28" s="2" t="n"/>
-      <c r="N28" s="3" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>2</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>bearing</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>360</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Zona A</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>113097.34</v>
-      </c>
-      <c r="F29" t="n">
-        <v>35774.33</v>
-      </c>
-      <c r="G29" t="n">
-        <v>77323</v>
-      </c>
-      <c r="J29" s="2" t="n"/>
-      <c r="M29" s="2" t="n"/>
-      <c r="N29" s="3" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>1</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>bearing</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>360</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Zona A</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>113097.34</v>
-      </c>
-      <c r="F30" t="n">
-        <v>35774.33</v>
-      </c>
-      <c r="G30" t="n">
-        <v>77323</v>
-      </c>
-      <c r="J30" s="2" t="n"/>
-      <c r="M30" s="2" t="n"/>
-      <c r="N30" s="3" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>admin</t>
         </is>
       </c>
     </row>

--- a/backend/data/reports/riwayat_hasil_ndt.xlsx
+++ b/backend/data/reports/riwayat_hasil_ndt.xlsx
@@ -612,7 +612,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P50"/>
+  <dimension ref="A1:P52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.09" customWidth="1" min="1" max="1"/>
@@ -768,7 +768,7 @@
       <c r="J6" s="3" t="n"/>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>: 20 Oktober 2026</t>
+          <t>: 27 Oktober 2026</t>
         </is>
       </c>
       <c r="L6" s="3" t="n"/>
@@ -802,7 +802,7 @@
       <c r="J7" s="7" t="n"/>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>: admin</t>
+          <t>: kahfi</t>
         </is>
       </c>
       <c r="L7" s="7" t="n"/>
@@ -836,7 +836,7 @@
       <c r="J8" s="7" t="n"/>
       <c r="K8" s="7" t="inlineStr">
         <is>
-          <t>: 30 data</t>
+          <t>: 32 data</t>
         </is>
       </c>
       <c r="L8" s="7" t="n"/>
@@ -870,7 +870,7 @@
       <c r="J9" s="12" t="n"/>
       <c r="K9" s="12" t="inlineStr">
         <is>
-          <t>: ACCEPT: 10  |  REJECT: 20</t>
+          <t>: ACC: 11  |  REJECT: 21</t>
         </is>
       </c>
       <c r="L9" s="12" t="n"/>
@@ -952,7 +952,7 @@
       </c>
       <c r="O11" s="17" t="inlineStr">
         <is>
-          <t>Inspector</t>
+          <t>Inspektur</t>
         </is>
       </c>
       <c r="P11" s="17" t="inlineStr">
@@ -963,7 +963,7 @@
     </row>
     <row r="12">
       <c r="A12" s="18" t="n">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="B12" s="19" t="inlineStr">
         <is>
@@ -995,23 +995,23 @@
       </c>
       <c r="J12" s="20" t="inlineStr">
         <is>
-          <t>ACCEPT</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="K12" s="19" t="n">
-        <v>312</v>
+        <v>1</v>
       </c>
       <c r="L12" s="19" t="n">
-        <v>42.05</v>
-      </c>
-      <c r="M12" s="21" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="N12" s="21" t="inlineStr">
-        <is>
-          <t>REJECT</t>
+        <v>0.09</v>
+      </c>
+      <c r="M12" s="20" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="N12" s="20" t="inlineStr">
+        <is>
+          <t>ACC</t>
         </is>
       </c>
       <c r="O12" s="19" t="inlineStr">
@@ -1027,7 +1027,7 @@
     </row>
     <row r="13">
       <c r="A13" s="18" t="n">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
@@ -1059,14 +1059,14 @@
       </c>
       <c r="J13" s="20" t="inlineStr">
         <is>
-          <t>ACCEPT</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="K13" s="19" t="n">
-        <v>299</v>
+        <v>80</v>
       </c>
       <c r="L13" s="19" t="n">
-        <v>39.61</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="M13" s="21" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
     </row>
     <row r="14">
       <c r="A14" s="18" t="n">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="B14" s="19" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="C14" s="19" t="n">
-        <v>150</v>
+        <v>38</v>
       </c>
       <c r="D14" s="19" t="inlineStr">
         <is>
@@ -1107,13 +1107,13 @@
         </is>
       </c>
       <c r="E14" s="19" t="n">
-        <v>23797.56</v>
+        <v>1432.57</v>
       </c>
       <c r="F14" s="19" t="n">
-        <v>6391.67</v>
+        <v>378.67</v>
       </c>
       <c r="G14" s="19" t="n">
-        <v>17405.89</v>
+        <v>1053.89</v>
       </c>
       <c r="H14" s="19" t="n">
         <v>0</v>
@@ -1123,39 +1123,39 @@
       </c>
       <c r="J14" s="20" t="inlineStr">
         <is>
-          <t>ACCEPT</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="K14" s="19" t="n">
-        <v>100</v>
+        <v>312</v>
       </c>
       <c r="L14" s="19" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="M14" s="20" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
-        </is>
-      </c>
-      <c r="N14" s="20" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+        <v>42.05</v>
+      </c>
+      <c r="M14" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="N14" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="O14" s="19" t="inlineStr">
         <is>
-          <t>kahfi</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="P14" s="19" t="inlineStr">
         <is>
-          <t>PLTA Maninjau</t>
+          <t>PLTU</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="18" t="n">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="B15" s="19" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="C15" s="19" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="D15" s="19" t="inlineStr">
         <is>
@@ -1171,30 +1171,30 @@
         </is>
       </c>
       <c r="E15" s="19" t="n">
-        <v>15150</v>
+        <v>1432.57</v>
       </c>
       <c r="F15" s="19" t="n">
-        <v>4662.16</v>
+        <v>378.67</v>
       </c>
       <c r="G15" s="19" t="n">
-        <v>10487.84</v>
+        <v>1053.89</v>
       </c>
       <c r="H15" s="19" t="n">
-        <v>2720</v>
+        <v>0</v>
       </c>
       <c r="I15" s="19" t="n">
-        <v>140.05</v>
-      </c>
-      <c r="J15" s="21" t="inlineStr">
-        <is>
-          <t>REJECT</t>
+        <v>0</v>
+      </c>
+      <c r="J15" s="20" t="inlineStr">
+        <is>
+          <t>ACC</t>
         </is>
       </c>
       <c r="K15" s="19" t="n">
-        <v>4550</v>
+        <v>299</v>
       </c>
       <c r="L15" s="19" t="n">
-        <v>76.63</v>
+        <v>39.61</v>
       </c>
       <c r="M15" s="21" t="inlineStr">
         <is>
@@ -1208,18 +1208,18 @@
       </c>
       <c r="O15" s="19" t="inlineStr">
         <is>
-          <t>kahfi</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="P15" s="19" t="inlineStr">
         <is>
-          <t>PLTA Maninjau</t>
+          <t>PLTU</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="18" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="B16" s="19" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         </is>
       </c>
       <c r="C16" s="19" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="D16" s="19" t="inlineStr">
         <is>
@@ -1235,39 +1235,39 @@
         </is>
       </c>
       <c r="E16" s="19" t="n">
-        <v>15150</v>
+        <v>23797.56</v>
       </c>
       <c r="F16" s="19" t="n">
-        <v>4662.16</v>
+        <v>6391.67</v>
       </c>
       <c r="G16" s="19" t="n">
-        <v>10487.84</v>
+        <v>17405.89</v>
       </c>
       <c r="H16" s="19" t="n">
-        <v>2720</v>
+        <v>0</v>
       </c>
       <c r="I16" s="19" t="n">
-        <v>140.05</v>
-      </c>
-      <c r="J16" s="21" t="inlineStr">
-        <is>
-          <t>REJECT</t>
+        <v>0</v>
+      </c>
+      <c r="J16" s="20" t="inlineStr">
+        <is>
+          <t>ACC</t>
         </is>
       </c>
       <c r="K16" s="19" t="n">
-        <v>4550</v>
+        <v>100</v>
       </c>
       <c r="L16" s="19" t="n">
-        <v>76.63</v>
-      </c>
-      <c r="M16" s="21" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="N16" s="21" t="inlineStr">
-        <is>
-          <t>REJECT</t>
+        <v>0.58</v>
+      </c>
+      <c r="M16" s="20" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="N16" s="20" t="inlineStr">
+        <is>
+          <t>ACC</t>
         </is>
       </c>
       <c r="O16" s="19" t="inlineStr">
@@ -1283,55 +1283,55 @@
     </row>
     <row r="17">
       <c r="A17" s="18" t="n">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="B17" s="19" t="inlineStr">
         <is>
-          <t>Beearing</t>
+          <t>Bearing</t>
         </is>
       </c>
       <c r="C17" s="19" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="D17" s="19" t="inlineStr">
         <is>
-          <t>Lower</t>
+          <t>Upper</t>
         </is>
       </c>
       <c r="E17" s="19" t="n">
-        <v>23797.56</v>
+        <v>15150</v>
       </c>
       <c r="F17" s="19" t="n">
-        <v>6391.67</v>
+        <v>4662.16</v>
       </c>
       <c r="G17" s="19" t="n">
-        <v>17405.89</v>
+        <v>10487.84</v>
       </c>
       <c r="H17" s="19" t="n">
-        <v>0</v>
+        <v>2720</v>
       </c>
       <c r="I17" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="20" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+        <v>140.05</v>
+      </c>
+      <c r="J17" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="K17" s="19" t="n">
-        <v>100</v>
+        <v>4550</v>
       </c>
       <c r="L17" s="19" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="M17" s="20" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
-        </is>
-      </c>
-      <c r="N17" s="20" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+        <v>76.63</v>
+      </c>
+      <c r="M17" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="N17" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="O17" s="19" t="inlineStr">
@@ -1341,17 +1341,17 @@
       </c>
       <c r="P17" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PLTA Maninjau</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="18" t="n">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="B18" s="19" t="inlineStr">
         <is>
-          <t>Beearing</t>
+          <t>Bearing</t>
         </is>
       </c>
       <c r="C18" s="19" t="n">
@@ -1405,21 +1405,21 @@
       </c>
       <c r="P18" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PLTA Maninjau</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="18" t="n">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="B19" s="19" t="inlineStr">
         <is>
-          <t>Bearing</t>
+          <t>Beearing</t>
         </is>
       </c>
       <c r="C19" s="19" t="n">
-        <v>17</v>
+        <v>150</v>
       </c>
       <c r="D19" s="19" t="inlineStr">
         <is>
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="E19" s="19" t="n">
-        <v>721</v>
+        <v>23797.56</v>
       </c>
       <c r="F19" s="19" t="n">
-        <v>260.84</v>
+        <v>6391.67</v>
       </c>
       <c r="G19" s="19" t="n">
-        <v>460.16</v>
+        <v>17405.89</v>
       </c>
       <c r="H19" s="19" t="n">
         <v>0</v>
@@ -1443,28 +1443,28 @@
       </c>
       <c r="J19" s="20" t="inlineStr">
         <is>
-          <t>ACCEPT</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="K19" s="19" t="n">
-        <v>1948</v>
+        <v>100</v>
       </c>
       <c r="L19" s="19" t="n">
-        <v>-130.93</v>
-      </c>
-      <c r="M19" s="21" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="N19" s="21" t="inlineStr">
-        <is>
-          <t>REJECT</t>
+        <v>0.58</v>
+      </c>
+      <c r="M19" s="20" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="N19" s="20" t="inlineStr">
+        <is>
+          <t>ACC</t>
         </is>
       </c>
       <c r="O19" s="19" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>kahfi</t>
         </is>
       </c>
       <c r="P19" s="19" t="inlineStr">
@@ -1475,15 +1475,15 @@
     </row>
     <row r="20">
       <c r="A20" s="18" t="n">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="B20" s="19" t="inlineStr">
         <is>
-          <t>Bearing</t>
+          <t>Beearing</t>
         </is>
       </c>
       <c r="C20" s="19" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D20" s="19" t="inlineStr">
         <is>
@@ -1491,30 +1491,30 @@
         </is>
       </c>
       <c r="E20" s="19" t="n">
-        <v>10822.79</v>
+        <v>15150</v>
       </c>
       <c r="F20" s="19" t="n">
-        <v>3962.32</v>
+        <v>4662.16</v>
       </c>
       <c r="G20" s="19" t="n">
-        <v>6860.47</v>
+        <v>10487.84</v>
       </c>
       <c r="H20" s="19" t="n">
-        <v>0</v>
+        <v>2720</v>
       </c>
       <c r="I20" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="20" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+        <v>140.05</v>
+      </c>
+      <c r="J20" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="K20" s="19" t="n">
-        <v>1560</v>
+        <v>4550</v>
       </c>
       <c r="L20" s="19" t="n">
-        <v>29.43</v>
+        <v>76.63</v>
       </c>
       <c r="M20" s="21" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="O20" s="19" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>kahfi</t>
         </is>
       </c>
       <c r="P20" s="19" t="inlineStr">
@@ -1539,29 +1539,29 @@
     </row>
     <row r="21">
       <c r="A21" s="18" t="n">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="B21" s="19" t="inlineStr">
         <is>
-          <t>bearing</t>
+          <t>Bearing</t>
         </is>
       </c>
       <c r="C21" s="19" t="n">
-        <v>795</v>
+        <v>17</v>
       </c>
       <c r="D21" s="19" t="inlineStr">
         <is>
-          <t>Upper</t>
+          <t>Lower</t>
         </is>
       </c>
       <c r="E21" s="19" t="n">
-        <v>427083.81</v>
+        <v>721</v>
       </c>
       <c r="F21" s="19" t="n">
-        <v>104131</v>
+        <v>260.84</v>
       </c>
       <c r="G21" s="19" t="n">
-        <v>322952.81</v>
+        <v>460.16</v>
       </c>
       <c r="H21" s="19" t="n">
         <v>0</v>
@@ -1571,14 +1571,14 @@
       </c>
       <c r="J21" s="20" t="inlineStr">
         <is>
-          <t>ACCEPT</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="K21" s="19" t="n">
-        <v>8612</v>
+        <v>1948</v>
       </c>
       <c r="L21" s="19" t="n">
-        <v>2.74</v>
+        <v>-130.93</v>
       </c>
       <c r="M21" s="21" t="inlineStr">
         <is>
@@ -1603,15 +1603,15 @@
     </row>
     <row r="22">
       <c r="A22" s="18" t="n">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="B22" s="19" t="inlineStr">
         <is>
-          <t>bearing</t>
+          <t>Bearing</t>
         </is>
       </c>
       <c r="C22" s="19" t="n">
-        <v>123</v>
+        <v>65</v>
       </c>
       <c r="D22" s="19" t="inlineStr">
         <is>
@@ -1619,13 +1619,13 @@
         </is>
       </c>
       <c r="E22" s="19" t="n">
-        <v>5989.45</v>
+        <v>10822.79</v>
       </c>
       <c r="F22" s="19" t="n">
-        <v>1351.65</v>
+        <v>3962.32</v>
       </c>
       <c r="G22" s="19" t="n">
-        <v>4637.8</v>
+        <v>6860.47</v>
       </c>
       <c r="H22" s="19" t="n">
         <v>0</v>
@@ -1635,14 +1635,14 @@
       </c>
       <c r="J22" s="20" t="inlineStr">
         <is>
-          <t>ACCEPT</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="K22" s="19" t="n">
-        <v>1253</v>
+        <v>1560</v>
       </c>
       <c r="L22" s="19" t="n">
-        <v>37.02</v>
+        <v>29.43</v>
       </c>
       <c r="M22" s="21" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
     </row>
     <row r="23">
       <c r="A23" s="18" t="n">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="B23" s="19" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="C23" s="19" t="n">
-        <v>123</v>
+        <v>795</v>
       </c>
       <c r="D23" s="19" t="inlineStr">
         <is>
@@ -1683,13 +1683,13 @@
         </is>
       </c>
       <c r="E23" s="19" t="n">
-        <v>5989.45</v>
+        <v>427083.81</v>
       </c>
       <c r="F23" s="19" t="n">
-        <v>1351.65</v>
+        <v>104131</v>
       </c>
       <c r="G23" s="19" t="n">
-        <v>4637.8</v>
+        <v>322952.81</v>
       </c>
       <c r="H23" s="19" t="n">
         <v>0</v>
@@ -1699,14 +1699,14 @@
       </c>
       <c r="J23" s="20" t="inlineStr">
         <is>
-          <t>ACCEPT</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="K23" s="19" t="n">
-        <v>1253</v>
+        <v>8612</v>
       </c>
       <c r="L23" s="19" t="n">
-        <v>37.02</v>
+        <v>2.74</v>
       </c>
       <c r="M23" s="21" t="inlineStr">
         <is>
@@ -1731,29 +1731,29 @@
     </row>
     <row r="24">
       <c r="A24" s="18" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="B24" s="19" t="inlineStr">
         <is>
-          <t>Bearing</t>
+          <t>bearing</t>
         </is>
       </c>
       <c r="C24" s="19" t="n">
-        <v>234</v>
+        <v>123</v>
       </c>
       <c r="D24" s="19" t="inlineStr">
         <is>
-          <t>Lower</t>
+          <t>Upper</t>
         </is>
       </c>
       <c r="E24" s="19" t="n">
-        <v>158788.66</v>
+        <v>5989.45</v>
       </c>
       <c r="F24" s="19" t="n">
-        <v>61617.57</v>
+        <v>1351.65</v>
       </c>
       <c r="G24" s="19" t="n">
-        <v>97171.09</v>
+        <v>4637.8</v>
       </c>
       <c r="H24" s="19" t="n">
         <v>0</v>
@@ -1763,14 +1763,14 @@
       </c>
       <c r="J24" s="20" t="inlineStr">
         <is>
-          <t>ACCEPT</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="K24" s="19" t="n">
-        <v>10620</v>
+        <v>1253</v>
       </c>
       <c r="L24" s="19" t="n">
-        <v>12.27</v>
+        <v>37.02</v>
       </c>
       <c r="M24" s="21" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
     </row>
     <row r="25">
       <c r="A25" s="18" t="n">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="B25" s="19" t="inlineStr">
         <is>
@@ -1803,38 +1803,42 @@
         </is>
       </c>
       <c r="C25" s="19" t="n">
-        <v>65</v>
-      </c>
-      <c r="D25" s="19" t="inlineStr"/>
+        <v>123</v>
+      </c>
+      <c r="D25" s="19" t="inlineStr">
+        <is>
+          <t>Upper</t>
+        </is>
+      </c>
       <c r="E25" s="19" t="n">
-        <v>5105.09</v>
+        <v>5989.45</v>
       </c>
       <c r="F25" s="19" t="n">
-        <v>5748.34</v>
+        <v>1351.65</v>
       </c>
       <c r="G25" s="19" t="n">
-        <v>-643.26</v>
+        <v>4637.8</v>
       </c>
       <c r="H25" s="19" t="n">
-        <v>176</v>
+        <v>0</v>
       </c>
       <c r="I25" s="19" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="J25" s="21" t="inlineStr">
-        <is>
-          <t>REJECT</t>
+        <v>0</v>
+      </c>
+      <c r="J25" s="20" t="inlineStr">
+        <is>
+          <t>ACC</t>
         </is>
       </c>
       <c r="K25" s="19" t="n">
-        <v>0</v>
+        <v>1253</v>
       </c>
       <c r="L25" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" s="20" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+        <v>37.02</v>
+      </c>
+      <c r="M25" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="N25" s="21" t="inlineStr">
@@ -1855,7 +1859,7 @@
     </row>
     <row r="26">
       <c r="A26" s="18" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="B26" s="19" t="inlineStr">
         <is>
@@ -1863,38 +1867,38 @@
         </is>
       </c>
       <c r="C26" s="19" t="n">
-        <v>0</v>
+        <v>234</v>
       </c>
       <c r="D26" s="19" t="inlineStr">
         <is>
-          <t>Upper</t>
+          <t>Lower</t>
         </is>
       </c>
       <c r="E26" s="19" t="n">
-        <v>15150</v>
+        <v>158788.66</v>
       </c>
       <c r="F26" s="19" t="n">
-        <v>4620</v>
+        <v>61617.57</v>
       </c>
       <c r="G26" s="19" t="n">
-        <v>10530</v>
+        <v>97171.09</v>
       </c>
       <c r="H26" s="19" t="n">
-        <v>2720</v>
+        <v>0</v>
       </c>
       <c r="I26" s="19" t="n">
-        <v>143.16</v>
-      </c>
-      <c r="J26" s="21" t="inlineStr">
-        <is>
-          <t>REJECT</t>
+        <v>0</v>
+      </c>
+      <c r="J26" s="20" t="inlineStr">
+        <is>
+          <t>ACC</t>
         </is>
       </c>
       <c r="K26" s="19" t="n">
-        <v>4550</v>
+        <v>10620</v>
       </c>
       <c r="L26" s="19" t="n">
-        <v>76.09</v>
+        <v>12.27</v>
       </c>
       <c r="M26" s="21" t="inlineStr">
         <is>
@@ -1908,7 +1912,7 @@
       </c>
       <c r="O26" s="19" t="inlineStr">
         <is>
-          <t>kahfi</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="P26" s="19" t="inlineStr">
@@ -1919,35 +1923,31 @@
     </row>
     <row r="27">
       <c r="A27" s="18" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="B27" s="19" t="inlineStr">
         <is>
-          <t>Bearing</t>
+          <t>bearing</t>
         </is>
       </c>
       <c r="C27" s="19" t="n">
-        <v>95.40000000000001</v>
-      </c>
-      <c r="D27" s="19" t="inlineStr">
-        <is>
-          <t>Upper</t>
-        </is>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="D27" s="19" t="inlineStr"/>
       <c r="E27" s="19" t="n">
-        <v>15135.25</v>
+        <v>5105.09</v>
       </c>
       <c r="F27" s="19" t="n">
-        <v>9868.5</v>
+        <v>5748.34</v>
       </c>
       <c r="G27" s="19" t="n">
-        <v>5266.75</v>
+        <v>-643.26</v>
       </c>
       <c r="H27" s="19" t="n">
-        <v>2720</v>
+        <v>176</v>
       </c>
       <c r="I27" s="19" t="n">
-        <v>38.05</v>
+        <v>3.16</v>
       </c>
       <c r="J27" s="21" t="inlineStr">
         <is>
@@ -1955,14 +1955,14 @@
         </is>
       </c>
       <c r="K27" s="19" t="n">
-        <v>4550</v>
+        <v>0</v>
       </c>
       <c r="L27" s="19" t="n">
-        <v>634.8099999999999</v>
-      </c>
-      <c r="M27" s="21" t="inlineStr">
-        <is>
-          <t>REJECT</t>
+        <v>0</v>
+      </c>
+      <c r="M27" s="20" t="inlineStr">
+        <is>
+          <t>ACC</t>
         </is>
       </c>
       <c r="N27" s="21" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="O27" s="19" t="inlineStr">
         <is>
-          <t>kahfi</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="P27" s="19" t="inlineStr">
@@ -1983,7 +1983,7 @@
     </row>
     <row r="28">
       <c r="A28" s="18" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="B28" s="19" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         </is>
       </c>
       <c r="C28" s="19" t="n">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="D28" s="19" t="inlineStr">
         <is>
@@ -1999,19 +1999,19 @@
         </is>
       </c>
       <c r="E28" s="19" t="n">
-        <v>84823</v>
+        <v>15150</v>
       </c>
       <c r="F28" s="19" t="n">
-        <v>33274.33</v>
+        <v>4620</v>
       </c>
       <c r="G28" s="19" t="n">
-        <v>51548.67</v>
+        <v>10530</v>
       </c>
       <c r="H28" s="19" t="n">
         <v>2720</v>
       </c>
       <c r="I28" s="19" t="n">
-        <v>8.9</v>
+        <v>143.16</v>
       </c>
       <c r="J28" s="21" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>4550</v>
       </c>
       <c r="L28" s="19" t="n">
-        <v>9.68</v>
+        <v>76.09</v>
       </c>
       <c r="M28" s="21" t="inlineStr">
         <is>
@@ -2047,15 +2047,15 @@
     </row>
     <row r="29">
       <c r="A29" s="18" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="B29" s="19" t="inlineStr">
         <is>
-          <t>bearing</t>
+          <t>Bearing</t>
         </is>
       </c>
       <c r="C29" s="19" t="n">
-        <v>65</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="D29" s="19" t="inlineStr">
         <is>
@@ -2063,19 +2063,19 @@
         </is>
       </c>
       <c r="E29" s="19" t="n">
-        <v>5105.09</v>
+        <v>15135.25</v>
       </c>
       <c r="F29" s="19" t="n">
-        <v>5105.09</v>
+        <v>9868.5</v>
       </c>
       <c r="G29" s="19" t="n">
-        <v>0</v>
+        <v>5266.75</v>
       </c>
       <c r="H29" s="19" t="n">
-        <v>14760</v>
+        <v>2720</v>
       </c>
       <c r="I29" s="19" t="n">
-        <v>-152.88</v>
+        <v>38.05</v>
       </c>
       <c r="J29" s="21" t="inlineStr">
         <is>
@@ -2083,14 +2083,14 @@
         </is>
       </c>
       <c r="K29" s="19" t="n">
-        <v>0</v>
+        <v>4550</v>
       </c>
       <c r="L29" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" s="20" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+        <v>634.8099999999999</v>
+      </c>
+      <c r="M29" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="N29" s="21" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="O29" s="19" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>kahfi</t>
         </is>
       </c>
       <c r="P29" s="19" t="inlineStr">
@@ -2111,7 +2111,7 @@
     </row>
     <row r="30">
       <c r="A30" s="18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B30" s="19" t="inlineStr">
         <is>
@@ -2123,48 +2123,48 @@
       </c>
       <c r="D30" s="19" t="inlineStr">
         <is>
-          <t>Zone C</t>
+          <t>Upper</t>
         </is>
       </c>
       <c r="E30" s="19" t="n">
-        <v>57114.15</v>
+        <v>84823</v>
       </c>
       <c r="F30" s="19" t="n">
-        <v>30824.33</v>
+        <v>33274.33</v>
       </c>
       <c r="G30" s="19" t="n">
-        <v>26289.82</v>
+        <v>51548.67</v>
       </c>
       <c r="H30" s="19" t="n">
-        <v>39</v>
+        <v>2720</v>
       </c>
       <c r="I30" s="19" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="J30" s="20" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+        <v>8.9</v>
+      </c>
+      <c r="J30" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="K30" s="19" t="n">
-        <v>300</v>
+        <v>4550</v>
       </c>
       <c r="L30" s="19" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="M30" s="20" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
-        </is>
-      </c>
-      <c r="N30" s="20" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+        <v>9.68</v>
+      </c>
+      <c r="M30" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="N30" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="O30" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>kahfi</t>
         </is>
       </c>
       <c r="P30" s="19" t="inlineStr">
@@ -2175,7 +2175,7 @@
     </row>
     <row r="31">
       <c r="A31" s="18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B31" s="19" t="inlineStr">
         <is>
@@ -2183,42 +2183,42 @@
         </is>
       </c>
       <c r="C31" s="19" t="n">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="D31" s="19" t="inlineStr">
         <is>
-          <t>zone a</t>
+          <t>Upper</t>
         </is>
       </c>
       <c r="E31" s="19" t="n">
-        <v>692.72</v>
+        <v>5105.09</v>
       </c>
       <c r="F31" s="19" t="n">
-        <v>199.34</v>
+        <v>5105.09</v>
       </c>
       <c r="G31" s="19" t="n">
-        <v>493.39</v>
+        <v>0</v>
       </c>
       <c r="H31" s="19" t="n">
-        <v>0</v>
+        <v>14760</v>
       </c>
       <c r="I31" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="20" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+        <v>-152.88</v>
+      </c>
+      <c r="J31" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="K31" s="19" t="n">
-        <v>6371</v>
+        <v>0</v>
       </c>
       <c r="L31" s="19" t="n">
-        <v>-108.39</v>
-      </c>
-      <c r="M31" s="21" t="inlineStr">
-        <is>
-          <t>REJECT</t>
+        <v>0</v>
+      </c>
+      <c r="M31" s="20" t="inlineStr">
+        <is>
+          <t>ACC</t>
         </is>
       </c>
       <c r="N31" s="21" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="O31" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="P31" s="19" t="inlineStr">
@@ -2239,55 +2239,55 @@
     </row>
     <row r="32">
       <c r="A32" s="18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B32" s="19" t="inlineStr">
         <is>
-          <t>bearing</t>
+          <t>Bearing</t>
         </is>
       </c>
       <c r="C32" s="19" t="n">
-        <v>21</v>
+        <v>360</v>
       </c>
       <c r="D32" s="19" t="inlineStr">
         <is>
-          <t>zone a</t>
+          <t>Zone C</t>
         </is>
       </c>
       <c r="E32" s="19" t="n">
-        <v>692.72</v>
+        <v>57114.15</v>
       </c>
       <c r="F32" s="19" t="n">
-        <v>199.34</v>
+        <v>30824.33</v>
       </c>
       <c r="G32" s="19" t="n">
-        <v>493.39</v>
+        <v>26289.82</v>
       </c>
       <c r="H32" s="19" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="I32" s="19" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="J32" s="20" t="inlineStr">
         <is>
-          <t>ACCEPT</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="K32" s="19" t="n">
-        <v>341</v>
+        <v>300</v>
       </c>
       <c r="L32" s="19" t="n">
-        <v>223.78</v>
-      </c>
-      <c r="M32" s="21" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="N32" s="21" t="inlineStr">
-        <is>
-          <t>REJECT</t>
+        <v>1.15</v>
+      </c>
+      <c r="M32" s="20" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="N32" s="20" t="inlineStr">
+        <is>
+          <t>ACC</t>
         </is>
       </c>
       <c r="O32" s="19" t="inlineStr">
@@ -2303,7 +2303,7 @@
     </row>
     <row r="33">
       <c r="A33" s="18" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B33" s="19" t="inlineStr">
         <is>
@@ -2311,31 +2311,47 @@
         </is>
       </c>
       <c r="C33" s="19" t="n">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="D33" s="19" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>zone a</t>
         </is>
       </c>
       <c r="E33" s="19" t="n">
-        <v>1616.35</v>
+        <v>692.72</v>
       </c>
       <c r="F33" s="19" t="n">
-        <v>2398.45</v>
+        <v>199.34</v>
       </c>
       <c r="G33" s="19" t="n">
-        <v>-782.1</v>
-      </c>
-      <c r="H33" s="19" t="n"/>
-      <c r="I33" s="19" t="n"/>
-      <c r="J33" s="19" t="n"/>
-      <c r="K33" s="19" t="n"/>
-      <c r="L33" s="19" t="n"/>
-      <c r="M33" s="19" t="n"/>
-      <c r="N33" s="20" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+        <v>493.39</v>
+      </c>
+      <c r="H33" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="20" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="K33" s="19" t="n">
+        <v>6371</v>
+      </c>
+      <c r="L33" s="19" t="n">
+        <v>-108.39</v>
+      </c>
+      <c r="M33" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="N33" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="O33" s="19" t="inlineStr">
@@ -2351,7 +2367,7 @@
     </row>
     <row r="34">
       <c r="A34" s="18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B34" s="19" t="inlineStr">
         <is>
@@ -2359,28 +2375,44 @@
         </is>
       </c>
       <c r="C34" s="19" t="n">
-        <v>360</v>
+        <v>21</v>
       </c>
       <c r="D34" s="19" t="inlineStr">
         <is>
-          <t>Zona A</t>
+          <t>zone a</t>
         </is>
       </c>
       <c r="E34" s="19" t="n">
-        <v>84823</v>
+        <v>692.72</v>
       </c>
       <c r="F34" s="19" t="n">
-        <v>33274.33</v>
+        <v>199.34</v>
       </c>
       <c r="G34" s="19" t="n">
-        <v>51548.67</v>
-      </c>
-      <c r="H34" s="19" t="n"/>
-      <c r="I34" s="19" t="n"/>
-      <c r="J34" s="19" t="n"/>
-      <c r="K34" s="19" t="n"/>
-      <c r="L34" s="19" t="n"/>
-      <c r="M34" s="19" t="n"/>
+        <v>493.39</v>
+      </c>
+      <c r="H34" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="20" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="K34" s="19" t="n">
+        <v>341</v>
+      </c>
+      <c r="L34" s="19" t="n">
+        <v>223.78</v>
+      </c>
+      <c r="M34" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
       <c r="N34" s="21" t="inlineStr">
         <is>
           <t>REJECT</t>
@@ -2399,7 +2431,7 @@
     </row>
     <row r="35">
       <c r="A35" s="18" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B35" s="19" t="inlineStr">
         <is>
@@ -2407,21 +2439,21 @@
         </is>
       </c>
       <c r="C35" s="19" t="n">
-        <v>360</v>
+        <v>49</v>
       </c>
       <c r="D35" s="19" t="inlineStr">
         <is>
-          <t>Zona A</t>
+          <t>b</t>
         </is>
       </c>
       <c r="E35" s="19" t="n">
-        <v>84823</v>
+        <v>1616.35</v>
       </c>
       <c r="F35" s="19" t="n">
-        <v>33274.33</v>
+        <v>2398.45</v>
       </c>
       <c r="G35" s="19" t="n">
-        <v>51548.67</v>
+        <v>-782.1</v>
       </c>
       <c r="H35" s="19" t="n"/>
       <c r="I35" s="19" t="n"/>
@@ -2429,9 +2461,9 @@
       <c r="K35" s="19" t="n"/>
       <c r="L35" s="19" t="n"/>
       <c r="M35" s="19" t="n"/>
-      <c r="N35" s="21" t="inlineStr">
-        <is>
-          <t>REJECT</t>
+      <c r="N35" s="20" t="inlineStr">
+        <is>
+          <t>ACC</t>
         </is>
       </c>
       <c r="O35" s="19" t="inlineStr">
@@ -2447,7 +2479,7 @@
     </row>
     <row r="36">
       <c r="A36" s="18" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B36" s="19" t="inlineStr">
         <is>
@@ -2463,13 +2495,13 @@
         </is>
       </c>
       <c r="E36" s="19" t="n">
-        <v>113097.34</v>
+        <v>84823</v>
       </c>
       <c r="F36" s="19" t="n">
-        <v>35774.33</v>
+        <v>33274.33</v>
       </c>
       <c r="G36" s="19" t="n">
-        <v>77323</v>
+        <v>51548.67</v>
       </c>
       <c r="H36" s="19" t="n"/>
       <c r="I36" s="19" t="n"/>
@@ -2477,9 +2509,9 @@
       <c r="K36" s="19" t="n"/>
       <c r="L36" s="19" t="n"/>
       <c r="M36" s="19" t="n"/>
-      <c r="N36" s="20" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+      <c r="N36" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="O36" s="19" t="inlineStr">
@@ -2495,7 +2527,7 @@
     </row>
     <row r="37">
       <c r="A37" s="18" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B37" s="19" t="inlineStr">
         <is>
@@ -2511,13 +2543,13 @@
         </is>
       </c>
       <c r="E37" s="19" t="n">
-        <v>113097.34</v>
+        <v>84823</v>
       </c>
       <c r="F37" s="19" t="n">
-        <v>35774.33</v>
+        <v>33274.33</v>
       </c>
       <c r="G37" s="19" t="n">
-        <v>77323</v>
+        <v>51548.67</v>
       </c>
       <c r="H37" s="19" t="n"/>
       <c r="I37" s="19" t="n"/>
@@ -2525,9 +2557,9 @@
       <c r="K37" s="19" t="n"/>
       <c r="L37" s="19" t="n"/>
       <c r="M37" s="19" t="n"/>
-      <c r="N37" s="20" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+      <c r="N37" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="O37" s="19" t="inlineStr">
@@ -2543,7 +2575,7 @@
     </row>
     <row r="38">
       <c r="A38" s="18" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B38" s="19" t="inlineStr">
         <is>
@@ -2575,7 +2607,7 @@
       <c r="M38" s="19" t="n"/>
       <c r="N38" s="20" t="inlineStr">
         <is>
-          <t>ACCEPT</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="O38" s="19" t="inlineStr">
@@ -2591,7 +2623,7 @@
     </row>
     <row r="39">
       <c r="A39" s="18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B39" s="19" t="inlineStr">
         <is>
@@ -2623,7 +2655,7 @@
       <c r="M39" s="19" t="n"/>
       <c r="N39" s="20" t="inlineStr">
         <is>
-          <t>ACCEPT</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="O39" s="19" t="inlineStr">
@@ -2639,7 +2671,7 @@
     </row>
     <row r="40">
       <c r="A40" s="18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B40" s="19" t="inlineStr">
         <is>
@@ -2671,7 +2703,7 @@
       <c r="M40" s="19" t="n"/>
       <c r="N40" s="20" t="inlineStr">
         <is>
-          <t>ACCEPT</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="O40" s="19" t="inlineStr">
@@ -2687,7 +2719,7 @@
     </row>
     <row r="41">
       <c r="A41" s="18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B41" s="19" t="inlineStr">
         <is>
@@ -2719,7 +2751,7 @@
       <c r="M41" s="19" t="n"/>
       <c r="N41" s="20" t="inlineStr">
         <is>
-          <t>ACCEPT</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="O41" s="19" t="inlineStr">
@@ -2733,165 +2765,273 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="B42" s="19" t="inlineStr">
+        <is>
+          <t>bearing</t>
+        </is>
+      </c>
+      <c r="C42" s="19" t="n">
+        <v>360</v>
+      </c>
+      <c r="D42" s="19" t="inlineStr">
+        <is>
+          <t>Zona A</t>
+        </is>
+      </c>
+      <c r="E42" s="19" t="n">
+        <v>113097.34</v>
+      </c>
+      <c r="F42" s="19" t="n">
+        <v>35774.33</v>
+      </c>
+      <c r="G42" s="19" t="n">
+        <v>77323</v>
+      </c>
+      <c r="H42" s="19" t="n"/>
+      <c r="I42" s="19" t="n"/>
+      <c r="J42" s="19" t="n"/>
+      <c r="K42" s="19" t="n"/>
+      <c r="L42" s="19" t="n"/>
+      <c r="M42" s="19" t="n"/>
+      <c r="N42" s="20" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="O42" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P42" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
     <row r="43">
-      <c r="D43" s="22" t="inlineStr">
+      <c r="A43" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="B43" s="19" t="inlineStr">
+        <is>
+          <t>bearing</t>
+        </is>
+      </c>
+      <c r="C43" s="19" t="n">
+        <v>360</v>
+      </c>
+      <c r="D43" s="19" t="inlineStr">
+        <is>
+          <t>Zona A</t>
+        </is>
+      </c>
+      <c r="E43" s="19" t="n">
+        <v>113097.34</v>
+      </c>
+      <c r="F43" s="19" t="n">
+        <v>35774.33</v>
+      </c>
+      <c r="G43" s="19" t="n">
+        <v>77323</v>
+      </c>
+      <c r="H43" s="19" t="n"/>
+      <c r="I43" s="19" t="n"/>
+      <c r="J43" s="19" t="n"/>
+      <c r="K43" s="19" t="n"/>
+      <c r="L43" s="19" t="n"/>
+      <c r="M43" s="19" t="n"/>
+      <c r="N43" s="20" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="O43" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P43" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="22" t="inlineStr">
+        <is>
+          <t>PREPARED BY</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n"/>
+      <c r="C45" s="3" t="n"/>
+      <c r="D45" s="4" t="n"/>
+      <c r="G45" s="22" t="inlineStr">
         <is>
           <t>CHECKED BY</t>
         </is>
       </c>
-      <c r="E43" s="3" t="n"/>
-      <c r="F43" s="4" t="n"/>
-      <c r="H43" s="22" t="inlineStr">
-        <is>
-          <t>CHECKED BY</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="n"/>
-      <c r="J43" s="4" t="n"/>
-      <c r="L43" s="22" t="inlineStr">
-        <is>
-          <t>CHECKED BY</t>
-        </is>
-      </c>
-      <c r="M43" s="3" t="n"/>
-      <c r="N43" s="4" t="n"/>
-    </row>
-    <row r="44">
-      <c r="D44" s="23" t="inlineStr">
-        <is>
-          <t>TL QUALITY CONTROL</t>
-        </is>
-      </c>
-      <c r="E44" s="12" t="n"/>
-      <c r="F44" s="13" t="n"/>
-      <c r="H44" s="23" t="inlineStr">
-        <is>
-          <t>TL QUALITY CONTROL</t>
-        </is>
-      </c>
-      <c r="I44" s="12" t="n"/>
-      <c r="J44" s="13" t="n"/>
-      <c r="L44" s="23" t="inlineStr">
-        <is>
-          <t>TL QUALITY CONTROL</t>
-        </is>
-      </c>
-      <c r="M44" s="12" t="n"/>
-      <c r="N44" s="13" t="n"/>
-    </row>
-    <row r="45">
-      <c r="D45" s="22" t="n"/>
-      <c r="E45" s="3" t="n"/>
-      <c r="F45" s="4" t="n"/>
-      <c r="H45" s="22" t="n"/>
+      <c r="H45" s="3" t="n"/>
       <c r="I45" s="3" t="n"/>
       <c r="J45" s="4" t="n"/>
-      <c r="L45" s="22" t="n"/>
-      <c r="M45" s="3" t="n"/>
-      <c r="N45" s="4" t="n"/>
+      <c r="M45" s="22" t="inlineStr">
+        <is>
+          <t>APPROVED BY</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="n"/>
+      <c r="O45" s="3" t="n"/>
+      <c r="P45" s="4" t="n"/>
     </row>
     <row r="46">
-      <c r="D46" s="5" t="n"/>
-      <c r="E46" s="7" t="n"/>
-      <c r="F46" s="8" t="n"/>
-      <c r="H46" s="5" t="n"/>
-      <c r="I46" s="7" t="n"/>
-      <c r="J46" s="8" t="n"/>
-      <c r="L46" s="5" t="n"/>
-      <c r="M46" s="7" t="n"/>
-      <c r="N46" s="8" t="n"/>
+      <c r="A46" s="23" t="inlineStr">
+        <is>
+          <t>STAFF QUALITY CONTROL</t>
+        </is>
+      </c>
+      <c r="B46" s="12" t="n"/>
+      <c r="C46" s="12" t="n"/>
+      <c r="D46" s="13" t="n"/>
+      <c r="G46" s="23" t="inlineStr">
+        <is>
+          <t>TL QUALITY CONTROL</t>
+        </is>
+      </c>
+      <c r="H46" s="12" t="n"/>
+      <c r="I46" s="12" t="n"/>
+      <c r="J46" s="13" t="n"/>
+      <c r="M46" s="23" t="n"/>
+      <c r="N46" s="12" t="n"/>
+      <c r="O46" s="12" t="n"/>
+      <c r="P46" s="13" t="n"/>
     </row>
     <row r="47">
-      <c r="D47" s="5" t="n"/>
-      <c r="E47" s="7" t="n"/>
-      <c r="F47" s="8" t="n"/>
-      <c r="H47" s="5" t="n"/>
-      <c r="I47" s="7" t="n"/>
-      <c r="J47" s="8" t="n"/>
-      <c r="L47" s="5" t="n"/>
-      <c r="M47" s="7" t="n"/>
-      <c r="N47" s="8" t="n"/>
+      <c r="A47" s="22" t="n"/>
+      <c r="B47" s="3" t="n"/>
+      <c r="C47" s="3" t="n"/>
+      <c r="D47" s="4" t="n"/>
+      <c r="G47" s="22" t="n"/>
+      <c r="H47" s="3" t="n"/>
+      <c r="I47" s="3" t="n"/>
+      <c r="J47" s="4" t="n"/>
+      <c r="M47" s="22" t="n"/>
+      <c r="N47" s="3" t="n"/>
+      <c r="O47" s="3" t="n"/>
+      <c r="P47" s="4" t="n"/>
     </row>
     <row r="48">
-      <c r="D48" s="10" t="n"/>
-      <c r="E48" s="12" t="n"/>
-      <c r="F48" s="13" t="n"/>
-      <c r="H48" s="10" t="n"/>
-      <c r="I48" s="12" t="n"/>
-      <c r="J48" s="13" t="n"/>
-      <c r="L48" s="10" t="n"/>
-      <c r="M48" s="12" t="n"/>
-      <c r="N48" s="13" t="n"/>
+      <c r="A48" s="5" t="n"/>
+      <c r="B48" s="7" t="n"/>
+      <c r="C48" s="7" t="n"/>
+      <c r="D48" s="8" t="n"/>
+      <c r="G48" s="5" t="n"/>
+      <c r="H48" s="7" t="n"/>
+      <c r="I48" s="7" t="n"/>
+      <c r="J48" s="8" t="n"/>
+      <c r="M48" s="5" t="n"/>
+      <c r="N48" s="7" t="n"/>
+      <c r="O48" s="7" t="n"/>
+      <c r="P48" s="8" t="n"/>
     </row>
     <row r="49">
-      <c r="D49" s="24" t="inlineStr">
-        <is>
-          <t>BAGUS SANJAYA PUTRA</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="n"/>
-      <c r="F49" s="4" t="n"/>
-      <c r="H49" s="24" t="inlineStr">
-        <is>
-          <t>BAGUS SANJAYA PUTRA</t>
-        </is>
-      </c>
-      <c r="I49" s="3" t="n"/>
-      <c r="J49" s="4" t="n"/>
-      <c r="L49" s="24" t="inlineStr">
-        <is>
-          <t>BAGUS SANJAYA PUTRA</t>
-        </is>
-      </c>
-      <c r="M49" s="3" t="n"/>
-      <c r="N49" s="4" t="n"/>
+      <c r="A49" s="5" t="n"/>
+      <c r="B49" s="7" t="n"/>
+      <c r="C49" s="7" t="n"/>
+      <c r="D49" s="8" t="n"/>
+      <c r="G49" s="5" t="n"/>
+      <c r="H49" s="7" t="n"/>
+      <c r="I49" s="7" t="n"/>
+      <c r="J49" s="8" t="n"/>
+      <c r="M49" s="5" t="n"/>
+      <c r="N49" s="7" t="n"/>
+      <c r="O49" s="7" t="n"/>
+      <c r="P49" s="8" t="n"/>
     </row>
     <row r="50">
-      <c r="D50" s="10" t="n"/>
-      <c r="E50" s="12" t="n"/>
-      <c r="F50" s="13" t="n"/>
-      <c r="H50" s="10" t="n"/>
+      <c r="A50" s="10" t="n"/>
+      <c r="B50" s="12" t="n"/>
+      <c r="C50" s="12" t="n"/>
+      <c r="D50" s="13" t="n"/>
+      <c r="G50" s="10" t="n"/>
+      <c r="H50" s="12" t="n"/>
       <c r="I50" s="12" t="n"/>
       <c r="J50" s="13" t="n"/>
-      <c r="L50" s="10" t="n"/>
-      <c r="M50" s="12" t="n"/>
-      <c r="N50" s="13" t="n"/>
+      <c r="M50" s="10" t="n"/>
+      <c r="N50" s="12" t="n"/>
+      <c r="O50" s="12" t="n"/>
+      <c r="P50" s="13" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="22" t="n"/>
+      <c r="B51" s="3" t="n"/>
+      <c r="C51" s="3" t="n"/>
+      <c r="D51" s="4" t="n"/>
+      <c r="G51" s="24" t="inlineStr">
+        <is>
+          <t>BAGUS SANJAYA PUTRA</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="n"/>
+      <c r="I51" s="3" t="n"/>
+      <c r="J51" s="4" t="n"/>
+      <c r="M51" s="22" t="n"/>
+      <c r="N51" s="3" t="n"/>
+      <c r="O51" s="3" t="n"/>
+      <c r="P51" s="4" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="10" t="n"/>
+      <c r="B52" s="12" t="n"/>
+      <c r="C52" s="12" t="n"/>
+      <c r="D52" s="13" t="n"/>
+      <c r="G52" s="10" t="n"/>
+      <c r="H52" s="12" t="n"/>
+      <c r="I52" s="12" t="n"/>
+      <c r="J52" s="13" t="n"/>
+      <c r="M52" s="10" t="n"/>
+      <c r="N52" s="12" t="n"/>
+      <c r="O52" s="12" t="n"/>
+      <c r="P52" s="13" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="33">
+    <mergeCell ref="M45:P45"/>
     <mergeCell ref="A5:P5"/>
     <mergeCell ref="B2:P2"/>
     <mergeCell ref="I6:J6"/>
-    <mergeCell ref="L49:N50"/>
+    <mergeCell ref="A51:D52"/>
     <mergeCell ref="C9:H9"/>
     <mergeCell ref="B1:P1"/>
+    <mergeCell ref="M51:P52"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="D43:F43"/>
     <mergeCell ref="K8:P8"/>
+    <mergeCell ref="G46:J46"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="I7:J7"/>
-    <mergeCell ref="L44:N44"/>
-    <mergeCell ref="D49:F50"/>
     <mergeCell ref="C8:H8"/>
     <mergeCell ref="C7:H7"/>
     <mergeCell ref="K7:P7"/>
-    <mergeCell ref="H49:J50"/>
+    <mergeCell ref="A45:D45"/>
     <mergeCell ref="K6:P6"/>
-    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="G51:J52"/>
     <mergeCell ref="I8:J8"/>
     <mergeCell ref="B4:P4"/>
     <mergeCell ref="A8:B8"/>
-    <mergeCell ref="H43:J43"/>
-    <mergeCell ref="D45:F48"/>
+    <mergeCell ref="A46:D46"/>
     <mergeCell ref="C6:H6"/>
-    <mergeCell ref="H45:J48"/>
     <mergeCell ref="K9:P9"/>
-    <mergeCell ref="H44:J44"/>
-    <mergeCell ref="L45:N48"/>
+    <mergeCell ref="A47:D50"/>
     <mergeCell ref="B3:P3"/>
-    <mergeCell ref="L43:N43"/>
+    <mergeCell ref="M47:P50"/>
+    <mergeCell ref="G47:J50"/>
+    <mergeCell ref="M46:P46"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="I9:J9"/>
+    <mergeCell ref="G45:J45"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>

--- a/backend/data/reports/riwayat_hasil_ndt.xlsx
+++ b/backend/data/reports/riwayat_hasil_ndt.xlsx
@@ -612,7 +612,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P50"/>
+  <dimension ref="A1:P53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.09" customWidth="1" min="1" max="1"/>
@@ -768,7 +768,7 @@
       <c r="J6" s="3" t="n"/>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>: 20 Oktober 2026</t>
+          <t>: 21 Oktober 2026</t>
         </is>
       </c>
       <c r="L6" s="3" t="n"/>
@@ -836,7 +836,7 @@
       <c r="J8" s="7" t="n"/>
       <c r="K8" s="7" t="inlineStr">
         <is>
-          <t>: 30 data</t>
+          <t>: 33 data</t>
         </is>
       </c>
       <c r="L8" s="7" t="n"/>
@@ -870,7 +870,7 @@
       <c r="J9" s="12" t="n"/>
       <c r="K9" s="12" t="inlineStr">
         <is>
-          <t>: ACCEPT: 10  |  REJECT: 20</t>
+          <t>: ACC: 11  |  REJECT: 22</t>
         </is>
       </c>
       <c r="L9" s="12" t="n"/>
@@ -952,7 +952,7 @@
       </c>
       <c r="O11" s="17" t="inlineStr">
         <is>
-          <t>Inspector</t>
+          <t>Inspektur</t>
         </is>
       </c>
       <c r="P11" s="17" t="inlineStr">
@@ -963,7 +963,7 @@
     </row>
     <row r="12">
       <c r="A12" s="18" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B12" s="19" t="inlineStr">
         <is>
@@ -995,23 +995,23 @@
       </c>
       <c r="J12" s="20" t="inlineStr">
         <is>
-          <t>ACCEPT</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="K12" s="19" t="n">
-        <v>312</v>
+        <v>1</v>
       </c>
       <c r="L12" s="19" t="n">
-        <v>42.05</v>
-      </c>
-      <c r="M12" s="21" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="N12" s="21" t="inlineStr">
-        <is>
-          <t>REJECT</t>
+        <v>0.09</v>
+      </c>
+      <c r="M12" s="20" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="N12" s="20" t="inlineStr">
+        <is>
+          <t>ACC</t>
         </is>
       </c>
       <c r="O12" s="19" t="inlineStr">
@@ -1027,7 +1027,7 @@
     </row>
     <row r="13">
       <c r="A13" s="18" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
@@ -1059,14 +1059,14 @@
       </c>
       <c r="J13" s="20" t="inlineStr">
         <is>
-          <t>ACCEPT</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="K13" s="19" t="n">
-        <v>299</v>
+        <v>63</v>
       </c>
       <c r="L13" s="19" t="n">
-        <v>39.61</v>
+        <v>6.36</v>
       </c>
       <c r="M13" s="21" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
     </row>
     <row r="14">
       <c r="A14" s="18" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B14" s="19" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="C14" s="19" t="n">
-        <v>150</v>
+        <v>38</v>
       </c>
       <c r="D14" s="19" t="inlineStr">
         <is>
@@ -1107,13 +1107,13 @@
         </is>
       </c>
       <c r="E14" s="19" t="n">
-        <v>23797.56</v>
+        <v>1432.57</v>
       </c>
       <c r="F14" s="19" t="n">
-        <v>6391.67</v>
+        <v>378.67</v>
       </c>
       <c r="G14" s="19" t="n">
-        <v>17405.89</v>
+        <v>1053.89</v>
       </c>
       <c r="H14" s="19" t="n">
         <v>0</v>
@@ -1123,39 +1123,39 @@
       </c>
       <c r="J14" s="20" t="inlineStr">
         <is>
-          <t>ACCEPT</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="K14" s="19" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="L14" s="19" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="M14" s="20" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
-        </is>
-      </c>
-      <c r="N14" s="20" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+        <v>8.210000000000001</v>
+      </c>
+      <c r="M14" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="N14" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="O14" s="19" t="inlineStr">
         <is>
-          <t>kahfi</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="P14" s="19" t="inlineStr">
         <is>
-          <t>PLTA Maninjau</t>
+          <t>PLTU</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="18" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B15" s="19" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="C15" s="19" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="D15" s="19" t="inlineStr">
         <is>
@@ -1171,30 +1171,30 @@
         </is>
       </c>
       <c r="E15" s="19" t="n">
-        <v>15150</v>
+        <v>1432.57</v>
       </c>
       <c r="F15" s="19" t="n">
-        <v>4662.16</v>
+        <v>378.67</v>
       </c>
       <c r="G15" s="19" t="n">
-        <v>10487.84</v>
+        <v>1053.89</v>
       </c>
       <c r="H15" s="19" t="n">
-        <v>2720</v>
+        <v>0</v>
       </c>
       <c r="I15" s="19" t="n">
-        <v>140.05</v>
-      </c>
-      <c r="J15" s="21" t="inlineStr">
-        <is>
-          <t>REJECT</t>
+        <v>0</v>
+      </c>
+      <c r="J15" s="20" t="inlineStr">
+        <is>
+          <t>ACC</t>
         </is>
       </c>
       <c r="K15" s="19" t="n">
-        <v>4550</v>
+        <v>312</v>
       </c>
       <c r="L15" s="19" t="n">
-        <v>76.63</v>
+        <v>42.05</v>
       </c>
       <c r="M15" s="21" t="inlineStr">
         <is>
@@ -1208,18 +1208,18 @@
       </c>
       <c r="O15" s="19" t="inlineStr">
         <is>
-          <t>kahfi</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="P15" s="19" t="inlineStr">
         <is>
-          <t>PLTA Maninjau</t>
+          <t>PLTU</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="18" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B16" s="19" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         </is>
       </c>
       <c r="C16" s="19" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="D16" s="19" t="inlineStr">
         <is>
@@ -1235,30 +1235,30 @@
         </is>
       </c>
       <c r="E16" s="19" t="n">
-        <v>15150</v>
+        <v>1432.57</v>
       </c>
       <c r="F16" s="19" t="n">
-        <v>4662.16</v>
+        <v>378.67</v>
       </c>
       <c r="G16" s="19" t="n">
-        <v>10487.84</v>
+        <v>1053.89</v>
       </c>
       <c r="H16" s="19" t="n">
-        <v>2720</v>
+        <v>0</v>
       </c>
       <c r="I16" s="19" t="n">
-        <v>140.05</v>
-      </c>
-      <c r="J16" s="21" t="inlineStr">
-        <is>
-          <t>REJECT</t>
+        <v>0</v>
+      </c>
+      <c r="J16" s="20" t="inlineStr">
+        <is>
+          <t>ACC</t>
         </is>
       </c>
       <c r="K16" s="19" t="n">
-        <v>4550</v>
+        <v>299</v>
       </c>
       <c r="L16" s="19" t="n">
-        <v>76.63</v>
+        <v>39.61</v>
       </c>
       <c r="M16" s="21" t="inlineStr">
         <is>
@@ -1272,22 +1272,22 @@
       </c>
       <c r="O16" s="19" t="inlineStr">
         <is>
-          <t>kahfi</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="P16" s="19" t="inlineStr">
         <is>
-          <t>PLTA Maninjau</t>
+          <t>PLTU</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="18" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B17" s="19" t="inlineStr">
         <is>
-          <t>Beearing</t>
+          <t>Bearing</t>
         </is>
       </c>
       <c r="C17" s="19" t="n">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="D17" s="19" t="inlineStr">
         <is>
-          <t>Lower</t>
+          <t>Upper</t>
         </is>
       </c>
       <c r="E17" s="19" t="n">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="J17" s="20" t="inlineStr">
         <is>
-          <t>ACCEPT</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="K17" s="19" t="n">
@@ -1326,12 +1326,12 @@
       </c>
       <c r="M17" s="20" t="inlineStr">
         <is>
-          <t>ACCEPT</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="N17" s="20" t="inlineStr">
         <is>
-          <t>ACCEPT</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="O17" s="19" t="inlineStr">
@@ -1341,17 +1341,17 @@
       </c>
       <c r="P17" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PLTA Maninjau</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="18" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B18" s="19" t="inlineStr">
         <is>
-          <t>Beearing</t>
+          <t>Bearing</t>
         </is>
       </c>
       <c r="C18" s="19" t="n">
@@ -1405,13 +1405,13 @@
       </c>
       <c r="P18" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PLTA Maninjau</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="18" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B19" s="19" t="inlineStr">
         <is>
@@ -1419,38 +1419,38 @@
         </is>
       </c>
       <c r="C19" s="19" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="D19" s="19" t="inlineStr">
         <is>
-          <t>Lower</t>
+          <t>Upper</t>
         </is>
       </c>
       <c r="E19" s="19" t="n">
-        <v>721</v>
+        <v>15150</v>
       </c>
       <c r="F19" s="19" t="n">
-        <v>260.84</v>
+        <v>4662.16</v>
       </c>
       <c r="G19" s="19" t="n">
-        <v>460.16</v>
+        <v>10487.84</v>
       </c>
       <c r="H19" s="19" t="n">
-        <v>0</v>
+        <v>2720</v>
       </c>
       <c r="I19" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="20" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+        <v>140.05</v>
+      </c>
+      <c r="J19" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="K19" s="19" t="n">
-        <v>1948</v>
+        <v>4550</v>
       </c>
       <c r="L19" s="19" t="n">
-        <v>-130.93</v>
+        <v>76.63</v>
       </c>
       <c r="M19" s="21" t="inlineStr">
         <is>
@@ -1464,40 +1464,40 @@
       </c>
       <c r="O19" s="19" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>kahfi</t>
         </is>
       </c>
       <c r="P19" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PLTA Maninjau</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="18" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B20" s="19" t="inlineStr">
         <is>
-          <t>Bearing</t>
+          <t>Beearing</t>
         </is>
       </c>
       <c r="C20" s="19" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="D20" s="19" t="inlineStr">
         <is>
-          <t>Upper</t>
+          <t>Lower</t>
         </is>
       </c>
       <c r="E20" s="19" t="n">
-        <v>10822.79</v>
+        <v>23797.56</v>
       </c>
       <c r="F20" s="19" t="n">
-        <v>3962.32</v>
+        <v>6391.67</v>
       </c>
       <c r="G20" s="19" t="n">
-        <v>6860.47</v>
+        <v>17405.89</v>
       </c>
       <c r="H20" s="19" t="n">
         <v>0</v>
@@ -1507,28 +1507,28 @@
       </c>
       <c r="J20" s="20" t="inlineStr">
         <is>
-          <t>ACCEPT</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="K20" s="19" t="n">
-        <v>1560</v>
+        <v>100</v>
       </c>
       <c r="L20" s="19" t="n">
-        <v>29.43</v>
-      </c>
-      <c r="M20" s="21" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="N20" s="21" t="inlineStr">
-        <is>
-          <t>REJECT</t>
+        <v>0.58</v>
+      </c>
+      <c r="M20" s="20" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="N20" s="20" t="inlineStr">
+        <is>
+          <t>ACC</t>
         </is>
       </c>
       <c r="O20" s="19" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>kahfi</t>
         </is>
       </c>
       <c r="P20" s="19" t="inlineStr">
@@ -1539,15 +1539,15 @@
     </row>
     <row r="21">
       <c r="A21" s="18" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B21" s="19" t="inlineStr">
         <is>
-          <t>bearing</t>
+          <t>Beearing</t>
         </is>
       </c>
       <c r="C21" s="19" t="n">
-        <v>795</v>
+        <v>0</v>
       </c>
       <c r="D21" s="19" t="inlineStr">
         <is>
@@ -1555,30 +1555,30 @@
         </is>
       </c>
       <c r="E21" s="19" t="n">
-        <v>427083.81</v>
+        <v>15150</v>
       </c>
       <c r="F21" s="19" t="n">
-        <v>104131</v>
+        <v>4662.16</v>
       </c>
       <c r="G21" s="19" t="n">
-        <v>322952.81</v>
+        <v>10487.84</v>
       </c>
       <c r="H21" s="19" t="n">
-        <v>0</v>
+        <v>2720</v>
       </c>
       <c r="I21" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="20" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+        <v>140.05</v>
+      </c>
+      <c r="J21" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="K21" s="19" t="n">
-        <v>8612</v>
+        <v>4550</v>
       </c>
       <c r="L21" s="19" t="n">
-        <v>2.74</v>
+        <v>76.63</v>
       </c>
       <c r="M21" s="21" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="O21" s="19" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>kahfi</t>
         </is>
       </c>
       <c r="P21" s="19" t="inlineStr">
@@ -1603,29 +1603,29 @@
     </row>
     <row r="22">
       <c r="A22" s="18" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B22" s="19" t="inlineStr">
         <is>
-          <t>bearing</t>
+          <t>Bearing</t>
         </is>
       </c>
       <c r="C22" s="19" t="n">
-        <v>123</v>
+        <v>17</v>
       </c>
       <c r="D22" s="19" t="inlineStr">
         <is>
-          <t>Upper</t>
+          <t>Lower</t>
         </is>
       </c>
       <c r="E22" s="19" t="n">
-        <v>5989.45</v>
+        <v>721</v>
       </c>
       <c r="F22" s="19" t="n">
-        <v>1351.65</v>
+        <v>260.84</v>
       </c>
       <c r="G22" s="19" t="n">
-        <v>4637.8</v>
+        <v>460.16</v>
       </c>
       <c r="H22" s="19" t="n">
         <v>0</v>
@@ -1635,14 +1635,14 @@
       </c>
       <c r="J22" s="20" t="inlineStr">
         <is>
-          <t>ACCEPT</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="K22" s="19" t="n">
-        <v>1253</v>
+        <v>1948</v>
       </c>
       <c r="L22" s="19" t="n">
-        <v>37.02</v>
+        <v>-130.93</v>
       </c>
       <c r="M22" s="21" t="inlineStr">
         <is>
@@ -1667,15 +1667,15 @@
     </row>
     <row r="23">
       <c r="A23" s="18" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B23" s="19" t="inlineStr">
         <is>
-          <t>bearing</t>
+          <t>Bearing</t>
         </is>
       </c>
       <c r="C23" s="19" t="n">
-        <v>123</v>
+        <v>65</v>
       </c>
       <c r="D23" s="19" t="inlineStr">
         <is>
@@ -1683,13 +1683,13 @@
         </is>
       </c>
       <c r="E23" s="19" t="n">
-        <v>5989.45</v>
+        <v>10822.79</v>
       </c>
       <c r="F23" s="19" t="n">
-        <v>1351.65</v>
+        <v>3962.32</v>
       </c>
       <c r="G23" s="19" t="n">
-        <v>4637.8</v>
+        <v>6860.47</v>
       </c>
       <c r="H23" s="19" t="n">
         <v>0</v>
@@ -1699,14 +1699,14 @@
       </c>
       <c r="J23" s="20" t="inlineStr">
         <is>
-          <t>ACCEPT</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="K23" s="19" t="n">
-        <v>1253</v>
+        <v>1560</v>
       </c>
       <c r="L23" s="19" t="n">
-        <v>37.02</v>
+        <v>29.43</v>
       </c>
       <c r="M23" s="21" t="inlineStr">
         <is>
@@ -1731,29 +1731,29 @@
     </row>
     <row r="24">
       <c r="A24" s="18" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B24" s="19" t="inlineStr">
         <is>
-          <t>Bearing</t>
+          <t>bearing</t>
         </is>
       </c>
       <c r="C24" s="19" t="n">
-        <v>234</v>
+        <v>795</v>
       </c>
       <c r="D24" s="19" t="inlineStr">
         <is>
-          <t>Lower</t>
+          <t>Upper</t>
         </is>
       </c>
       <c r="E24" s="19" t="n">
-        <v>158788.66</v>
+        <v>427083.81</v>
       </c>
       <c r="F24" s="19" t="n">
-        <v>61617.57</v>
+        <v>104131</v>
       </c>
       <c r="G24" s="19" t="n">
-        <v>97171.09</v>
+        <v>322952.81</v>
       </c>
       <c r="H24" s="19" t="n">
         <v>0</v>
@@ -1763,14 +1763,14 @@
       </c>
       <c r="J24" s="20" t="inlineStr">
         <is>
-          <t>ACCEPT</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="K24" s="19" t="n">
-        <v>10620</v>
+        <v>8612</v>
       </c>
       <c r="L24" s="19" t="n">
-        <v>12.27</v>
+        <v>2.74</v>
       </c>
       <c r="M24" s="21" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
     </row>
     <row r="25">
       <c r="A25" s="18" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B25" s="19" t="inlineStr">
         <is>
@@ -1803,38 +1803,42 @@
         </is>
       </c>
       <c r="C25" s="19" t="n">
-        <v>65</v>
-      </c>
-      <c r="D25" s="19" t="inlineStr"/>
+        <v>123</v>
+      </c>
+      <c r="D25" s="19" t="inlineStr">
+        <is>
+          <t>Upper</t>
+        </is>
+      </c>
       <c r="E25" s="19" t="n">
-        <v>5105.09</v>
+        <v>5989.45</v>
       </c>
       <c r="F25" s="19" t="n">
-        <v>5748.34</v>
+        <v>1351.65</v>
       </c>
       <c r="G25" s="19" t="n">
-        <v>-643.26</v>
+        <v>4637.8</v>
       </c>
       <c r="H25" s="19" t="n">
-        <v>176</v>
+        <v>0</v>
       </c>
       <c r="I25" s="19" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="J25" s="21" t="inlineStr">
-        <is>
-          <t>REJECT</t>
+        <v>0</v>
+      </c>
+      <c r="J25" s="20" t="inlineStr">
+        <is>
+          <t>ACC</t>
         </is>
       </c>
       <c r="K25" s="19" t="n">
-        <v>0</v>
+        <v>1253</v>
       </c>
       <c r="L25" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" s="20" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+        <v>37.02</v>
+      </c>
+      <c r="M25" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="N25" s="21" t="inlineStr">
@@ -1855,15 +1859,15 @@
     </row>
     <row r="26">
       <c r="A26" s="18" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B26" s="19" t="inlineStr">
         <is>
-          <t>Bearing</t>
+          <t>bearing</t>
         </is>
       </c>
       <c r="C26" s="19" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="D26" s="19" t="inlineStr">
         <is>
@@ -1871,30 +1875,30 @@
         </is>
       </c>
       <c r="E26" s="19" t="n">
-        <v>15150</v>
+        <v>5989.45</v>
       </c>
       <c r="F26" s="19" t="n">
-        <v>4620</v>
+        <v>1351.65</v>
       </c>
       <c r="G26" s="19" t="n">
-        <v>10530</v>
+        <v>4637.8</v>
       </c>
       <c r="H26" s="19" t="n">
-        <v>2720</v>
+        <v>0</v>
       </c>
       <c r="I26" s="19" t="n">
-        <v>143.16</v>
-      </c>
-      <c r="J26" s="21" t="inlineStr">
-        <is>
-          <t>REJECT</t>
+        <v>0</v>
+      </c>
+      <c r="J26" s="20" t="inlineStr">
+        <is>
+          <t>ACC</t>
         </is>
       </c>
       <c r="K26" s="19" t="n">
-        <v>4550</v>
+        <v>1253</v>
       </c>
       <c r="L26" s="19" t="n">
-        <v>76.09</v>
+        <v>37.02</v>
       </c>
       <c r="M26" s="21" t="inlineStr">
         <is>
@@ -1908,7 +1912,7 @@
       </c>
       <c r="O26" s="19" t="inlineStr">
         <is>
-          <t>kahfi</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="P26" s="19" t="inlineStr">
@@ -1919,7 +1923,7 @@
     </row>
     <row r="27">
       <c r="A27" s="18" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="B27" s="19" t="inlineStr">
         <is>
@@ -1927,38 +1931,38 @@
         </is>
       </c>
       <c r="C27" s="19" t="n">
-        <v>95.40000000000001</v>
+        <v>234</v>
       </c>
       <c r="D27" s="19" t="inlineStr">
         <is>
-          <t>Upper</t>
+          <t>Lower</t>
         </is>
       </c>
       <c r="E27" s="19" t="n">
-        <v>15135.25</v>
+        <v>158788.66</v>
       </c>
       <c r="F27" s="19" t="n">
-        <v>9868.5</v>
+        <v>61617.57</v>
       </c>
       <c r="G27" s="19" t="n">
-        <v>5266.75</v>
+        <v>97171.09</v>
       </c>
       <c r="H27" s="19" t="n">
-        <v>2720</v>
+        <v>0</v>
       </c>
       <c r="I27" s="19" t="n">
-        <v>38.05</v>
-      </c>
-      <c r="J27" s="21" t="inlineStr">
-        <is>
-          <t>REJECT</t>
+        <v>0</v>
+      </c>
+      <c r="J27" s="20" t="inlineStr">
+        <is>
+          <t>ACC</t>
         </is>
       </c>
       <c r="K27" s="19" t="n">
-        <v>4550</v>
+        <v>10620</v>
       </c>
       <c r="L27" s="19" t="n">
-        <v>634.8099999999999</v>
+        <v>12.27</v>
       </c>
       <c r="M27" s="21" t="inlineStr">
         <is>
@@ -1972,7 +1976,7 @@
       </c>
       <c r="O27" s="19" t="inlineStr">
         <is>
-          <t>kahfi</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="P27" s="19" t="inlineStr">
@@ -1983,35 +1987,31 @@
     </row>
     <row r="28">
       <c r="A28" s="18" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="B28" s="19" t="inlineStr">
         <is>
-          <t>Bearing</t>
+          <t>bearing</t>
         </is>
       </c>
       <c r="C28" s="19" t="n">
-        <v>360</v>
-      </c>
-      <c r="D28" s="19" t="inlineStr">
-        <is>
-          <t>Upper</t>
-        </is>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="D28" s="19" t="inlineStr"/>
       <c r="E28" s="19" t="n">
-        <v>84823</v>
+        <v>5105.09</v>
       </c>
       <c r="F28" s="19" t="n">
-        <v>33274.33</v>
+        <v>5748.34</v>
       </c>
       <c r="G28" s="19" t="n">
-        <v>51548.67</v>
+        <v>-643.26</v>
       </c>
       <c r="H28" s="19" t="n">
-        <v>2720</v>
+        <v>176</v>
       </c>
       <c r="I28" s="19" t="n">
-        <v>8.9</v>
+        <v>3.16</v>
       </c>
       <c r="J28" s="21" t="inlineStr">
         <is>
@@ -2019,14 +2019,14 @@
         </is>
       </c>
       <c r="K28" s="19" t="n">
-        <v>4550</v>
+        <v>0</v>
       </c>
       <c r="L28" s="19" t="n">
-        <v>9.68</v>
-      </c>
-      <c r="M28" s="21" t="inlineStr">
-        <is>
-          <t>REJECT</t>
+        <v>0</v>
+      </c>
+      <c r="M28" s="20" t="inlineStr">
+        <is>
+          <t>ACC</t>
         </is>
       </c>
       <c r="N28" s="21" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="O28" s="19" t="inlineStr">
         <is>
-          <t>kahfi</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="P28" s="19" t="inlineStr">
@@ -2047,15 +2047,15 @@
     </row>
     <row r="29">
       <c r="A29" s="18" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B29" s="19" t="inlineStr">
         <is>
-          <t>bearing</t>
+          <t>Bearing</t>
         </is>
       </c>
       <c r="C29" s="19" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D29" s="19" t="inlineStr">
         <is>
@@ -2063,19 +2063,19 @@
         </is>
       </c>
       <c r="E29" s="19" t="n">
-        <v>5105.09</v>
+        <v>15150</v>
       </c>
       <c r="F29" s="19" t="n">
-        <v>5105.09</v>
+        <v>4620</v>
       </c>
       <c r="G29" s="19" t="n">
-        <v>0</v>
+        <v>10530</v>
       </c>
       <c r="H29" s="19" t="n">
-        <v>14760</v>
+        <v>2720</v>
       </c>
       <c r="I29" s="19" t="n">
-        <v>-152.88</v>
+        <v>143.16</v>
       </c>
       <c r="J29" s="21" t="inlineStr">
         <is>
@@ -2083,14 +2083,14 @@
         </is>
       </c>
       <c r="K29" s="19" t="n">
-        <v>0</v>
+        <v>4550</v>
       </c>
       <c r="L29" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" s="20" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+        <v>76.09</v>
+      </c>
+      <c r="M29" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="N29" s="21" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="O29" s="19" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>kahfi</t>
         </is>
       </c>
       <c r="P29" s="19" t="inlineStr">
@@ -2111,7 +2111,7 @@
     </row>
     <row r="30">
       <c r="A30" s="18" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="B30" s="19" t="inlineStr">
         <is>
@@ -2119,52 +2119,52 @@
         </is>
       </c>
       <c r="C30" s="19" t="n">
-        <v>360</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="D30" s="19" t="inlineStr">
         <is>
-          <t>Zone C</t>
+          <t>Upper</t>
         </is>
       </c>
       <c r="E30" s="19" t="n">
-        <v>57114.15</v>
+        <v>15135.25</v>
       </c>
       <c r="F30" s="19" t="n">
-        <v>30824.33</v>
+        <v>9868.5</v>
       </c>
       <c r="G30" s="19" t="n">
-        <v>26289.82</v>
+        <v>5266.75</v>
       </c>
       <c r="H30" s="19" t="n">
-        <v>39</v>
+        <v>2720</v>
       </c>
       <c r="I30" s="19" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="J30" s="20" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+        <v>38.05</v>
+      </c>
+      <c r="J30" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="K30" s="19" t="n">
-        <v>300</v>
+        <v>4550</v>
       </c>
       <c r="L30" s="19" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="M30" s="20" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
-        </is>
-      </c>
-      <c r="N30" s="20" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+        <v>634.8099999999999</v>
+      </c>
+      <c r="M30" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="N30" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="O30" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>kahfi</t>
         </is>
       </c>
       <c r="P30" s="19" t="inlineStr">
@@ -2175,46 +2175,46 @@
     </row>
     <row r="31">
       <c r="A31" s="18" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="B31" s="19" t="inlineStr">
         <is>
-          <t>bearing</t>
+          <t>Bearing</t>
         </is>
       </c>
       <c r="C31" s="19" t="n">
-        <v>21</v>
+        <v>360</v>
       </c>
       <c r="D31" s="19" t="inlineStr">
         <is>
-          <t>zone a</t>
+          <t>Upper</t>
         </is>
       </c>
       <c r="E31" s="19" t="n">
-        <v>692.72</v>
+        <v>84823</v>
       </c>
       <c r="F31" s="19" t="n">
-        <v>199.34</v>
+        <v>33274.33</v>
       </c>
       <c r="G31" s="19" t="n">
-        <v>493.39</v>
+        <v>51548.67</v>
       </c>
       <c r="H31" s="19" t="n">
-        <v>0</v>
+        <v>2720</v>
       </c>
       <c r="I31" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="20" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+        <v>8.9</v>
+      </c>
+      <c r="J31" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="K31" s="19" t="n">
-        <v>6371</v>
+        <v>4550</v>
       </c>
       <c r="L31" s="19" t="n">
-        <v>-108.39</v>
+        <v>9.68</v>
       </c>
       <c r="M31" s="21" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="O31" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>kahfi</t>
         </is>
       </c>
       <c r="P31" s="19" t="inlineStr">
@@ -2239,7 +2239,7 @@
     </row>
     <row r="32">
       <c r="A32" s="18" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="B32" s="19" t="inlineStr">
         <is>
@@ -2247,42 +2247,42 @@
         </is>
       </c>
       <c r="C32" s="19" t="n">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="D32" s="19" t="inlineStr">
         <is>
-          <t>zone a</t>
+          <t>Upper</t>
         </is>
       </c>
       <c r="E32" s="19" t="n">
-        <v>692.72</v>
+        <v>5105.09</v>
       </c>
       <c r="F32" s="19" t="n">
-        <v>199.34</v>
+        <v>5105.09</v>
       </c>
       <c r="G32" s="19" t="n">
-        <v>493.39</v>
+        <v>0</v>
       </c>
       <c r="H32" s="19" t="n">
-        <v>0</v>
+        <v>14760</v>
       </c>
       <c r="I32" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="20" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+        <v>-152.88</v>
+      </c>
+      <c r="J32" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="K32" s="19" t="n">
-        <v>341</v>
+        <v>0</v>
       </c>
       <c r="L32" s="19" t="n">
-        <v>223.78</v>
-      </c>
-      <c r="M32" s="21" t="inlineStr">
-        <is>
-          <t>REJECT</t>
+        <v>0</v>
+      </c>
+      <c r="M32" s="20" t="inlineStr">
+        <is>
+          <t>ACC</t>
         </is>
       </c>
       <c r="N32" s="21" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="O32" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="P32" s="19" t="inlineStr">
@@ -2303,39 +2303,55 @@
     </row>
     <row r="33">
       <c r="A33" s="18" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B33" s="19" t="inlineStr">
         <is>
-          <t>bearing</t>
+          <t>Bearing</t>
         </is>
       </c>
       <c r="C33" s="19" t="n">
-        <v>49</v>
+        <v>360</v>
       </c>
       <c r="D33" s="19" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>Zone C</t>
         </is>
       </c>
       <c r="E33" s="19" t="n">
-        <v>1616.35</v>
+        <v>57114.15</v>
       </c>
       <c r="F33" s="19" t="n">
-        <v>2398.45</v>
+        <v>30824.33</v>
       </c>
       <c r="G33" s="19" t="n">
-        <v>-782.1</v>
-      </c>
-      <c r="H33" s="19" t="n"/>
-      <c r="I33" s="19" t="n"/>
-      <c r="J33" s="19" t="n"/>
-      <c r="K33" s="19" t="n"/>
-      <c r="L33" s="19" t="n"/>
-      <c r="M33" s="19" t="n"/>
+        <v>26289.82</v>
+      </c>
+      <c r="H33" s="19" t="n">
+        <v>39</v>
+      </c>
+      <c r="I33" s="19" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="J33" s="20" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="K33" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="L33" s="19" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="M33" s="20" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
       <c r="N33" s="20" t="inlineStr">
         <is>
-          <t>ACCEPT</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="O33" s="19" t="inlineStr">
@@ -2351,7 +2367,7 @@
     </row>
     <row r="34">
       <c r="A34" s="18" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B34" s="19" t="inlineStr">
         <is>
@@ -2359,28 +2375,44 @@
         </is>
       </c>
       <c r="C34" s="19" t="n">
-        <v>360</v>
+        <v>21</v>
       </c>
       <c r="D34" s="19" t="inlineStr">
         <is>
-          <t>Zona A</t>
+          <t>zone a</t>
         </is>
       </c>
       <c r="E34" s="19" t="n">
-        <v>84823</v>
+        <v>692.72</v>
       </c>
       <c r="F34" s="19" t="n">
-        <v>33274.33</v>
+        <v>199.34</v>
       </c>
       <c r="G34" s="19" t="n">
-        <v>51548.67</v>
-      </c>
-      <c r="H34" s="19" t="n"/>
-      <c r="I34" s="19" t="n"/>
-      <c r="J34" s="19" t="n"/>
-      <c r="K34" s="19" t="n"/>
-      <c r="L34" s="19" t="n"/>
-      <c r="M34" s="19" t="n"/>
+        <v>493.39</v>
+      </c>
+      <c r="H34" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="20" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="K34" s="19" t="n">
+        <v>6371</v>
+      </c>
+      <c r="L34" s="19" t="n">
+        <v>-108.39</v>
+      </c>
+      <c r="M34" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
       <c r="N34" s="21" t="inlineStr">
         <is>
           <t>REJECT</t>
@@ -2399,7 +2431,7 @@
     </row>
     <row r="35">
       <c r="A35" s="18" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B35" s="19" t="inlineStr">
         <is>
@@ -2407,28 +2439,44 @@
         </is>
       </c>
       <c r="C35" s="19" t="n">
-        <v>360</v>
+        <v>21</v>
       </c>
       <c r="D35" s="19" t="inlineStr">
         <is>
-          <t>Zona A</t>
+          <t>zone a</t>
         </is>
       </c>
       <c r="E35" s="19" t="n">
-        <v>84823</v>
+        <v>692.72</v>
       </c>
       <c r="F35" s="19" t="n">
-        <v>33274.33</v>
+        <v>199.34</v>
       </c>
       <c r="G35" s="19" t="n">
-        <v>51548.67</v>
-      </c>
-      <c r="H35" s="19" t="n"/>
-      <c r="I35" s="19" t="n"/>
-      <c r="J35" s="19" t="n"/>
-      <c r="K35" s="19" t="n"/>
-      <c r="L35" s="19" t="n"/>
-      <c r="M35" s="19" t="n"/>
+        <v>493.39</v>
+      </c>
+      <c r="H35" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="20" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="K35" s="19" t="n">
+        <v>341</v>
+      </c>
+      <c r="L35" s="19" t="n">
+        <v>223.78</v>
+      </c>
+      <c r="M35" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
       <c r="N35" s="21" t="inlineStr">
         <is>
           <t>REJECT</t>
@@ -2447,7 +2495,7 @@
     </row>
     <row r="36">
       <c r="A36" s="18" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B36" s="19" t="inlineStr">
         <is>
@@ -2455,21 +2503,21 @@
         </is>
       </c>
       <c r="C36" s="19" t="n">
-        <v>360</v>
+        <v>49</v>
       </c>
       <c r="D36" s="19" t="inlineStr">
         <is>
-          <t>Zona A</t>
+          <t>b</t>
         </is>
       </c>
       <c r="E36" s="19" t="n">
-        <v>113097.34</v>
+        <v>1616.35</v>
       </c>
       <c r="F36" s="19" t="n">
-        <v>35774.33</v>
+        <v>2398.45</v>
       </c>
       <c r="G36" s="19" t="n">
-        <v>77323</v>
+        <v>-782.1</v>
       </c>
       <c r="H36" s="19" t="n"/>
       <c r="I36" s="19" t="n"/>
@@ -2479,7 +2527,7 @@
       <c r="M36" s="19" t="n"/>
       <c r="N36" s="20" t="inlineStr">
         <is>
-          <t>ACCEPT</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="O36" s="19" t="inlineStr">
@@ -2495,7 +2543,7 @@
     </row>
     <row r="37">
       <c r="A37" s="18" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B37" s="19" t="inlineStr">
         <is>
@@ -2511,13 +2559,13 @@
         </is>
       </c>
       <c r="E37" s="19" t="n">
-        <v>113097.34</v>
+        <v>84823</v>
       </c>
       <c r="F37" s="19" t="n">
-        <v>35774.33</v>
+        <v>33274.33</v>
       </c>
       <c r="G37" s="19" t="n">
-        <v>77323</v>
+        <v>51548.67</v>
       </c>
       <c r="H37" s="19" t="n"/>
       <c r="I37" s="19" t="n"/>
@@ -2525,9 +2573,9 @@
       <c r="K37" s="19" t="n"/>
       <c r="L37" s="19" t="n"/>
       <c r="M37" s="19" t="n"/>
-      <c r="N37" s="20" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+      <c r="N37" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="O37" s="19" t="inlineStr">
@@ -2543,7 +2591,7 @@
     </row>
     <row r="38">
       <c r="A38" s="18" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B38" s="19" t="inlineStr">
         <is>
@@ -2559,13 +2607,13 @@
         </is>
       </c>
       <c r="E38" s="19" t="n">
-        <v>113097.34</v>
+        <v>84823</v>
       </c>
       <c r="F38" s="19" t="n">
-        <v>35774.33</v>
+        <v>33274.33</v>
       </c>
       <c r="G38" s="19" t="n">
-        <v>77323</v>
+        <v>51548.67</v>
       </c>
       <c r="H38" s="19" t="n"/>
       <c r="I38" s="19" t="n"/>
@@ -2573,9 +2621,9 @@
       <c r="K38" s="19" t="n"/>
       <c r="L38" s="19" t="n"/>
       <c r="M38" s="19" t="n"/>
-      <c r="N38" s="20" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
+      <c r="N38" s="21" t="inlineStr">
+        <is>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="O38" s="19" t="inlineStr">
@@ -2591,7 +2639,7 @@
     </row>
     <row r="39">
       <c r="A39" s="18" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B39" s="19" t="inlineStr">
         <is>
@@ -2623,7 +2671,7 @@
       <c r="M39" s="19" t="n"/>
       <c r="N39" s="20" t="inlineStr">
         <is>
-          <t>ACCEPT</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="O39" s="19" t="inlineStr">
@@ -2639,7 +2687,7 @@
     </row>
     <row r="40">
       <c r="A40" s="18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B40" s="19" t="inlineStr">
         <is>
@@ -2671,7 +2719,7 @@
       <c r="M40" s="19" t="n"/>
       <c r="N40" s="20" t="inlineStr">
         <is>
-          <t>ACCEPT</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="O40" s="19" t="inlineStr">
@@ -2687,7 +2735,7 @@
     </row>
     <row r="41">
       <c r="A41" s="18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B41" s="19" t="inlineStr">
         <is>
@@ -2719,7 +2767,7 @@
       <c r="M41" s="19" t="n"/>
       <c r="N41" s="20" t="inlineStr">
         <is>
-          <t>ACCEPT</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="O41" s="19" t="inlineStr">
@@ -2733,164 +2781,320 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="B42" s="19" t="inlineStr">
+        <is>
+          <t>bearing</t>
+        </is>
+      </c>
+      <c r="C42" s="19" t="n">
+        <v>360</v>
+      </c>
+      <c r="D42" s="19" t="inlineStr">
+        <is>
+          <t>Zona A</t>
+        </is>
+      </c>
+      <c r="E42" s="19" t="n">
+        <v>113097.34</v>
+      </c>
+      <c r="F42" s="19" t="n">
+        <v>35774.33</v>
+      </c>
+      <c r="G42" s="19" t="n">
+        <v>77323</v>
+      </c>
+      <c r="H42" s="19" t="n"/>
+      <c r="I42" s="19" t="n"/>
+      <c r="J42" s="19" t="n"/>
+      <c r="K42" s="19" t="n"/>
+      <c r="L42" s="19" t="n"/>
+      <c r="M42" s="19" t="n"/>
+      <c r="N42" s="20" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="O42" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P42" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
     <row r="43">
-      <c r="D43" s="22" t="inlineStr">
+      <c r="A43" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="B43" s="19" t="inlineStr">
+        <is>
+          <t>bearing</t>
+        </is>
+      </c>
+      <c r="C43" s="19" t="n">
+        <v>360</v>
+      </c>
+      <c r="D43" s="19" t="inlineStr">
+        <is>
+          <t>Zona A</t>
+        </is>
+      </c>
+      <c r="E43" s="19" t="n">
+        <v>113097.34</v>
+      </c>
+      <c r="F43" s="19" t="n">
+        <v>35774.33</v>
+      </c>
+      <c r="G43" s="19" t="n">
+        <v>77323</v>
+      </c>
+      <c r="H43" s="19" t="n"/>
+      <c r="I43" s="19" t="n"/>
+      <c r="J43" s="19" t="n"/>
+      <c r="K43" s="19" t="n"/>
+      <c r="L43" s="19" t="n"/>
+      <c r="M43" s="19" t="n"/>
+      <c r="N43" s="20" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="O43" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P43" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="B44" s="19" t="inlineStr">
+        <is>
+          <t>bearing</t>
+        </is>
+      </c>
+      <c r="C44" s="19" t="n">
+        <v>360</v>
+      </c>
+      <c r="D44" s="19" t="inlineStr">
+        <is>
+          <t>Zona A</t>
+        </is>
+      </c>
+      <c r="E44" s="19" t="n">
+        <v>113097.34</v>
+      </c>
+      <c r="F44" s="19" t="n">
+        <v>35774.33</v>
+      </c>
+      <c r="G44" s="19" t="n">
+        <v>77323</v>
+      </c>
+      <c r="H44" s="19" t="n"/>
+      <c r="I44" s="19" t="n"/>
+      <c r="J44" s="19" t="n"/>
+      <c r="K44" s="19" t="n"/>
+      <c r="L44" s="19" t="n"/>
+      <c r="M44" s="19" t="n"/>
+      <c r="N44" s="20" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="O44" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P44" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="22" t="inlineStr">
+        <is>
+          <t>PREPARED BY</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n"/>
+      <c r="C46" s="3" t="n"/>
+      <c r="D46" s="4" t="n"/>
+      <c r="G46" s="22" t="inlineStr">
         <is>
           <t>CHECKED BY</t>
         </is>
       </c>
-      <c r="E43" s="3" t="n"/>
-      <c r="F43" s="4" t="n"/>
-      <c r="H43" s="22" t="inlineStr">
-        <is>
-          <t>CHECKED BY</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="n"/>
-      <c r="J43" s="4" t="n"/>
-      <c r="L43" s="22" t="inlineStr">
-        <is>
-          <t>CHECKED BY</t>
-        </is>
-      </c>
-      <c r="M43" s="3" t="n"/>
-      <c r="N43" s="4" t="n"/>
-    </row>
-    <row r="44">
-      <c r="D44" s="23" t="inlineStr">
+      <c r="H46" s="3" t="n"/>
+      <c r="I46" s="3" t="n"/>
+      <c r="J46" s="4" t="n"/>
+      <c r="M46" s="22" t="inlineStr">
+        <is>
+          <t>APPROVED BY</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="n"/>
+      <c r="O46" s="3" t="n"/>
+      <c r="P46" s="4" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="23" t="inlineStr">
+        <is>
+          <t>STAFF QUALITY CONTROL</t>
+        </is>
+      </c>
+      <c r="B47" s="12" t="n"/>
+      <c r="C47" s="12" t="n"/>
+      <c r="D47" s="13" t="n"/>
+      <c r="G47" s="23" t="inlineStr">
         <is>
           <t>TL QUALITY CONTROL</t>
         </is>
       </c>
-      <c r="E44" s="12" t="n"/>
-      <c r="F44" s="13" t="n"/>
-      <c r="H44" s="23" t="inlineStr">
-        <is>
-          <t>TL QUALITY CONTROL</t>
-        </is>
-      </c>
-      <c r="I44" s="12" t="n"/>
-      <c r="J44" s="13" t="n"/>
-      <c r="L44" s="23" t="inlineStr">
-        <is>
-          <t>TL QUALITY CONTROL</t>
-        </is>
-      </c>
-      <c r="M44" s="12" t="n"/>
-      <c r="N44" s="13" t="n"/>
-    </row>
-    <row r="45">
-      <c r="D45" s="22" t="n"/>
-      <c r="E45" s="3" t="n"/>
-      <c r="F45" s="4" t="n"/>
-      <c r="H45" s="22" t="n"/>
-      <c r="I45" s="3" t="n"/>
-      <c r="J45" s="4" t="n"/>
-      <c r="L45" s="22" t="n"/>
-      <c r="M45" s="3" t="n"/>
-      <c r="N45" s="4" t="n"/>
-    </row>
-    <row r="46">
-      <c r="D46" s="5" t="n"/>
-      <c r="E46" s="7" t="n"/>
-      <c r="F46" s="8" t="n"/>
-      <c r="H46" s="5" t="n"/>
-      <c r="I46" s="7" t="n"/>
-      <c r="J46" s="8" t="n"/>
-      <c r="L46" s="5" t="n"/>
-      <c r="M46" s="7" t="n"/>
-      <c r="N46" s="8" t="n"/>
-    </row>
-    <row r="47">
-      <c r="D47" s="5" t="n"/>
-      <c r="E47" s="7" t="n"/>
-      <c r="F47" s="8" t="n"/>
-      <c r="H47" s="5" t="n"/>
-      <c r="I47" s="7" t="n"/>
-      <c r="J47" s="8" t="n"/>
-      <c r="L47" s="5" t="n"/>
-      <c r="M47" s="7" t="n"/>
-      <c r="N47" s="8" t="n"/>
+      <c r="H47" s="12" t="n"/>
+      <c r="I47" s="12" t="n"/>
+      <c r="J47" s="13" t="n"/>
+      <c r="M47" s="23" t="n"/>
+      <c r="N47" s="12" t="n"/>
+      <c r="O47" s="12" t="n"/>
+      <c r="P47" s="13" t="n"/>
     </row>
     <row r="48">
-      <c r="D48" s="10" t="n"/>
-      <c r="E48" s="12" t="n"/>
-      <c r="F48" s="13" t="n"/>
-      <c r="H48" s="10" t="n"/>
-      <c r="I48" s="12" t="n"/>
-      <c r="J48" s="13" t="n"/>
-      <c r="L48" s="10" t="n"/>
-      <c r="M48" s="12" t="n"/>
-      <c r="N48" s="13" t="n"/>
+      <c r="A48" s="22" t="n"/>
+      <c r="B48" s="3" t="n"/>
+      <c r="C48" s="3" t="n"/>
+      <c r="D48" s="4" t="n"/>
+      <c r="G48" s="22" t="n"/>
+      <c r="H48" s="3" t="n"/>
+      <c r="I48" s="3" t="n"/>
+      <c r="J48" s="4" t="n"/>
+      <c r="M48" s="22" t="n"/>
+      <c r="N48" s="3" t="n"/>
+      <c r="O48" s="3" t="n"/>
+      <c r="P48" s="4" t="n"/>
     </row>
     <row r="49">
-      <c r="D49" s="24" t="inlineStr">
+      <c r="A49" s="5" t="n"/>
+      <c r="B49" s="7" t="n"/>
+      <c r="C49" s="7" t="n"/>
+      <c r="D49" s="8" t="n"/>
+      <c r="G49" s="5" t="n"/>
+      <c r="H49" s="7" t="n"/>
+      <c r="I49" s="7" t="n"/>
+      <c r="J49" s="8" t="n"/>
+      <c r="M49" s="5" t="n"/>
+      <c r="N49" s="7" t="n"/>
+      <c r="O49" s="7" t="n"/>
+      <c r="P49" s="8" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="n"/>
+      <c r="B50" s="7" t="n"/>
+      <c r="C50" s="7" t="n"/>
+      <c r="D50" s="8" t="n"/>
+      <c r="G50" s="5" t="n"/>
+      <c r="H50" s="7" t="n"/>
+      <c r="I50" s="7" t="n"/>
+      <c r="J50" s="8" t="n"/>
+      <c r="M50" s="5" t="n"/>
+      <c r="N50" s="7" t="n"/>
+      <c r="O50" s="7" t="n"/>
+      <c r="P50" s="8" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="n"/>
+      <c r="B51" s="12" t="n"/>
+      <c r="C51" s="12" t="n"/>
+      <c r="D51" s="13" t="n"/>
+      <c r="G51" s="10" t="n"/>
+      <c r="H51" s="12" t="n"/>
+      <c r="I51" s="12" t="n"/>
+      <c r="J51" s="13" t="n"/>
+      <c r="M51" s="10" t="n"/>
+      <c r="N51" s="12" t="n"/>
+      <c r="O51" s="12" t="n"/>
+      <c r="P51" s="13" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="22" t="n"/>
+      <c r="B52" s="3" t="n"/>
+      <c r="C52" s="3" t="n"/>
+      <c r="D52" s="4" t="n"/>
+      <c r="G52" s="24" t="inlineStr">
         <is>
           <t>BAGUS SANJAYA PUTRA</t>
         </is>
       </c>
-      <c r="E49" s="3" t="n"/>
-      <c r="F49" s="4" t="n"/>
-      <c r="H49" s="24" t="inlineStr">
-        <is>
-          <t>BAGUS SANJAYA PUTRA</t>
-        </is>
-      </c>
-      <c r="I49" s="3" t="n"/>
-      <c r="J49" s="4" t="n"/>
-      <c r="L49" s="24" t="inlineStr">
-        <is>
-          <t>BAGUS SANJAYA PUTRA</t>
-        </is>
-      </c>
-      <c r="M49" s="3" t="n"/>
-      <c r="N49" s="4" t="n"/>
-    </row>
-    <row r="50">
-      <c r="D50" s="10" t="n"/>
-      <c r="E50" s="12" t="n"/>
-      <c r="F50" s="13" t="n"/>
-      <c r="H50" s="10" t="n"/>
-      <c r="I50" s="12" t="n"/>
-      <c r="J50" s="13" t="n"/>
-      <c r="L50" s="10" t="n"/>
-      <c r="M50" s="12" t="n"/>
-      <c r="N50" s="13" t="n"/>
+      <c r="H52" s="3" t="n"/>
+      <c r="I52" s="3" t="n"/>
+      <c r="J52" s="4" t="n"/>
+      <c r="M52" s="22" t="n"/>
+      <c r="N52" s="3" t="n"/>
+      <c r="O52" s="3" t="n"/>
+      <c r="P52" s="4" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="10" t="n"/>
+      <c r="B53" s="12" t="n"/>
+      <c r="C53" s="12" t="n"/>
+      <c r="D53" s="13" t="n"/>
+      <c r="G53" s="10" t="n"/>
+      <c r="H53" s="12" t="n"/>
+      <c r="I53" s="12" t="n"/>
+      <c r="J53" s="13" t="n"/>
+      <c r="M53" s="10" t="n"/>
+      <c r="N53" s="12" t="n"/>
+      <c r="O53" s="12" t="n"/>
+      <c r="P53" s="13" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="33">
     <mergeCell ref="A5:P5"/>
+    <mergeCell ref="A48:D51"/>
     <mergeCell ref="B2:P2"/>
     <mergeCell ref="I6:J6"/>
-    <mergeCell ref="L49:N50"/>
+    <mergeCell ref="G52:J53"/>
     <mergeCell ref="C9:H9"/>
+    <mergeCell ref="G47:J47"/>
     <mergeCell ref="B1:P1"/>
+    <mergeCell ref="M47:P47"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="D43:F43"/>
     <mergeCell ref="K8:P8"/>
+    <mergeCell ref="G46:J46"/>
+    <mergeCell ref="G48:J51"/>
+    <mergeCell ref="M48:P51"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="I7:J7"/>
-    <mergeCell ref="L44:N44"/>
-    <mergeCell ref="D49:F50"/>
     <mergeCell ref="C8:H8"/>
     <mergeCell ref="C7:H7"/>
     <mergeCell ref="K7:P7"/>
-    <mergeCell ref="H49:J50"/>
     <mergeCell ref="K6:P6"/>
-    <mergeCell ref="D44:F44"/>
     <mergeCell ref="I8:J8"/>
     <mergeCell ref="B4:P4"/>
     <mergeCell ref="A8:B8"/>
-    <mergeCell ref="H43:J43"/>
-    <mergeCell ref="D45:F48"/>
+    <mergeCell ref="A46:D46"/>
     <mergeCell ref="C6:H6"/>
-    <mergeCell ref="H45:J48"/>
     <mergeCell ref="K9:P9"/>
-    <mergeCell ref="H44:J44"/>
-    <mergeCell ref="L45:N48"/>
     <mergeCell ref="B3:P3"/>
-    <mergeCell ref="L43:N43"/>
+    <mergeCell ref="A52:D53"/>
+    <mergeCell ref="M52:P53"/>
+    <mergeCell ref="M46:P46"/>
     <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A47:D47"/>
     <mergeCell ref="I9:J9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
